--- a/tame_output/ON/bt/strategyON_20240807.xlsx
+++ b/tame_output/ON/bt/strategyON_20240807.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>86.1%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.8%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.5%</t>
+          <t>-672.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.7%</t>
+          <t>-153.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.4%</t>
+          <t>-193.8%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.9%</t>
+          <t>-131.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-49.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2047"/>
+  <dimension ref="A1:G2049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.098141848004651</v>
+        <v>-4.065910449097639</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.220749151940488</v>
+        <v>1.233641711503293</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5699062950289651</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.143448667403631</v>
+        <v>-4.111217268496619</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.194402199625421</v>
+        <v>1.207294759188227</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5290961320197343</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.172481772105932</v>
+        <v>-4.14025037319892</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.183340830777603</v>
+        <v>1.196233390340408</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5290961320197343</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.079671290655073</v>
+        <v>-4.04743989174806</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.149737715249312</v>
+        <v>1.162630274812117</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6219066134705936</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.1240607599845</v>
+        <v>-4.091829361077488</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133855403442142</v>
+        <v>1.146747963004947</v>
       </c>
       <c r="F1947" t="n">
         <v>0.577517144141166</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.240602365089843</v>
+        <v>-4.20837096618283</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.082314469911728</v>
+        <v>1.095207029474533</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4609755390358232</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.12822536390717</v>
+        <v>-4.095993965000157</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.132756566215464</v>
+        <v>1.145649125778269</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4609755390358232</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.156005761808522</v>
+        <v>-4.12377436290151</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.133141608823462</v>
+        <v>1.146034168386267</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4331951411344701</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.274386434538661</v>
+        <v>-4.242155035631648</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9241450597320604</v>
+        <v>0.9370376192948653</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3659772889834939</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.383000512981992</v>
+        <v>-4.350769114074979</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.000849089073933</v>
+        <v>1.013741648636739</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3659772889834939</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.347591474733849</v>
+        <v>-4.315360075826836</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.029525730475514</v>
+        <v>1.042418290038319</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3659772889834939</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309207812175698</v>
+        <v>-4.276976413268685</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.042298636841143</v>
+        <v>1.055191196403948</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4043609515416451</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132091482140532</v>
+        <v>-4.099860083233519</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109874197700511</v>
+        <v>1.122766757263316</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4043609515416451</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177183726974078</v>
+        <v>-4.144952328067065</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.092520691529006</v>
+        <v>1.105413251091811</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3424649083722553</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.99780830573531</v>
+        <v>-3.965576906828297</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.158057835330927</v>
+        <v>1.170950394893732</v>
       </c>
       <c r="F1957" t="n">
         <v>0.499241666542974</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042822519255916</v>
+        <v>-4.010591120348904</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.120859605254275</v>
+        <v>1.133752164817079</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4688927712283694</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309827029528351</v>
+        <v>-4.277595630621339</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019749363484246</v>
+        <v>1.032641923047051</v>
       </c>
       <c r="F1959" t="n">
         <v>0.2745297331854208</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.411024810965523</v>
+        <v>-4.378793412058512</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9784741728058788</v>
+        <v>0.9913667323686837</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2061209196401016</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.404513844351211</v>
+        <v>-4.372282445444199</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9786785210059206</v>
+        <v>0.9915710805687254</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2061209196401016</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385475716643914</v>
+        <v>-4.353244317736902</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9828184912970845</v>
+        <v>0.9957110508598892</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1479373083089071</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.416602347794532</v>
+        <v>-4.38437094888752</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.089662240471027</v>
+        <v>1.102554800033832</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1479373083089071</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43046910912845</v>
+        <v>-4.398237710221438</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084948864923594</v>
+        <v>1.097841424486399</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1100793915750841</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.38566493758852</v>
+        <v>-4.353433538681508</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.108879063936492</v>
+        <v>1.121771623499296</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1100793915750841</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237921967353517</v>
+        <v>-4.205690568446506</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.065926473307692</v>
+        <v>1.078819032870497</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2778867488099673</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321743188628216</v>
+        <v>-4.289511789721204</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.035191606329294</v>
+        <v>1.048084165892099</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2778867488099673</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315590482575431</v>
+        <v>-4.28335908366842</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.038315037142066</v>
+        <v>1.051207596704871</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2840394548627516</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.332399780725933</v>
+        <v>-4.300168381818922</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.030671794621975</v>
+        <v>1.04356435418478</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2672301567122499</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.270101781949811</v>
+        <v>-4.237870383042799</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.121926547929245</v>
+        <v>1.13481910749205</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2672301567122499</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.068311584284653</v>
+        <v>-4.036080185377641</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.004934628709436</v>
+        <v>1.01782718827224</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4652483488814043</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.119198296970848</v>
+        <v>-4.086966898063836</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.054870175957133</v>
+        <v>1.067762735519938</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4143616361952098</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.216938841595822</v>
+        <v>-4.18470744268881</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.030401694223187</v>
+        <v>1.043294253785991</v>
       </c>
       <c r="F1973" t="n">
         <v>0.3984723580622296</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.277148139601107</v>
+        <v>-4.244916740694095</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.004853955845745</v>
+        <v>1.017746515408549</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3382630600569451</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.20072609316918</v>
+        <v>-4.168494694262169</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.033914392458444</v>
+        <v>1.046806952021248</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3382630600569451</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.156352961530612</v>
+        <v>-4.1241215626236</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.051526512549307</v>
+        <v>1.064419072112112</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3826361916955137</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.178833312389497</v>
+        <v>-4.146601913482485</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.036928166344344</v>
+        <v>1.049820725907149</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3826361916955137</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.131177581828441</v>
+        <v>-4.098946182921429</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.062372215596571</v>
+        <v>1.075264775159376</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4302919222565693</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.030659423329686</v>
+        <v>-3.998428024422674</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.107471852370798</v>
+        <v>1.120364411933602</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5308100807553239</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.091326013732075</v>
+        <v>-4.059094614825064</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069959888685714</v>
+        <v>1.082852448248519</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4491117640367902</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.046487612123677</v>
+        <v>-4.014256213216665</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091992951939702</v>
+        <v>1.104885511502507</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4536551969816597</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.065986068365685</v>
+        <v>-4.033754669458673</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.088354509073977</v>
+        <v>1.101247068636781</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4055705557017554</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.021783231279785</v>
+        <v>-3.989551832372773</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111915246436174</v>
+        <v>1.124807805998979</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4497733927876558</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.058762258943228</v>
+        <v>-4.026530860036216</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.095533635840044</v>
+        <v>1.108426195402849</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4867472945789864</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.900470841403955</v>
+        <v>-3.868239442496944</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210097968038793</v>
+        <v>1.222990527601598</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4867472945789864</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.692828837769479</v>
+        <v>-3.660597438862467</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291595474086837</v>
+        <v>1.304488033649641</v>
       </c>
       <c r="F1986" t="n">
         <v>0.6943892982134625</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.641796745046951</v>
+        <v>-3.609565346139939</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.306956539414118</v>
+        <v>1.319849098976923</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7454213909359905</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.576572563919745</v>
+        <v>-3.544341165012733</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.350233615957705</v>
+        <v>1.36312617552051</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8106455720631961</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.539145543848611</v>
+        <v>-3.5069141449416</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.361165396285439</v>
+        <v>1.374057955848244</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8158971100923778</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.55925719988332</v>
+        <v>-3.527025800976308</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.354377526202796</v>
+        <v>1.367270085765601</v>
       </c>
       <c r="F1990" t="n">
         <v>0.826924455089797</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.505512385456115</v>
+        <v>-3.473280986549103</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.536433222994889</v>
+        <v>1.549325782557693</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8369877645302589</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.430730124431102</v>
+        <v>-3.398498725524091</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.686459036622711</v>
+        <v>1.699351596185516</v>
       </c>
       <c r="F1992" t="n">
         <v>0.9117700255552715</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.404646040167294</v>
+        <v>-3.372414641260283</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.688600646342093</v>
+        <v>1.701493205904898</v>
       </c>
       <c r="F1993" t="n">
         <v>0.9117700255552715</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.326514859318348</v>
+        <v>-3.294283460411336</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.718046314265451</v>
+        <v>1.730938873828256</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9859468364389561</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.317622397925065</v>
+        <v>-3.285390999018053</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.739157704549556</v>
+        <v>1.752050264112361</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9859468364389561</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.486098514894942</v>
+        <v>-3.453867115987931</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.663622305166189</v>
+        <v>1.676514864728993</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9579990007223753</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.788298986033359</v>
+        <v>-2.756067587126347</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.924011813898684</v>
+        <v>1.936904373461489</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8876509413519647</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.765577882350207</v>
+        <v>-2.733346483443195</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.92376427786885</v>
+        <v>1.936656837431654</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8876509413519647</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.894779695644249</v>
+        <v>-2.862548296737237</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.030989678402402</v>
+        <v>2.043882237965206</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7584491280579224</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.049560702422505</v>
+        <v>-3.017329303515493</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.006155098184746</v>
+        <v>2.01904765774755</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7250814540034463</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.042506012207331</v>
+        <v>-3.010274613300319</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.00565233026036</v>
+        <v>2.018544889823165</v>
       </c>
       <c r="F2001" t="n">
         <v>0.7321361442186201</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.015554787880843</v>
+        <v>-2.983323388973831</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.026438973635697</v>
+        <v>2.039331533198502</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7470164902463392</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.151507795937159</v>
+        <v>-3.119276397030148</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.15616090255813</v>
+        <v>2.169053462120935</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7470164902463392</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173915913742031</v>
+        <v>-3.14168451483502</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.139314350339175</v>
+        <v>2.152206909901979</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7470164902463392</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.321921681221431</v>
+        <v>-3.289690282314419</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.082166042897052</v>
+        <v>2.095058602459857</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6602894813827977</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.331362607109961</v>
+        <v>-3.299131208202949</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.134643390263487</v>
+        <v>2.147535949826292</v>
       </c>
       <c r="F2006" t="n">
         <v>0.7827165989261892</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.383636214445602</v>
+        <v>-3.35140481553859</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.116625041874532</v>
+        <v>2.129517601437336</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7304429915905479</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.459966192046508</v>
+        <v>-3.427734793139496</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.084204863727945</v>
+        <v>2.097097423290749</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7304429915905479</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.662219912370861</v>
+        <v>-3.62998851346385</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.998123605201066</v>
+        <v>2.01101616476387</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5281892712661944</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.823788337898117</v>
+        <v>-3.791556938991105</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.931930245200316</v>
+        <v>1.94482280476312</v>
       </c>
       <c r="F2010" t="n">
         <v>0.4014063474683151</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.95608962999567</v>
+        <v>-3.923858231088658</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.892083135227213</v>
+        <v>1.904975694790018</v>
       </c>
       <c r="F2011" t="n">
         <v>0.4014063474683151</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.141957940834899</v>
+        <v>-4.109726541927888</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.809741007674461</v>
+        <v>1.822633567237266</v>
       </c>
       <c r="F2012" t="n">
         <v>0.2428407541483674</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.169858727944372</v>
+        <v>-4.13762732903736</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.797104733957674</v>
+        <v>1.809997293520479</v>
       </c>
       <c r="F2013" t="n">
         <v>0.2082438300054326</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.292384830647266</v>
+        <v>-4.260153431740254</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.744858736853716</v>
+        <v>1.75775129641652</v>
       </c>
       <c r="F2014" t="n">
         <v>0.08571772730253868</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.522899326832855</v>
+        <v>-4.490667927925843</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.719358897969984</v>
+        <v>1.732251457532788</v>
       </c>
       <c r="F2015" t="n">
         <v>-0.14479676888305</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.779620144827678</v>
+        <v>-4.747388745920667</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.756982289773901</v>
+        <v>1.769874849336706</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.2532113430268649</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.933606562603819</v>
+        <v>-4.901375163696807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.764367991809085</v>
+        <v>1.77726055137189</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.2532113430268649</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.883084658776153</v>
+        <v>-4.850853259869141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.770627955460272</v>
+        <v>1.783520515023077</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.2532113430268649</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.135559812783877</v>
+        <v>-5.103328413876866</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.681508382912596</v>
+        <v>1.694400942475401</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.2532113430268649</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.428455569263289</v>
+        <v>-5.396224170356278</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.565560614839775</v>
+        <v>1.57845317440258</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.2532113430268649</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.585999640992731</v>
+        <v>-5.553768242085719</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.50666472837532</v>
+        <v>1.519557287938125</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.3201131481671394</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.863964036576005</v>
+        <v>-5.831732637668993</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.3905568228782</v>
+        <v>1.403449382441005</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.4097328824526236</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.980931729214896</v>
+        <v>-5.948700330307884</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.505973802521688</v>
+        <v>1.518866362084493</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.4097328824526236</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.065649671435849</v>
+        <v>-6.033418272528837</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.466933263597121</v>
+        <v>1.479825823159925</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.49484891138067</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.147584489704732</v>
+        <v>-6.11535309079772</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.444388753858058</v>
+        <v>1.457281313420863</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.5047836569677502</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.249560611953139</v>
+        <v>-6.217329213046128</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.412523943414598</v>
+        <v>1.425416502977403</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.6067597792161578</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.139554328475918</v>
+        <v>-6.107322929568906</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.448679344049662</v>
+        <v>1.461571903612466</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.5835552072988826</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.996494752734993</v>
+        <v>-5.964263353827981</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.510153185068006</v>
+        <v>1.523045744630811</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.5755417807089033</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.695048027263155</v>
+        <v>-5.662816628356143</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.637992758139277</v>
+        <v>1.650885317702082</v>
       </c>
       <c r="F2029" t="n">
         <v>-0.274095055237066</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.719638271498339</v>
+        <v>-5.687406872591327</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.629127838197914</v>
+        <v>1.642020397760719</v>
       </c>
       <c r="F2030" t="n">
         <v>-0.274095055237066</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.668599895491819</v>
+        <v>-5.636368496584807</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.650386092980277</v>
+        <v>1.663278652543082</v>
       </c>
       <c r="F2031" t="n">
         <v>-0.274095055237066</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.627460600625188</v>
+        <v>-5.595229201718176</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.685879909801075</v>
+        <v>1.69877246936388</v>
       </c>
       <c r="F2032" t="n">
         <v>-0.2329557603704352</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.516854460545586</v>
+        <v>-5.484623061638574</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.546306361956851</v>
+        <v>1.559198921519656</v>
       </c>
       <c r="F2033" t="n">
         <v>-0.1223496202908332</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.647435195076429</v>
+        <v>-5.615203796169417</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.497576112218477</v>
+        <v>1.510468671781282</v>
       </c>
       <c r="F2034" t="n">
         <v>-0.2529303548216757</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.482938860885467</v>
+        <v>-5.450707461978455</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.547801464970945</v>
+        <v>1.56069402453375</v>
       </c>
       <c r="F2035" t="n">
         <v>-0.2529303548216757</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.510308793569899</v>
+        <v>-5.478077394662887</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.536041202333601</v>
+        <v>1.548933761896406</v>
       </c>
       <c r="F2036" t="n">
         <v>-0.2529303548216757</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.520693988459788</v>
+        <v>-5.488462589552777</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.541755903502718</v>
+        <v>1.554648463065523</v>
       </c>
       <c r="F2037" t="n">
         <v>-0.263315549711565</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.539282147182013</v>
+        <v>-5.507050748275002</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.605157645790253</v>
+        <v>1.618050205353058</v>
       </c>
       <c r="F2038" t="n">
         <v>-0.2819037084337904</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.539580693878049</v>
+        <v>-5.507349294971037</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.601907237930138</v>
+        <v>1.614799797492942</v>
       </c>
       <c r="F2039" t="n">
         <v>-0.2819037084337904</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.438757560187621</v>
+        <v>-5.40652616128061</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.6467673863457</v>
+        <v>1.659659945908505</v>
       </c>
       <c r="F2040" t="n">
         <v>-0.2694394929494365</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.247976199435215</v>
+        <v>-5.215744800528203</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.723209184125206</v>
+        <v>1.736101743688011</v>
       </c>
       <c r="F2041" t="n">
         <v>-0.07865813219702916</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.229459345393394</v>
+        <v>-5.197227946486382</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.710452771479531</v>
+        <v>1.723345331042335</v>
       </c>
       <c r="F2042" t="n">
         <v>-0.06572800277182095</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.204266160892076</v>
+        <v>-5.172034761985064</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.755496981892116</v>
+        <v>1.768389541454921</v>
       </c>
       <c r="F2043" t="n">
         <v>-0.04053481827050259</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.192212033979113</v>
+        <v>-5.159980635072102</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.754005200558739</v>
+        <v>1.766897760121544</v>
       </c>
       <c r="F2044" t="n">
         <v>-0.02848069135753978</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.198835280669472</v>
+        <v>-5.16660388176246</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.753236532066732</v>
+        <v>1.766129091629537</v>
       </c>
       <c r="F2045" t="n">
         <v>-0.03510393804789813</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.095954691140879</v>
+        <v>-5.063723292233867</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.807239793756052</v>
+        <v>1.820132353318856</v>
       </c>
       <c r="F2046" t="n">
         <v>0.06777665148069478</v>
@@ -48632,16 +48632,62 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.119396730320966</v>
+        <v>-5.087165331413954</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.818065648257611</v>
+        <v>1.830958207820415</v>
       </c>
       <c r="F2047" t="n">
         <v>0.06777665148069478</v>
       </c>
       <c r="G2047" t="n">
         <v>3.906846755588162</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="2" t="n">
+        <v>45510</v>
+      </c>
+      <c r="B2048" t="n">
+        <v>3.666767386781704</v>
+      </c>
+      <c r="C2048" t="n">
+        <v>3.866180764699744</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>-5.105237839705565</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>1.823729204503771</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>0.06777665148069478</v>
+      </c>
+      <c r="G2048" t="n">
+        <v>3.906846755588162</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="2" t="n">
+        <v>45511</v>
+      </c>
+      <c r="B2049" t="n">
+        <v>3.736022413116509</v>
+      </c>
+      <c r="C2049" t="n">
+        <v>3.977602593787736</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>-5.105237839705565</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>1.823729204503771</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>0.06777665148069478</v>
+      </c>
+      <c r="G2049" t="n">
+        <v>3.970666390774104</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240807.xlsx
+++ b/tame_output/ON/bt/strategyON_20240807.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,47 +834,47 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>72.6%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.1%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>67.4%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>451.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-672.1%</t>
+          <t>-675.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.4%</t>
+          <t>-136.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.8%</t>
+          <t>-218.6%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-131.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-48.7%</t>
         </is>
       </c>
     </row>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>2.921711838980584</v>
       </c>
       <c r="D1904" t="n">
         <v>-7.203507737648524</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.274099494475748</v>
+        <v>0.03995231960742718</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7755814117351372</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.690510166807822</v>
+        <v>2.456362991939502</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>2.917079325727611</v>
       </c>
       <c r="D1905" t="n">
         <v>-7.071232264017637</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3223771706751295</v>
+        <v>0.08822999580680868</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6433059381042505</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.765242937733382</v>
+        <v>2.531095762865061</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>2.919894386415248</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.915493931457895</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3874875643866629</v>
+        <v>0.1533403895183421</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.487567605544509</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.861500997956863</v>
+        <v>2.627353823088542</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>2.932800727638906</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.666494132774314</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4999938250837541</v>
+        <v>0.2658466502154333</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2385678068609283</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.023807218390671</v>
+        <v>2.78966004352235</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.804824798039688</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.772084122547419</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3297818995752935</v>
+        <v>0.09563472470697265</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3441577966340326</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.832477294927589</v>
+        <v>2.598330120059269</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.853369139916774</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.790819024666016</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3708322806049411</v>
+        <v>0.1366851057366203</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3497538062941639</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.877664031008597</v>
+        <v>2.643516856140276</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.733490217228606</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.642878983258417</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3101293744798133</v>
+        <v>0.07598219961149244</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3294328903856064</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769977657865564</v>
+        <v>2.535830482997243</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.724776230975128</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.589909461004428</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3226031971279304</v>
+        <v>0.08845602225960958</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2764633681316175</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793045384964479</v>
+        <v>2.558898210096158</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.717815618880035</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.546361054233738</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3330619477411134</v>
+        <v>0.0989147728727926</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2764633681316175</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786084772869386</v>
+        <v>2.551937598001065</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.732277973261178</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.512997847754969</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3608695847137642</v>
+        <v>0.1267224098454434</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2764633681316175</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800547127250529</v>
+        <v>2.566399952382208</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.726810093720373</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.404738710632447</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3987053600219679</v>
+        <v>0.1645581851536471</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2764633681316175</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795079247709724</v>
+        <v>2.560932072841403</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.72430818773095</v>
       </c>
       <c r="D1915" t="n">
         <v>-6.281447575815316</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.445519907959397</v>
+        <v>0.2113727330910762</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.153172233314487</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866552022610579</v>
+        <v>2.632404847742258</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.732009165968275</v>
       </c>
       <c r="D1916" t="n">
         <v>-6.260298376911873</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4616805657580993</v>
+        <v>0.2275333908897785</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1320230344110436</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88694252018997</v>
+        <v>2.652795345321649</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.727789874315326</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.016532934928429</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5549674508985278</v>
+        <v>0.320820276030207</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1320230344110436</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.882723228537021</v>
+        <v>2.6485760536687</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.729914188235342</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.914770114651134</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5977968929294621</v>
+        <v>0.3636497180611413</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1188039660186149</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.892778983492494</v>
+        <v>2.658631808624173</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.722656263219044</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.664919720702059</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6904791254927938</v>
+        <v>0.456331950624473</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1188039660186149</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.885521058476196</v>
+        <v>2.651373883607875</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.726255386739693</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.489027628234627</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7644350860004154</v>
+        <v>0.5302879111320946</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1188039660186149</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.889120181996845</v>
+        <v>2.654973007128524</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.739582892794246</v>
       </c>
       <c r="D1921" t="n">
         <v>-5.317581165212164</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8463411772639544</v>
+        <v>0.6121940023956336</v>
       </c>
       <c r="F1921" t="n">
         <v>0.05264249700384821</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.005315565864877</v>
+        <v>2.771168390996556</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.738603370410543</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.243291599473825</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.875077481175587</v>
+        <v>0.6409303063072662</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1269320627421875</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.048909782924177</v>
+        <v>2.814762608055856</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.743298171464861</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.17965585723989</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9052265791234784</v>
+        <v>0.6710794042551576</v>
       </c>
       <c r="F1923" t="n">
         <v>0.190567804976122</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.091786029318855</v>
+        <v>2.857638854450534</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.724492430248656</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.06822909791397</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.930991541637642</v>
+        <v>0.6968443667693212</v>
       </c>
       <c r="F1924" t="n">
         <v>0.190567804976122</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.072980288102651</v>
+        <v>2.83883311323433</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.726235506873534</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.078731720979259</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9285335690364036</v>
+        <v>0.6943863941680828</v>
       </c>
       <c r="F1925" t="n">
         <v>0.1800651819108331</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.068421790888355</v>
+        <v>2.834274616020034</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.730164820708354</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.006489152808064</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9613599101397019</v>
+        <v>0.7272127352713811</v>
       </c>
       <c r="F1926" t="n">
         <v>0.1800651819108331</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.072351104723175</v>
+        <v>2.838203929854854</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.730843404625694</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.988775465930199</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9691239688081881</v>
+        <v>0.7349767939398673</v>
       </c>
       <c r="F1927" t="n">
         <v>0.18324651080775</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.074938485978665</v>
+        <v>2.840791311110344</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.727841475845687</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.879970580450472</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.009643994220072</v>
+        <v>0.7754968193517515</v>
       </c>
       <c r="F1928" t="n">
         <v>0.18324651080775</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.071936557198658</v>
+        <v>2.837789382330338</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.729420512856302</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.659949782413461</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.099231350445491</v>
+        <v>0.8650841755771699</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3244663558757302</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.158247501250061</v>
+        <v>2.92410032638174</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.745314695658125</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.527082093350184</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.168272608872625</v>
+        <v>0.9341254340043041</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3244663558757302</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.174141684051884</v>
+        <v>2.939994509183563</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.746460540098427</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.406909009985685</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.217487686658726</v>
+        <v>0.9833405117904055</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4446394392402291</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.247391378510885</v>
+        <v>3.013244203642564</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.756548642659867</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.262236864885947</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.285444647260061</v>
+        <v>1.05129747239174</v>
       </c>
       <c r="F1932" t="n">
         <v>0.5893115843399666</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.344282768132168</v>
+        <v>3.110135593263847</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.742586134061292</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.32211169224364</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24753220771841</v>
+        <v>1.013385032850089</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5294367569822744</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.294395363118978</v>
+        <v>3.060248188250657</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.757875303295501</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.202291461332803</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.310749469316953</v>
+        <v>1.076602294448633</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5294367569822744</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.309684532353187</v>
+        <v>3.075537357484866</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.665519502617943</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.204761167794609</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.217405786054673</v>
+        <v>0.9832586111863517</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5269670505204682</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.215846907798545</v>
+        <v>2.981699732930224</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.584781364103244</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.273131354118619</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10931957301037</v>
+        <v>0.8751723981420492</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5362427495566832</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.140674188705575</v>
+        <v>2.906527013837254</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.575218072735135</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.286919406965666</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.094241060503442</v>
+        <v>0.8600938856351217</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5362427495566832</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.131110897337466</v>
+        <v>2.896963722469145</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>2.712248909427338</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.342439482858255</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.209063866838609</v>
+        <v>0.9749166919702883</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5362427495566832</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.268141734029669</v>
+        <v>3.033994559161348</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>2.716816141419125</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.166965223065786</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.283820802747385</v>
+        <v>1.049673627879064</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5362427495566832</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.272708966021456</v>
+        <v>3.038561791153136</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>2.692558170180332</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.277901475707035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.215188330452092</v>
+        <v>0.9810411555837715</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5362427495566832</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.248450994782663</v>
+        <v>3.014303819914343</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>2.621096483581782</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.244237930234752</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.157192062042455</v>
+        <v>0.9230448871741341</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5699062950289651</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.197187435467483</v>
+        <v>2.963040260599162</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>2.631268870013915</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.184385311031029</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.191305496156077</v>
+        <v>0.9571583212877557</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5699062950289651</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.207359821899615</v>
+        <v>2.973212647031294</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>2.626215140587775</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.065910449097639</v>
+        <v>-4.098141848004651</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.233641711503293</v>
+        <v>0.986601977072167</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5699062950289651</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.202306092473475</v>
+        <v>2.968158917605154</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>2.6179909160323</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.111217268496619</v>
+        <v>-4.143448667403631</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.207294759188227</v>
+        <v>0.9602550247571007</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5290961320197343</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.169595770112462</v>
+        <v>2.935448595244141</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>2.618542789065402</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.14025037319892</v>
+        <v>-4.172481772105932</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.196233390340408</v>
+        <v>0.9491936559092817</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5290961320197343</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.170147643145564</v>
+        <v>2.936000468277243</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>2.547815480956768</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.04743989174806</v>
+        <v>-4.079671290655073</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.162630274812117</v>
+        <v>0.9155905403809914</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6219066134705936</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.155106623907445</v>
+        <v>2.920959449039124</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>2.549688956881369</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.091829361077488</v>
+        <v>-4.1240607599845</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.146747963004947</v>
+        <v>0.8997082285738212</v>
       </c>
       <c r="F1947" t="n">
         <v>0.577517144141166</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.130346418234389</v>
+        <v>2.896199243366068</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>2.544764665393092</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.20837096618283</v>
+        <v>-4.240602365089843</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.095207029474533</v>
+        <v>0.8481672950434072</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4609755390358232</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.055497163682907</v>
+        <v>2.821349988814586</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>2.550255961223759</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.095993965000157</v>
+        <v>-4.12822536390717</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.145649125778269</v>
+        <v>0.8986093913471436</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4609755390358232</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.060988459513574</v>
+        <v>2.826841284645253</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>2.561753162992298</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.12377436290151</v>
+        <v>-4.156005761808522</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.146034168386267</v>
+        <v>0.8989944339551417</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4331951411344701</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.055817422541301</v>
+        <v>2.82167024767298</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>2.400108882992951</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.242155035631648</v>
+        <v>-4.274386434538661</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9370376192948653</v>
+        <v>0.6899978848637396</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3659772889834939</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.853842431251369</v>
+        <v>2.619695256383048</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>2.520258543712157</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.350769114074979</v>
+        <v>-4.383000512981992</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.013741648636739</v>
+        <v>0.7667019142056126</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3659772889834939</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.973992091970574</v>
+        <v>2.739844917102253</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>2.53477156981448</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.315360075826836</v>
+        <v>-4.347591474733849</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.042418290038319</v>
+        <v>0.7953785556071928</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3659772889834939</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.988505118072897</v>
+        <v>2.754357943204576</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>2.532191011156848</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.276976413268685</v>
+        <v>-4.309207812175698</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.055191196403948</v>
+        <v>0.8081514619728218</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4043609515416451</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.008954756950156</v>
+        <v>2.774807582081836</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>2.52892004000215</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.099860083233519</v>
+        <v>-4.132091482140532</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.122766757263316</v>
+        <v>0.8757270228321903</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4043609515416451</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.005683785795458</v>
+        <v>2.771536610927138</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>2.529603431764063</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.144952328067065</v>
+        <v>-4.177183726974078</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.105413251091811</v>
+        <v>0.8583735166606852</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3424649083722553</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.969229551655738</v>
+        <v>2.735082376787417</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>2.523390407070478</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.965576906828297</v>
+        <v>-3.99780830573531</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.170950394893732</v>
+        <v>0.9239106604626066</v>
       </c>
       <c r="F1957" t="n">
         <v>0.499241666542974</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.057082581864583</v>
+        <v>2.822935406996263</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>2.504197862402068</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.010591120348904</v>
+        <v>-4.042822519255916</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.133752164817079</v>
+        <v>0.8867124303859539</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4688927712283694</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.01968070000741</v>
+        <v>2.78553352513909</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>2.509889424741013</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.277595630621339</v>
+        <v>-4.309827029528351</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.032641923047051</v>
+        <v>0.7856021886159257</v>
       </c>
       <c r="F1959" t="n">
         <v>0.2745297331854208</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.908754439520587</v>
+        <v>2.674607264652266</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>2.509093346637515</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.378793412058512</v>
+        <v>-4.411024810965523</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9913667323686837</v>
+        <v>0.744326997937558</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2061209196401016</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.866913073289897</v>
+        <v>2.632765898421576</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>2.506693308191831</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.372282445444199</v>
+        <v>-4.404513844351211</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9915710805687254</v>
+        <v>0.7445313461375997</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2061209196401016</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.864513034844213</v>
+        <v>2.630365859975893</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>2.503218027400076</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.353244317736902</v>
+        <v>-4.385475716643914</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9957110508598892</v>
+        <v>0.7486713164287637</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1479373083089071</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.826127587253742</v>
+        <v>2.591980412385421</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.856659603902588</v>
+        <v>2.622512429034267</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.38437094888752</v>
+        <v>-4.416602347794532</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.102554800033832</v>
+        <v>0.8555150656027066</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1479373083089071</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.945421988887932</v>
+        <v>2.711274814019611</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.857492932888721</v>
+        <v>2.6233457580204</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.398237710221438</v>
+        <v>-4.43046910912845</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.097841424486399</v>
+        <v>0.8508016900552731</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1100793915750841</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.923540567833772</v>
+        <v>2.689393392965451</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.863501463285647</v>
+        <v>2.629354288417326</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.353433538681508</v>
+        <v>-4.38566493758852</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.121771623499296</v>
+        <v>0.874731889068171</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1100793915750841</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.929549098230698</v>
+        <v>2.695401923362377</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.761451684562847</v>
+        <v>2.527304509694526</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.205690568446506</v>
+        <v>-4.237921967353517</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.078819032870497</v>
+        <v>0.8317792984393715</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2778867488099673</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.928183733848827</v>
+        <v>2.694036558980506</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.530098131226007</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.289511789721204</v>
+        <v>-4.321743188628216</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.048084165892099</v>
+        <v>0.801044431460973</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2778867488099673</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.930977355380308</v>
+        <v>2.696830180511987</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.530760479617665</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.28335908366842</v>
+        <v>-4.315590482575431</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.051207596704871</v>
+        <v>0.8041678622737451</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2840394548627516</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.935331327403637</v>
+        <v>2.701184152535316</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.529840956357775</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.300168381818922</v>
+        <v>-4.332399780725933</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.04356435418478</v>
+        <v>0.7965246197536546</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2672301567122499</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.924326225253446</v>
+        <v>2.690179050385126</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.596176510154596</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.237870383042799</v>
+        <v>-4.270101781949811</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.13481910749205</v>
+        <v>0.8877793730609245</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2672301567122499</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.990661779050267</v>
+        <v>2.756514604181946</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.398468511868723</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.036080185377641</v>
+        <v>-4.068311584284653</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.01782718827224</v>
+        <v>0.7707874538411148</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4652483488814043</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.911764696065887</v>
+        <v>2.677617521197566</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.468758744190898</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.086966898063836</v>
+        <v>-4.119198296970848</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.067762735519938</v>
+        <v>0.820723001088812</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4143616361952098</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.951522900776345</v>
+        <v>2.717375725908024</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.483386480306942</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.18470744268881</v>
+        <v>-4.216938841595822</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.043294253785991</v>
+        <v>0.796254519354866</v>
       </c>
       <c r="F1973" t="n">
         <v>0.3984723580622296</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.956617070012601</v>
+        <v>2.72246989514428</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.481922461131614</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.244916740694095</v>
+        <v>-4.277148139601107</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.017746515408549</v>
+        <v>0.7707067809774237</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3382630600569451</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.919027472034102</v>
+        <v>2.684880297165781</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.480414079171542</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.168494694262169</v>
+        <v>-4.20072609316918</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.046806952021248</v>
+        <v>0.7997672175901229</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3382630600569451</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.91751909007403</v>
+        <v>2.68337191520571</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.480276946606979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.1241215626236</v>
+        <v>-4.156352961530612</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.064419072112112</v>
+        <v>0.8173793376809866</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3826361916955137</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.944005836492608</v>
+        <v>2.709858661624287</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.474670740745569</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.146601913482485</v>
+        <v>-4.178833312389497</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.049820725907149</v>
+        <v>0.8027809914760231</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3826361916955137</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938399630631198</v>
+        <v>2.704252455762878</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.481052497773374</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.098946182921429</v>
+        <v>-4.131177581828441</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.075264775159376</v>
+        <v>0.8282250407282501</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4302919222565693</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973374825995637</v>
+        <v>2.739227651127316</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.485944871148098</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.998428024422674</v>
+        <v>-4.030659423329686</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.120364411933602</v>
+        <v>0.8733246775024768</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5308100807553239</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038578094469614</v>
+        <v>2.804430919601293</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.472699543623971</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.059094614825064</v>
+        <v>-4.091326013732075</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.082852448248519</v>
+        <v>0.8358127138173932</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4491117640367902</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.976313776914366</v>
+        <v>2.742166602046045</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.476797246234599</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.014256213216665</v>
+        <v>-4.046487612123677</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.104885511502507</v>
+        <v>0.8578457770713812</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4536551969816597</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.983137539291916</v>
+        <v>2.748990364423595</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.480958185865677</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.033754669458673</v>
+        <v>-4.065986068365685</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.101247068636781</v>
+        <v>0.854207334205656</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4055705557017554</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.958447694155052</v>
+        <v>2.724300519286731</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.486837788393514</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.989551832372773</v>
+        <v>-4.021783231279785</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.124807805998979</v>
+        <v>0.8777680715678533</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4497733927876558</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.990848998934429</v>
+        <v>2.756701824066108</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.485247788862762</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.026530860036216</v>
+        <v>-4.058762258943228</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.108426195402849</v>
+        <v>0.8613864609717237</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4867472945789864</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.011443340478475</v>
+        <v>2.777296165610154</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.536495554045802</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.868239442496944</v>
+        <v>-3.900470841403955</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.222990527601598</v>
+        <v>0.9759507931704723</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4867472945789864</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.062691105661515</v>
+        <v>2.828543930793194</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.534936258640055</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.660597438862467</v>
+        <v>-3.692828837769479</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.304488033649641</v>
+        <v>1.057448299218516</v>
       </c>
       <c r="F1986" t="n">
         <v>0.6943892982134625</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.185717012436454</v>
+        <v>2.951569837568133</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.529884486878325</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.609565346139939</v>
+        <v>-3.641796745046951</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.319849098976923</v>
+        <v>1.072809364545797</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7454213909359905</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.21128449630824</v>
+        <v>2.977137321439919</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.54707189097103</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.544341165012733</v>
+        <v>-3.576572563919745</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.36312617552051</v>
+        <v>1.116086441089384</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8106455720631961</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.267606409077268</v>
+        <v>3.033459234208947</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.54303286327031</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.5069141449416</v>
+        <v>-3.539145543848611</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.374057955848244</v>
+        <v>1.127018221417118</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8158971100923778</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.266718304194058</v>
+        <v>3.032571129325737</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.54428965560155</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.527025800976308</v>
+        <v>-3.55925719988332</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.367270085765601</v>
+        <v>1.120230351334475</v>
       </c>
       <c r="F1990" t="n">
         <v>0.826924455089797</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.27459150352375</v>
+        <v>3.040444328655429</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.704847426622761</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.473280986549103</v>
+        <v>-3.505512385456115</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.549325782557693</v>
+        <v>1.302286048126568</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8369877645302589</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.441187260209237</v>
+        <v>3.207040085340917</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>2.824960335840578</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.398498725524091</v>
+        <v>-3.430730124431102</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.699351596185516</v>
+        <v>1.45231186175439</v>
       </c>
       <c r="F1992" t="n">
         <v>0.9117700255552715</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.606169526042062</v>
+        <v>3.372022351173741</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.816668311854437</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.372414641260283</v>
+        <v>-3.404646040167294</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.701493205904898</v>
+        <v>1.454453471473772</v>
       </c>
       <c r="F1993" t="n">
         <v>0.9117700255552715</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.597877502055921</v>
+        <v>3.3637303271876</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.814861507438217</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.294283460411336</v>
+        <v>-3.326514859318348</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.730938873828256</v>
+        <v>1.483899139397131</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9859468364389561</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.640576784169911</v>
+        <v>3.406429609301591</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>2.832415913165008</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.285390999018053</v>
+        <v>-3.317622397925065</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.752050264112361</v>
+        <v>1.505010529681235</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9859468364389561</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.658131189896703</v>
+        <v>3.423984015028382</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>2.824270960569592</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.453867115987931</v>
+        <v>-3.486098514894942</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.676514864728993</v>
+        <v>1.429475130297868</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9579990007223753</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.633217535871339</v>
+        <v>3.399070361003018</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.805540657757454</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.756067587126347</v>
+        <v>-2.788298986033359</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.936904373461489</v>
+        <v>1.689864639030363</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8876509413519647</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.572278397436954</v>
+        <v>3.338131222568633</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.796204680254359</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.733346483443195</v>
+        <v>-2.765577882350207</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.936656837431654</v>
+        <v>1.689617103000529</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8876509413519647</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.562942419933858</v>
+        <v>3.328795245065538</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>2.955110806105528</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.862548296737237</v>
+        <v>-2.894779695644249</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.043882237965206</v>
+        <v>1.796842503534081</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7584491280579224</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.644327457808602</v>
+        <v>3.410180282940281</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>2.992188628599174</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.017329303515493</v>
+        <v>-3.049560702422505</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.01904765774755</v>
+        <v>1.772007923316425</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7250814540034463</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.661384675869563</v>
+        <v>3.427237501001242</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>2.988863984588719</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.010274613300319</v>
+        <v>-3.042506012207331</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.018544889823165</v>
+        <v>1.77150515539204</v>
       </c>
       <c r="F2001" t="n">
         <v>0.7321361442186201</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.662292845988212</v>
+        <v>3.428145671119891</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>2.998870138233461</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.983323388973831</v>
+        <v>-3.015554787880843</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.039331533198502</v>
+        <v>1.792291798767376</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7470164902463392</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.681227207249585</v>
+        <v>3.447080032381264</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.182973270378421</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.119276397030148</v>
+        <v>-3.151507795937159</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.169053462120935</v>
+        <v>1.922013727689809</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7470164902463392</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.865330339394545</v>
+        <v>3.631183164526224</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.175089965281414</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.14168451483502</v>
+        <v>-3.173915913742031</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.152206909901979</v>
+        <v>1.905167175470854</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7470164902463392</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.857447034297538</v>
+        <v>3.623299859429217</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.177143964831051</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.289690282314419</v>
+        <v>-3.321921681221431</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.095058602459857</v>
+        <v>1.848018868028731</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6602894813827977</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.807464828529051</v>
+        <v>3.57331765366073</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.233397682552898</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.299131208202949</v>
+        <v>-3.331362607109961</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.147535949826292</v>
+        <v>1.900496215395167</v>
       </c>
       <c r="F2006" t="n">
         <v>0.7827165989261892</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.937174816776933</v>
+        <v>3.703027641908612</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.236288777098199</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.35140481553859</v>
+        <v>-3.383636214445602</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.129517601437336</v>
+        <v>1.882477867006211</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7304429915905479</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.908701746920849</v>
+        <v>3.674554572052528</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.234400589991974</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.427734793139496</v>
+        <v>-3.459966192046508</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.097097423290749</v>
+        <v>1.850057688859624</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7304429915905479</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.906813559814624</v>
+        <v>3.672666384946303</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.229220819594837</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.62998851346385</v>
+        <v>-3.662219912370861</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.01101616476387</v>
+        <v>1.763976430332745</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5281892712661944</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.780281557222875</v>
+        <v>3.546134382354554</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.227654829804989</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.791556938991105</v>
+        <v>-3.823788337898117</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.94482280476312</v>
+        <v>1.697783070331995</v>
       </c>
       <c r="F2010" t="n">
         <v>0.4014063474683151</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.702645813154299</v>
+        <v>3.468498638285978</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.240728236670908</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.923858231088658</v>
+        <v>-3.95608962999567</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.904975694790018</v>
+        <v>1.657935960358892</v>
       </c>
       <c r="F2011" t="n">
         <v>0.4014063474683151</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.715719220020218</v>
+        <v>3.481572045151897</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.232733433453848</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.109726541927888</v>
+        <v>-4.141957940834899</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.822633567237266</v>
+        <v>1.575593832806141</v>
       </c>
       <c r="F2012" t="n">
         <v>0.2428407541483674</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.612585060811189</v>
+        <v>3.378437885942868</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.23125747458085</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.13762732903736</v>
+        <v>-4.169858727944372</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.809997293520479</v>
+        <v>1.562957559089353</v>
       </c>
       <c r="F2013" t="n">
         <v>0.2082438300054326</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.59035094745243</v>
+        <v>3.356203772584109</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.228021918558048</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.260153431740254</v>
+        <v>-4.292384830647266</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.75775129641652</v>
+        <v>1.510711561985395</v>
       </c>
       <c r="F2014" t="n">
         <v>0.08571772730253868</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.513599729807892</v>
+        <v>3.279452554939572</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.294727878148552</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.490667927925843</v>
+        <v>-4.522899326832855</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.732251457532788</v>
+        <v>1.485211723101663</v>
       </c>
       <c r="F2015" t="n">
         <v>-0.14479676888305</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.441996991687043</v>
+        <v>3.207849816818722</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.435039597150399</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.747388745920667</v>
+        <v>-4.779620144827678</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.769874849336706</v>
+        <v>1.522835114905581</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.2532113430268649</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.517259966202601</v>
+        <v>3.28311279133428</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.504019866296039</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.901375163696807</v>
+        <v>-4.933606562603819</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.77726055137189</v>
+        <v>1.530220816940764</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.2532113430268649</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.586240235348241</v>
+        <v>3.35209306047992</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.49007106841616</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.850853259869141</v>
+        <v>-4.883084658776153</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.783520515023077</v>
+        <v>1.536480780591951</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.2532113430268649</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.572291437468362</v>
+        <v>3.338144262600041</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.501941557471574</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.103328413876866</v>
+        <v>-5.135559812783877</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.694400942475401</v>
+        <v>1.447361208044275</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.2532113430268649</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.584161926523776</v>
+        <v>3.350014751655455</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.503152091990517</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.396224170356278</v>
+        <v>-5.428455569263289</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.57845317440258</v>
+        <v>1.331413439971454</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.2532113430268649</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.58537246104272</v>
+        <v>3.351225286174399</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.507273834217839</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.553768242085719</v>
+        <v>-5.585999640992731</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.519557287938125</v>
+        <v>1.272517553506999</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.3201131481671394</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.549353120185876</v>
+        <v>3.315205945317556</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.502351686954028</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.831732637668993</v>
+        <v>-5.863964036576005</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.403449382441005</v>
+        <v>1.156409648009879</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.4097328824526236</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.490659132350775</v>
+        <v>3.256511957482454</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.664555743653072</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.948700330307884</v>
+        <v>-5.980931729214896</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.518866362084493</v>
+        <v>1.271826627653367</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.4097328824526236</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.652863189049819</v>
+        <v>3.418716014181499</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.659402381616887</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.033418272528837</v>
+        <v>-6.065649671435849</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.479825823159925</v>
+        <v>1.2327860887288</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.49484891138067</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.596640209656806</v>
+        <v>3.362493034788485</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.669631799185378</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.11535309079772</v>
+        <v>-6.147584489704732</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.457281313420863</v>
+        <v>1.210241578989737</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.5047836569677502</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.600908779873049</v>
+        <v>3.366761605004728</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.67855743764128</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.217329213046128</v>
+        <v>-6.249560611953139</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.425416502977403</v>
+        <v>1.178376768546277</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.6067597792161578</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.548648744979907</v>
+        <v>3.314501570111586</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.670710324885456</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.107322929568906</v>
+        <v>-6.139554328475918</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.461571903612466</v>
+        <v>1.214532169181341</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.5835552072988826</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.554724375374447</v>
+        <v>3.320577200506126</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.67496033560743</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.964263353827981</v>
+        <v>-5.996494752734993</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.523045744630811</v>
+        <v>1.276006010199685</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.5755417807089033</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.563782442050409</v>
+        <v>3.329635267182088</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.682221218489966</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.662816628356143</v>
+        <v>-5.695048027263155</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.650885317702082</v>
+        <v>1.403845583270956</v>
       </c>
       <c r="F2029" t="n">
         <v>-0.274095055237066</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.751911360216047</v>
+        <v>3.517764185347727</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.683192396242676</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.687406872591327</v>
+        <v>-5.719638271498339</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.642020397760719</v>
+        <v>1.394980663329593</v>
       </c>
       <c r="F2030" t="n">
         <v>-0.274095055237066</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.752882537968758</v>
+        <v>3.518735363100437</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.684035300622432</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.636368496584807</v>
+        <v>-5.668599895491819</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.663278652543082</v>
+        <v>1.416238918111957</v>
       </c>
       <c r="F2031" t="n">
         <v>-0.274095055237066</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.753725442348513</v>
+        <v>3.519578267480193</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.703073399496577</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.595229201718176</v>
+        <v>-5.627460600625188</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.69877246936388</v>
+        <v>1.451732734932755</v>
       </c>
       <c r="F2032" t="n">
         <v>-0.2329557603704352</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.797447118142637</v>
+        <v>3.563299943274317</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.519257395620512</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.484623061638574</v>
+        <v>-5.516854460545586</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.559198921519656</v>
+        <v>1.31215918708853</v>
       </c>
       <c r="F2033" t="n">
         <v>-0.1223496202908332</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.679994798314333</v>
+        <v>3.445847623446012</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.522759439694476</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.615203796169417</v>
+        <v>-5.647435195076429</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.510468671781282</v>
+        <v>1.263428937350157</v>
       </c>
       <c r="F2034" t="n">
         <v>-0.2529303548216757</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.605148401669791</v>
+        <v>3.371001226801471</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.507186258770559</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.450707461978455</v>
+        <v>-5.482938860885467</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.56069402453375</v>
+        <v>1.313654290102625</v>
       </c>
       <c r="F2035" t="n">
         <v>-0.2529303548216757</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.589575220745874</v>
+        <v>3.355428045877554</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.506373969206988</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.478077394662887</v>
+        <v>-5.510308793569899</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.548933761896406</v>
+        <v>1.301894027465281</v>
       </c>
       <c r="F2036" t="n">
         <v>-0.2529303548216757</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.588762931182303</v>
+        <v>3.354615756313983</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.516242748332061</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.488462589552777</v>
+        <v>-5.520693988459788</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.554648463065523</v>
+        <v>1.307608728634398</v>
       </c>
       <c r="F2037" t="n">
         <v>-0.263315549711565</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.592400593373442</v>
+        <v>3.358253418505122</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.587079754108486</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.507050748275002</v>
+        <v>-5.539282147182013</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.618050205353058</v>
+        <v>1.371010470921934</v>
       </c>
       <c r="F2038" t="n">
         <v>-0.2819037084337904</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.652084703916532</v>
+        <v>3.417937529048212</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.583948764926784</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.507349294971037</v>
+        <v>-5.539580693878049</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.614799797492942</v>
+        <v>1.367760063061818</v>
       </c>
       <c r="F2039" t="n">
         <v>-0.2819037084337904</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.648953714734831</v>
+        <v>3.414806539866511</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.588479659866176</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.40652616128061</v>
+        <v>-5.438757560187621</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.659659945908505</v>
+        <v>1.41262021147738</v>
       </c>
       <c r="F2040" t="n">
         <v>-0.2694394929494365</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.660963138964834</v>
+        <v>3.426815964096514</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.588608913344719</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.215744800528203</v>
+        <v>-5.247976199435215</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.736101743688011</v>
+        <v>1.489062009256886</v>
       </c>
       <c r="F2041" t="n">
         <v>-0.07865813219702916</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.775561208894822</v>
+        <v>3.541414034026502</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.568445759082316</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.197227946486382</v>
+        <v>-5.229459345393394</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.723345331042335</v>
+        <v>1.476305596611211</v>
       </c>
       <c r="F2042" t="n">
         <v>-0.06572800277182095</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.763156132287544</v>
+        <v>3.529008957419224</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.603412695694374</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.172034761985064</v>
+        <v>-5.204266160892076</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.768389541454921</v>
+        <v>1.521349807023797</v>
       </c>
       <c r="F2043" t="n">
         <v>-0.04053481827050259</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.813238979600393</v>
+        <v>3.579091804732073</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.597099263595812</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.159980635072102</v>
+        <v>-5.192212033979113</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.766897760121544</v>
+        <v>1.519858025690419</v>
       </c>
       <c r="F2044" t="n">
         <v>-0.02848069135753978</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.814158023649608</v>
+        <v>3.580010848781289</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.598979893779948</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.16660388176246</v>
+        <v>-5.198835280669472</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.766129091629537</v>
+        <v>1.519089357198412</v>
       </c>
       <c r="F2045" t="n">
         <v>-0.03510393804789813</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.812064705819529</v>
+        <v>3.577917530951209</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.61183091965783</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.063723292233867</v>
+        <v>-5.095954691140879</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.820132353318856</v>
+        <v>1.573092618887732</v>
       </c>
       <c r="F2046" t="n">
         <v>0.06777665148069478</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.886644085414567</v>
+        <v>3.652496910546247</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.632033589831424</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.087165331413954</v>
+        <v>-5.119396730320966</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.830958207820415</v>
+        <v>1.583918473389291</v>
       </c>
       <c r="F2047" t="n">
         <v>0.06777665148069478</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.906846755588162</v>
+        <v>3.672699580719842</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.632033589831424</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.105237839705565</v>
+        <v>-5.137469238612577</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.823729204503771</v>
+        <v>1.576689470072646</v>
       </c>
       <c r="F2048" t="n">
         <v>0.06777665148069478</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.906846755588162</v>
+        <v>3.672699580719842</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.736022413116509</v>
+        <v>3.868079651332323</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.977602593787736</v>
+        <v>3.980347296657929</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.105237839705565</v>
+        <v>-5.137469238612577</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.823729204503771</v>
+        <v>1.576689470072646</v>
       </c>
       <c r="F2049" t="n">
         <v>0.06777665148069478</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.970666390774104</v>
+        <v>3.973411093644296</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240807.xlsx
+++ b/tame_output/ON/bt/strategyON_20240807.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,37 +834,37 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>127.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.8%</t>
+          <t>450.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.3%</t>
+          <t>-694.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-136.9%</t>
+          <t>-140.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-218.6%</t>
+          <t>-232.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.3%</t>
+          <t>-132.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.2%</t>
+          <t>-217.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-82.7%</t>
         </is>
       </c>
     </row>
@@ -45343,16 +45343,16 @@
         <v>2.921711838980584</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.203507737648524</v>
+        <v>-7.167780081789072</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.03995231960742718</v>
+        <v>0.05424338195120759</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7755814117351372</v>
+        <v>-0.7748853340647507</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.456362991939502</v>
+        <v>2.456780638541734</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>2.917079325727611</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.071232264017637</v>
+        <v>-7.035504608158186</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.08822999580680868</v>
+        <v>0.1025210581505891</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6433059381042505</v>
+        <v>-0.642609860433864</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.531095762865061</v>
+        <v>2.531513409467293</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>2.919894386415248</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.915493931457895</v>
+        <v>-6.879766275598444</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1533403895183421</v>
+        <v>0.1676314518621229</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.487567605544509</v>
+        <v>-0.4868715278741225</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.627353823088542</v>
+        <v>2.627771469690774</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>2.932800727638906</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.666494132774314</v>
+        <v>-6.630766476914863</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2658466502154333</v>
+        <v>0.2801377125592137</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2385678068609283</v>
+        <v>-0.2378717291905418</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.78966004352235</v>
+        <v>2.790077690124582</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.804824798039688</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.772084122547419</v>
+        <v>-6.736356466687967</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09563472470697265</v>
+        <v>0.1099257870507535</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3441577966340326</v>
+        <v>-0.3434617189636461</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.598330120059269</v>
+        <v>2.5987477666615</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.853369139916774</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.790819024666016</v>
+        <v>-6.755091368806564</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1366851057366203</v>
+        <v>0.1509761680804012</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3497538062941639</v>
+        <v>-0.3490577286237774</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.643516856140276</v>
+        <v>2.643934502742508</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.733490217228606</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.642878983258417</v>
+        <v>-6.607151327398965</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07598219961149244</v>
+        <v>0.0902732619552733</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3294328903856064</v>
+        <v>-0.3287368127152199</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.535830482997243</v>
+        <v>2.536248129599475</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.724776230975128</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.589909461004428</v>
+        <v>-6.554181805144976</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.08845602225960958</v>
+        <v>0.1027470846033904</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.275767290461231</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.558898210096158</v>
+        <v>2.55931585669839</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.717815618880035</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.546361054233738</v>
+        <v>-6.510633398374286</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0989147728727926</v>
+        <v>0.1132058352165735</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.275767290461231</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.551937598001065</v>
+        <v>2.552355244603297</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.732277973261178</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.512997847754969</v>
+        <v>-6.477270191895517</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1267224098454434</v>
+        <v>0.1410134721892238</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.275767290461231</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.566399952382208</v>
+        <v>2.56681759898444</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.726810093720373</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.404738710632447</v>
+        <v>-6.369011054772995</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1645581851536471</v>
+        <v>0.1788492474974275</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.275767290461231</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.560932072841403</v>
+        <v>2.561349719443635</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.72430818773095</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.281447575815316</v>
+        <v>-6.245719919955865</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2113727330910762</v>
+        <v>0.225663795434857</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.153172233314487</v>
+        <v>-0.1524761556441005</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.632404847742258</v>
+        <v>2.63282249434449</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.732009165968275</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.260298376911873</v>
+        <v>-6.224570721052421</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2275333908897785</v>
+        <v>0.2418244532335594</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1320230344110436</v>
+        <v>-0.1313269567406571</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.652795345321649</v>
+        <v>2.653212991923881</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.727789874315326</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.016532934928429</v>
+        <v>-5.980805279068977</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.320820276030207</v>
+        <v>0.3351113383739879</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1320230344110436</v>
+        <v>-0.1313269567406571</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.6485760536687</v>
+        <v>2.648993700270932</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.729914188235342</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.914770114651134</v>
+        <v>-5.879042458791682</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3636497180611413</v>
+        <v>0.3779407804049217</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1188039660186149</v>
+        <v>-0.1181078883482284</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.658631808624173</v>
+        <v>2.659049455226405</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.722656263219044</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.664919720702059</v>
+        <v>-5.629192064842607</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.456331950624473</v>
+        <v>0.4706230129682538</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1188039660186149</v>
+        <v>-0.1181078883482284</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.651373883607875</v>
+        <v>2.651791530210107</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.726255386739693</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.489027628234627</v>
+        <v>-5.453299972375175</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5302879111320946</v>
+        <v>0.5445789734758755</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1188039660186149</v>
+        <v>-0.1181078883482284</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.654973007128524</v>
+        <v>2.655390653730756</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.739582892794246</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.317581165212164</v>
+        <v>-5.281853509352712</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6121940023956336</v>
+        <v>0.6264850647394145</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.05264249700384821</v>
+        <v>0.0533385746742347</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.771168390996556</v>
+        <v>2.771586037598788</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.738603370410543</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.243291599473825</v>
+        <v>-5.207563943614373</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6409303063072662</v>
+        <v>0.6552213686510471</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1269320627421875</v>
+        <v>0.127628140412574</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.814762608055856</v>
+        <v>2.815180254658088</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.743298171464861</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.17965585723989</v>
+        <v>-5.143928201380438</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6710794042551576</v>
+        <v>0.685370466598938</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.190567804976122</v>
+        <v>0.1912638826465085</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.857638854450534</v>
+        <v>2.858056501052766</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.724492430248656</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.06822909791397</v>
+        <v>-5.032501442054518</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6968443667693212</v>
+        <v>0.711135429113102</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.190567804976122</v>
+        <v>0.1912638826465085</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.83883311323433</v>
+        <v>2.839250759836562</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.726235506873534</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.078731720979259</v>
+        <v>-5.043004065119807</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6943863941680828</v>
+        <v>0.7086774565118636</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1800651819108331</v>
+        <v>0.1807612595812196</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.834274616020034</v>
+        <v>2.834692262622266</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.730164820708354</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.006489152808064</v>
+        <v>-4.970761496948612</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7272127352713811</v>
+        <v>0.7415037976151617</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1800651819108331</v>
+        <v>0.1807612595812196</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.838203929854854</v>
+        <v>2.838621576457086</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.730843404625694</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.988775465930199</v>
+        <v>-4.953047810070747</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7349767939398673</v>
+        <v>0.7492678562836479</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.18324651080775</v>
+        <v>0.1839425884781364</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.840791311110344</v>
+        <v>2.841208957712576</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.727841475845687</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.879970580450472</v>
+        <v>-4.84424292459102</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7754968193517515</v>
+        <v>0.7897878816955322</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.18324651080775</v>
+        <v>0.1839425884781364</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.837789382330338</v>
+        <v>2.83820702893257</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.729420512856302</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.659949782413461</v>
+        <v>-4.62422212655401</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8650841755771699</v>
+        <v>0.8793752379209505</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3244663558757302</v>
+        <v>0.3251624335461167</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.92410032638174</v>
+        <v>2.924517972983972</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.745314695658125</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.527082093350184</v>
+        <v>-4.491354437490732</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9341254340043041</v>
+        <v>0.9484164963480848</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3244663558757302</v>
+        <v>0.3251624335461167</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.939994509183563</v>
+        <v>2.940412155785795</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.746460540098427</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.406909009985685</v>
+        <v>-4.371181354126233</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9833405117904055</v>
+        <v>0.9976315741341861</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4446394392402291</v>
+        <v>0.4453355169106156</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.013244203642564</v>
+        <v>3.013661850244796</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.756548642659867</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.262236864885947</v>
+        <v>-4.226509209026496</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.05129747239174</v>
+        <v>1.065588534735521</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5893115843399666</v>
+        <v>0.590007662010353</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.110135593263847</v>
+        <v>3.110553239866079</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.742586134061292</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.32211169224364</v>
+        <v>-4.286384036384188</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.013385032850089</v>
+        <v>1.02767609519387</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5294367569822744</v>
+        <v>0.5301328346526609</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.060248188250657</v>
+        <v>3.060665834852889</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.757875303295501</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.202291461332803</v>
+        <v>-4.166563805473351</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.076602294448633</v>
+        <v>1.090893356792413</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5294367569822744</v>
+        <v>0.5301328346526609</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.075537357484866</v>
+        <v>3.075955004087098</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.665519502617943</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.204761167794609</v>
+        <v>-4.169033511935157</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9832586111863517</v>
+        <v>0.9975496735301324</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5269670505204682</v>
+        <v>0.5276631281908548</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.981699732930224</v>
+        <v>2.982117379532456</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.584781364103244</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.273131354118619</v>
+        <v>-4.237403698259167</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8751723981420492</v>
+        <v>0.8894634604858298</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5369388272270698</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.906527013837254</v>
+        <v>2.906944660439486</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.575218072735135</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.286919406965666</v>
+        <v>-4.251191751106214</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8600938856351217</v>
+        <v>0.8743849479789023</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5369388272270698</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.896963722469145</v>
+        <v>2.897381369071377</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.712248909427338</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.342439482858255</v>
+        <v>-4.306711826998804</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9749166919702883</v>
+        <v>0.9892077543140689</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5369388272270698</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.033994559161348</v>
+        <v>3.03441220576358</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.716816141419125</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.166965223065786</v>
+        <v>-4.131237567206334</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.049673627879064</v>
+        <v>1.063964690222845</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5369388272270698</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.038561791153136</v>
+        <v>3.038979437755367</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.692558170180332</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.277901475707035</v>
+        <v>-4.242173819847583</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9810411555837715</v>
+        <v>0.9953322179275521</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5369388272270698</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.014303819914343</v>
+        <v>3.014721466516574</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.621096483581782</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.244237930234752</v>
+        <v>-4.208510274375301</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9230448871741341</v>
+        <v>0.9373359495179148</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5699062950289651</v>
+        <v>0.5706023726993517</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.963040260599162</v>
+        <v>2.963457907201394</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.631268870013915</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.184385311031029</v>
+        <v>-4.148657655171577</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9571583212877557</v>
+        <v>0.9714493836315363</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5699062950289651</v>
+        <v>0.5706023726993517</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.973212647031294</v>
+        <v>2.973630293633526</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.626215140587775</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.098141848004651</v>
+        <v>-4.0624141921452</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.986601977072167</v>
+        <v>1.000893039415948</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5699062950289651</v>
+        <v>0.5706023726993517</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.968158917605154</v>
+        <v>2.968576564207386</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.6179909160323</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.143448667403631</v>
+        <v>-4.10772101154418</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9602550247571007</v>
+        <v>0.9745460871008813</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5290961320197343</v>
+        <v>0.5297922096901209</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.935448595244141</v>
+        <v>2.935866241846373</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.618542789065402</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.172481772105932</v>
+        <v>-4.136754116246481</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9491936559092817</v>
+        <v>0.9634847182530626</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5290961320197343</v>
+        <v>0.5297922096901209</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.936000468277243</v>
+        <v>2.936418114879475</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.547815480956768</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.079671290655073</v>
+        <v>-4.043943634795621</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9155905403809914</v>
+        <v>0.929881602724772</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6219066134705936</v>
+        <v>0.6226026911409802</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.920959449039124</v>
+        <v>2.921377095641356</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.549688956881369</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.1240607599845</v>
+        <v>-4.088333104125049</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8997082285738212</v>
+        <v>0.9139992909176018</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.577517144141166</v>
+        <v>0.5782132218115525</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.896199243366068</v>
+        <v>2.8966168899683</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.544764665393092</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.240602365089843</v>
+        <v>-4.204874709230391</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8481672950434072</v>
+        <v>0.8624583573871878</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4609755390358232</v>
+        <v>0.4616716167062098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.821349988814586</v>
+        <v>2.821767635416818</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.550255961223759</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.12822536390717</v>
+        <v>-4.092497708047718</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8986093913471436</v>
+        <v>0.9129004536909242</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4609755390358232</v>
+        <v>0.4616716167062098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.826841284645253</v>
+        <v>2.827258931247485</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.561753162992298</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.156005761808522</v>
+        <v>-4.120278105949071</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8989944339551417</v>
+        <v>0.9132854962989223</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4331951411344701</v>
+        <v>0.4338912188048567</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.82167024767298</v>
+        <v>2.822087894275212</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.400108882992951</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.274386434538661</v>
+        <v>-4.238658778679209</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6899978848637396</v>
+        <v>0.7042889472075202</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3659772889834939</v>
+        <v>0.3666733666538805</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.619695256383048</v>
+        <v>2.62011290298528</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.520258543712157</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.383000512981992</v>
+        <v>-4.34727285712254</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7667019142056126</v>
+        <v>0.7809929765493933</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3659772889834939</v>
+        <v>0.3666733666538805</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.739844917102253</v>
+        <v>2.740262563704485</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.53477156981448</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.347591474733849</v>
+        <v>-4.311863818874397</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7953785556071928</v>
+        <v>0.8096696179509735</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3659772889834939</v>
+        <v>0.3666733666538805</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.754357943204576</v>
+        <v>2.754775589806808</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.532191011156848</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309207812175698</v>
+        <v>-4.273480156316246</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8081514619728218</v>
+        <v>0.8224425243166027</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4043609515416451</v>
+        <v>0.4050570292120317</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.774807582081836</v>
+        <v>2.775225228684068</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.52892004000215</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132091482140532</v>
+        <v>-4.09636382628108</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8757270228321903</v>
+        <v>0.8900180851759709</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4043609515416451</v>
+        <v>0.4050570292120317</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.771536610927138</v>
+        <v>2.771954257529369</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.529603431764063</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177183726974078</v>
+        <v>-4.141456071114626</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8583735166606852</v>
+        <v>0.8726645790044658</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3424649083722553</v>
+        <v>0.3431609860426419</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.735082376787417</v>
+        <v>2.735500023389649</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.523390407070478</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.99780830573531</v>
+        <v>-3.962080649875858</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9239106604626066</v>
+        <v>0.9382017228063873</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.499241666542974</v>
+        <v>0.4999377442133606</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.822935406996263</v>
+        <v>2.823353053598495</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.504197862402068</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042822519255916</v>
+        <v>-4.007094863396464</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8867124303859539</v>
+        <v>0.9010034927297346</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4688927712283694</v>
+        <v>0.469588848898756</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.78553352513909</v>
+        <v>2.785951171741321</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.509889424741013</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309827029528351</v>
+        <v>-4.2740993736689</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7856021886159257</v>
+        <v>0.7998932509597061</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2745297331854208</v>
+        <v>0.2752258108558074</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.674607264652266</v>
+        <v>2.675024911254498</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.509093346637515</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.411024810965523</v>
+        <v>-4.375297155106073</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.744326997937558</v>
+        <v>0.7586180602813384</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2061209196401016</v>
+        <v>0.2068169973104882</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.632765898421576</v>
+        <v>2.633183545023808</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.506693308191831</v>
+        <v>2.445175604934414</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.404513844351211</v>
+        <v>-4.36878618849176</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7445313461375997</v>
+        <v>0.6973047052239627</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2061209196401016</v>
+        <v>0.2068169973104882</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.630365859975893</v>
+        <v>2.569265803320707</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.503218027400076</v>
+        <v>2.441700324142659</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385475716643914</v>
+        <v>-4.349748060784463</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7486713164287637</v>
+        <v>0.7014446755151265</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1479373083089071</v>
+        <v>0.1486333859792937</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.591980412385421</v>
+        <v>2.530880355730235</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.622512429034267</v>
+        <v>2.560994725776849</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.416602347794532</v>
+        <v>-4.380874691935081</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8555150656027066</v>
+        <v>0.8082884246890696</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1479373083089071</v>
+        <v>0.1486333859792937</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.711274814019611</v>
+        <v>2.650174757364426</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.6233457580204</v>
+        <v>2.561828054762983</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43046910912845</v>
+        <v>-4.394741453268999</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8508016900552731</v>
+        <v>0.803575049141636</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1100793915750841</v>
+        <v>0.1107754692454707</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.689393392965451</v>
+        <v>2.628293336310266</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.629354288417326</v>
+        <v>2.567836585159909</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.38566493758852</v>
+        <v>-4.349937281729069</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.874731889068171</v>
+        <v>0.8275052481545337</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1100793915750841</v>
+        <v>0.1107754692454707</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.695401923362377</v>
+        <v>2.634301866707192</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.527304509694526</v>
+        <v>2.465786806437108</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237921967353517</v>
+        <v>-4.202194311494067</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8317792984393715</v>
+        <v>0.7845526575257344</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2778867488099673</v>
+        <v>0.2785828264803539</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.694036558980506</v>
+        <v>2.632936502325321</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.530098131226007</v>
+        <v>2.468580427968589</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321743188628216</v>
+        <v>-4.286015532768765</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.801044431460973</v>
+        <v>0.753817790547336</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2778867488099673</v>
+        <v>0.2785828264803539</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.696830180511987</v>
+        <v>2.635730123856802</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.530760479617665</v>
+        <v>2.469242776360248</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315590482575431</v>
+        <v>-4.279862826715981</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8041678622737451</v>
+        <v>0.7569412213601081</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2840394548627516</v>
+        <v>0.2847355325331382</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.701184152535316</v>
+        <v>2.640084095880131</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.529840956357775</v>
+        <v>2.468323253100358</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.332399780725933</v>
+        <v>-4.296672124866483</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7965246197536546</v>
+        <v>0.7492979788400176</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2672301567122499</v>
+        <v>0.2679262343826365</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.690179050385126</v>
+        <v>2.62907899372994</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.596176510154596</v>
+        <v>2.534658806897179</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.270101781949811</v>
+        <v>-4.23437412609036</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8877793730609245</v>
+        <v>0.8405527321472874</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2672301567122499</v>
+        <v>0.2679262343826365</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.756514604181946</v>
+        <v>2.695414547526761</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.398468511868723</v>
+        <v>2.336950808611306</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.068311584284653</v>
+        <v>-4.032583928425202</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7707874538411148</v>
+        <v>0.7235608129274775</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4652483488814043</v>
+        <v>0.4659444265517909</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.677617521197566</v>
+        <v>2.616517464542381</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.468758744190898</v>
+        <v>2.407241040933481</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.119198296970848</v>
+        <v>-4.083470641111397</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.820723001088812</v>
+        <v>0.773496360175175</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4143616361952098</v>
+        <v>0.4150577138655964</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.717375725908024</v>
+        <v>2.656275669252839</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.483386480306942</v>
+        <v>2.421868777049525</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.216938841595822</v>
+        <v>-4.181211185736371</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.796254519354866</v>
+        <v>0.7490278784412288</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3984723580622296</v>
+        <v>0.3991684357326162</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.72246989514428</v>
+        <v>2.661369838489095</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.481922461131614</v>
+        <v>2.420404757874196</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.277148139601107</v>
+        <v>-4.241420483741656</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7707067809774237</v>
+        <v>0.7234801400637865</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3382630600569451</v>
+        <v>0.3389591377273317</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.684880297165781</v>
+        <v>2.623780240510595</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.480414079171542</v>
+        <v>2.418896375914125</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.20072609316918</v>
+        <v>-4.16499843730973</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7997672175901229</v>
+        <v>0.7525405766764859</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3382630600569451</v>
+        <v>0.3389591377273317</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.68337191520571</v>
+        <v>2.622271858550524</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.480276946606979</v>
+        <v>2.418759243349561</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.156352961530612</v>
+        <v>-4.120625305671161</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8173793376809866</v>
+        <v>0.7701526967673495</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3826361916955137</v>
+        <v>0.3833322693659003</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.709858661624287</v>
+        <v>2.648758604969101</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.474670740745569</v>
+        <v>2.413153037488152</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.178833312389497</v>
+        <v>-4.143105656530046</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8027809914760231</v>
+        <v>0.7555543505623861</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3826361916955137</v>
+        <v>0.3833322693659003</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.704252455762878</v>
+        <v>2.643152399107692</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.481052497773374</v>
+        <v>2.419534794515956</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.131177581828441</v>
+        <v>-4.09544992596899</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8282250407282501</v>
+        <v>0.7809983998146126</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4302919222565693</v>
+        <v>0.4309879999269559</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.739227651127316</v>
+        <v>2.67812759447213</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.485944871148098</v>
+        <v>2.424427167890681</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.030659423329686</v>
+        <v>-3.994931767470235</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8733246775024768</v>
+        <v>0.8260980365888393</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5308100807553239</v>
+        <v>0.5315061584257105</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.804430919601293</v>
+        <v>2.743330862946107</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.472699543623971</v>
+        <v>2.411181840366553</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.091326013732075</v>
+        <v>-4.055598357872624</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8358127138173932</v>
+        <v>0.7885860729037559</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4491117640367902</v>
+        <v>0.4498078417071768</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.742166602046045</v>
+        <v>2.681066545390859</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.476797246234599</v>
+        <v>2.415279542977181</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.046487612123677</v>
+        <v>-4.010759956264225</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8578457770713812</v>
+        <v>0.8106191361577439</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4536551969816597</v>
+        <v>0.4543512746520463</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.748990364423595</v>
+        <v>2.687890307768409</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.480958185865677</v>
+        <v>2.419440482608259</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.065986068365685</v>
+        <v>-4.030258412506234</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.854207334205656</v>
+        <v>0.8069806932920187</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4055705557017554</v>
+        <v>0.406266633372142</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.724300519286731</v>
+        <v>2.663200462631545</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.486837788393514</v>
+        <v>2.425320085136097</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.021783231279785</v>
+        <v>-3.986055575420333</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8777680715678533</v>
+        <v>0.830541430654216</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4497733927876558</v>
+        <v>0.4504694704580424</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.756701824066108</v>
+        <v>2.695601767410922</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.485247788862762</v>
+        <v>2.423730085605344</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.058762258943228</v>
+        <v>-4.023034603083776</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8613864609717237</v>
+        <v>0.8141598200580864</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.487443372249373</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.777296165610154</v>
+        <v>2.716196108954968</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.536495554045802</v>
+        <v>2.474977850788384</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.900470841403955</v>
+        <v>-3.864743185544504</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9759507931704723</v>
+        <v>0.928724152256835</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.487443372249373</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.828543930793194</v>
+        <v>2.767443874138008</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.534936258640055</v>
+        <v>2.473418555382637</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.692828837769479</v>
+        <v>-3.657101181910027</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.057448299218516</v>
+        <v>1.010221658304879</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6943892982134625</v>
+        <v>0.6950853758838491</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.951569837568133</v>
+        <v>2.890469780912947</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.529884486878325</v>
+        <v>2.468366783620907</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.641796745046951</v>
+        <v>-3.606069089187499</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.072809364545797</v>
+        <v>1.02558272363216</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7454213909359905</v>
+        <v>0.7461174686063771</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.977137321439919</v>
+        <v>2.916037264784733</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.54707189097103</v>
+        <v>2.485554187713612</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.576572563919745</v>
+        <v>-3.540844908060294</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.116086441089384</v>
+        <v>1.068859800175747</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8106455720631961</v>
+        <v>0.8113416497335827</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.033459234208947</v>
+        <v>2.972359177553762</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.54303286327031</v>
+        <v>2.481515160012892</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.539145543848611</v>
+        <v>-3.50341788798916</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.127018221417118</v>
+        <v>1.079791580503481</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8158971100923778</v>
+        <v>0.8165931877627643</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.032571129325737</v>
+        <v>2.971471072670551</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.54428965560155</v>
+        <v>2.482771952344133</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.55925719988332</v>
+        <v>-3.523529544023868</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.120230351334475</v>
+        <v>1.073003710420838</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.826924455089797</v>
+        <v>0.8276205327601835</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.040444328655429</v>
+        <v>2.979344272000243</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.704847426622761</v>
+        <v>2.643329723365343</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.505512385456115</v>
+        <v>-3.469784729596663</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.302286048126568</v>
+        <v>1.255059407212931</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8369877645302589</v>
+        <v>0.8376838422006455</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.207040085340917</v>
+        <v>3.145940028685731</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.824960335840578</v>
+        <v>2.76344263258316</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.430730124431102</v>
+        <v>-3.395002468571651</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.45231186175439</v>
+        <v>1.405085220840753</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9117700255552715</v>
+        <v>0.9124661032256581</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.372022351173741</v>
+        <v>3.310922294518555</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.816668311854437</v>
+        <v>2.755150608597019</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.404646040167294</v>
+        <v>-3.368918384307843</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.454453471473772</v>
+        <v>1.407226830560135</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9117700255552715</v>
+        <v>0.9124661032256581</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.3637303271876</v>
+        <v>3.302630270532414</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.814861507438217</v>
+        <v>2.753343804180799</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.326514859318348</v>
+        <v>-3.290787203458896</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.483899139397131</v>
+        <v>1.436672498483493</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9859468364389561</v>
+        <v>0.9866429141093427</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.406429609301591</v>
+        <v>3.345329552646405</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.832415913165008</v>
+        <v>2.77089820990759</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.317622397925065</v>
+        <v>-3.281894742065613</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.505010529681235</v>
+        <v>1.457783888767598</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9859468364389561</v>
+        <v>0.9866429141093427</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.423984015028382</v>
+        <v>3.362883958373196</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.824270960569592</v>
+        <v>2.762753257312174</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.486098514894942</v>
+        <v>-3.450370859035491</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.429475130297868</v>
+        <v>1.382248489384231</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9579990007223753</v>
+        <v>0.9586950783927619</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.399070361003018</v>
+        <v>3.337970304347832</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.805540657757454</v>
+        <v>2.744022954500036</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.788298986033359</v>
+        <v>-2.752571330173907</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.689864639030363</v>
+        <v>1.642637998116726</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.8883470190223512</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.338131222568633</v>
+        <v>3.277031165913447</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.796204680254359</v>
+        <v>2.734686976996941</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.765577882350207</v>
+        <v>-2.729850226490755</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.689617103000529</v>
+        <v>1.642390462086891</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.8883470190223512</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.328795245065538</v>
+        <v>3.267695188410352</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.955110806105528</v>
+        <v>2.89359310284811</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.894779695644249</v>
+        <v>-2.859052039784797</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.796842503534081</v>
+        <v>1.749615862620443</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7584491280579224</v>
+        <v>0.759145205728309</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.410180282940281</v>
+        <v>3.349080226285095</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.992188628599174</v>
+        <v>2.930670925341756</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.049560702422505</v>
+        <v>-3.013833046563053</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.772007923316425</v>
+        <v>1.724781282402788</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7250814540034463</v>
+        <v>0.7257775316738329</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.427237501001242</v>
+        <v>3.366137444346056</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.988863984588719</v>
+        <v>2.927346281331301</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.042506012207331</v>
+        <v>-3.006778356347879</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.77150515539204</v>
+        <v>1.724278514478402</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7321361442186201</v>
+        <v>0.7328322218890067</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.428145671119891</v>
+        <v>3.367045614464706</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.998870138233461</v>
+        <v>2.937352434976043</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.015554787880843</v>
+        <v>-2.979827132021391</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.792291798767376</v>
+        <v>1.745065157853739</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7477125679167258</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.447080032381264</v>
+        <v>3.385979975726078</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.182973270378421</v>
+        <v>3.121455567121003</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.151507795937159</v>
+        <v>-3.115780140077708</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.922013727689809</v>
+        <v>1.874787086776172</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7477125679167258</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.631183164526224</v>
+        <v>3.570083107871039</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.175089965281414</v>
+        <v>3.113572262023996</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173915913742031</v>
+        <v>-3.13818825788258</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.905167175470854</v>
+        <v>1.857940534557217</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7477125679167258</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.623299859429217</v>
+        <v>3.562199802774032</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.177143964831051</v>
+        <v>3.115626261573633</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.321921681221431</v>
+        <v>-3.286194025361979</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.848018868028731</v>
+        <v>1.800792227115094</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6602894813827977</v>
+        <v>0.6609855590531843</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.57331765366073</v>
+        <v>3.512217597005544</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.233397682552898</v>
+        <v>3.17187997929548</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.331362607109961</v>
+        <v>-3.295634951250509</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.900496215395167</v>
+        <v>1.85326957448153</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7827165989261892</v>
+        <v>0.7834126765965758</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.703027641908612</v>
+        <v>3.641927585253426</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.236288777098199</v>
+        <v>3.174771073840781</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.383636214445602</v>
+        <v>-3.347908558586151</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.882477867006211</v>
+        <v>1.835251226092574</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.7311390692609345</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.674554572052528</v>
+        <v>3.613454515397342</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.234400589991974</v>
+        <v>3.172882886734556</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.459966192046508</v>
+        <v>-3.424238536187056</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.850057688859624</v>
+        <v>1.802831047945987</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.7311390692609345</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.672666384946303</v>
+        <v>3.611566328291117</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.229220819594837</v>
+        <v>3.167703116337419</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.662219912370861</v>
+        <v>-3.62649225651141</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.763976430332745</v>
+        <v>1.716749789419107</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5281892712661944</v>
+        <v>0.528885348936581</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.546134382354554</v>
+        <v>3.485034325699368</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.227654829804989</v>
+        <v>3.166137126547571</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.823788337898117</v>
+        <v>-3.788060682038665</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.697783070331995</v>
+        <v>1.650556429418358</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4021024251387016</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.468498638285978</v>
+        <v>3.407398581630792</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.240728236670908</v>
+        <v>3.17921053341349</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.95608962999567</v>
+        <v>-3.920361974136218</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.657935960358892</v>
+        <v>1.610709319445255</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4021024251387016</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.481572045151897</v>
+        <v>3.420471988496711</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.232733433453848</v>
+        <v>3.17121573019643</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.141957940834899</v>
+        <v>-4.106230284975448</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.575593832806141</v>
+        <v>1.528367191892503</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.2428407541483674</v>
+        <v>0.243536831818754</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.378437885942868</v>
+        <v>3.317337829287682</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.23125747458085</v>
+        <v>3.169739771323432</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.169858727944372</v>
+        <v>-4.13413107208492</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.562957559089353</v>
+        <v>1.515730918175716</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2082438300054326</v>
+        <v>0.2089399076758192</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.356203772584109</v>
+        <v>3.295103715928923</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.228021918558048</v>
+        <v>3.16650421530063</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.292384830647266</v>
+        <v>-4.256657174787814</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.510711561985395</v>
+        <v>1.463484921071758</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.08571772730253868</v>
+        <v>0.08641380497292528</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.279452554939572</v>
+        <v>3.218352498284386</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.294727878148552</v>
+        <v>3.233210174891134</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.522899326832855</v>
+        <v>-4.487171670973403</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.485211723101663</v>
+        <v>1.437985082188026</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.14479676888305</v>
+        <v>-0.1441006912126634</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.207849816818722</v>
+        <v>3.146749760163536</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.435039597150399</v>
+        <v>3.373521893892981</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.779620144827678</v>
+        <v>-4.743892488968227</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.522835114905581</v>
+        <v>1.475608473991943</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.2532113430268649</v>
+        <v>-0.2525152653564783</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.28311279133428</v>
+        <v>3.222012734679094</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.504019866296039</v>
+        <v>3.442502163038621</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.933606562603819</v>
+        <v>-4.897878906744367</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.530220816940764</v>
+        <v>1.482994176027127</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.2532113430268649</v>
+        <v>-0.2525152653564783</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.35209306047992</v>
+        <v>3.290993003824734</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.49007106841616</v>
+        <v>3.428553365158742</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.883084658776153</v>
+        <v>-4.847357002916701</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.536480780591951</v>
+        <v>1.489254139678314</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.2532113430268649</v>
+        <v>-0.2525152653564783</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.338144262600041</v>
+        <v>3.277044205944855</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.501941557471574</v>
+        <v>3.440423854214156</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.135559812783877</v>
+        <v>-5.099832156924426</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.447361208044275</v>
+        <v>1.400134567130638</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.2532113430268649</v>
+        <v>-0.2525152653564783</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.350014751655455</v>
+        <v>3.288914695000269</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.503152091990517</v>
+        <v>3.4416343887331</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.428455569263289</v>
+        <v>-5.392727913403838</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.331413439971454</v>
+        <v>1.284186799057817</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.2532113430268649</v>
+        <v>-0.2525152653564783</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.351225286174399</v>
+        <v>3.290125229519213</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.507273834217839</v>
+        <v>3.445756130960421</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.585999640992731</v>
+        <v>-5.550271985133279</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.272517553506999</v>
+        <v>1.225290912593362</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.3201131481671394</v>
+        <v>-0.3194170704967528</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.315205945317556</v>
+        <v>3.254105888662369</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.502351686954028</v>
+        <v>3.44083398369661</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.863964036576005</v>
+        <v>-5.828236380716553</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.156409648009879</v>
+        <v>1.109183007096242</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.4097328824526236</v>
+        <v>-0.409036804782237</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.256511957482454</v>
+        <v>3.195411900827268</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.664555743653072</v>
+        <v>3.603038040395655</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.980931729214896</v>
+        <v>-5.945204073355444</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.271826627653367</v>
+        <v>1.22459998673973</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.4097328824526236</v>
+        <v>-0.409036804782237</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.418716014181499</v>
+        <v>3.357615957526312</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.659402381616887</v>
+        <v>3.597884678359469</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.065649671435849</v>
+        <v>-6.029922015576397</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.2327860887288</v>
+        <v>1.185559447815162</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.49484891138067</v>
+        <v>-0.4941528337102834</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.362493034788485</v>
+        <v>3.301392978133299</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.669631799185378</v>
+        <v>3.60811409592796</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.147584489704732</v>
+        <v>-6.11185683384528</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.210241578989737</v>
+        <v>1.1630149380761</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.5047836569677502</v>
+        <v>-0.5040875792973636</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.366761605004728</v>
+        <v>3.305661548349542</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.67855743764128</v>
+        <v>3.617039734383862</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.249560611953139</v>
+        <v>-6.213832956093688</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.178376768546277</v>
+        <v>1.13115012763264</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.6067597792161578</v>
+        <v>-0.6060637015457712</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.314501570111586</v>
+        <v>3.2534015134564</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.670710324885456</v>
+        <v>3.609192621628038</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.139554328475918</v>
+        <v>-6.103826672616466</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.214532169181341</v>
+        <v>1.167305528267704</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.5835552072988826</v>
+        <v>-0.582859129628496</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.320577200506126</v>
+        <v>3.25947714385094</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.67496033560743</v>
+        <v>3.613442632350012</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.996494752734993</v>
+        <v>-5.960767096875541</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.276006010199685</v>
+        <v>1.228779369286048</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.5755417807089033</v>
+        <v>-0.5748457030385167</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.329635267182088</v>
+        <v>3.268535210526902</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.682221218489966</v>
+        <v>3.620703515232548</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.695048027263155</v>
+        <v>-5.659320371403703</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.403845583270956</v>
+        <v>1.356618942357319</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.274095055237066</v>
+        <v>-0.2733989775666794</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.517764185347727</v>
+        <v>3.456664128692541</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.683192396242676</v>
+        <v>3.621674692985259</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.719638271498339</v>
+        <v>-5.683910615638887</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.394980663329593</v>
+        <v>1.347754022415956</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.274095055237066</v>
+        <v>-0.2733989775666794</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.518735363100437</v>
+        <v>3.457635306445251</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.684035300622432</v>
+        <v>3.622517597365014</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.668599895491819</v>
+        <v>-5.632872239632367</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.416238918111957</v>
+        <v>1.36901227719832</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.274095055237066</v>
+        <v>-0.2733989775666794</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.519578267480193</v>
+        <v>3.458478210825007</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.703073399496577</v>
+        <v>3.64155569623916</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.627460600625188</v>
+        <v>-5.591732944765736</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.451732734932755</v>
+        <v>1.404506094019118</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.2329557603704352</v>
+        <v>-0.2322596827000486</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.563299943274317</v>
+        <v>3.502199886619131</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.519257395620512</v>
+        <v>3.457739692363094</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.516854460545586</v>
+        <v>-5.481126804686134</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.31215918708853</v>
+        <v>1.264932546174893</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.1223496202908332</v>
+        <v>-0.1216535426204466</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.445847623446012</v>
+        <v>3.384747566790826</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.522759439694476</v>
+        <v>3.461241736437058</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.647435195076429</v>
+        <v>-5.611707539216977</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.263428937350157</v>
+        <v>1.21620229643652</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.2529303548216757</v>
+        <v>-0.2522342771512891</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.371001226801471</v>
+        <v>3.309901170146285</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.507186258770559</v>
+        <v>3.445668555513141</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.482938860885467</v>
+        <v>-5.447211205026015</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.313654290102625</v>
+        <v>1.266427649188988</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.2529303548216757</v>
+        <v>-0.2522342771512891</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.355428045877554</v>
+        <v>3.294327989222368</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.506373969206988</v>
+        <v>3.444856265949571</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.510308793569899</v>
+        <v>-5.474581137710447</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.301894027465281</v>
+        <v>1.254667386551644</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.2529303548216757</v>
+        <v>-0.2522342771512891</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.354615756313983</v>
+        <v>3.293515699658797</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.516242748332061</v>
+        <v>3.454725045074643</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.520693988459788</v>
+        <v>-5.484966332600337</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.307608728634398</v>
+        <v>1.260382087720761</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.263315549711565</v>
+        <v>-0.2626194720411784</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.358253418505122</v>
+        <v>3.297153361849936</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.587079754108486</v>
+        <v>3.525562050851068</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.539282147182013</v>
+        <v>-5.503554491322562</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.371010470921934</v>
+        <v>1.323783830008296</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.2819037084337904</v>
+        <v>-0.2812076307634038</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.417937529048212</v>
+        <v>3.356837472393026</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.583948764926784</v>
+        <v>3.522431061669367</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.539580693878049</v>
+        <v>-5.503853038018597</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.367760063061818</v>
+        <v>1.32053342214818</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.2819037084337904</v>
+        <v>-0.2812076307634038</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.414806539866511</v>
+        <v>3.353706483211325</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.588479659866176</v>
+        <v>3.526961956608758</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.438757560187621</v>
+        <v>-5.40302990432817</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.41262021147738</v>
+        <v>1.365393570563743</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.2694394929494365</v>
+        <v>-0.2687434152790499</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.426815964096514</v>
+        <v>3.365715907441328</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.588608913344719</v>
+        <v>3.527091210087301</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.247976199435215</v>
+        <v>-5.212248543575763</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.489062009256886</v>
+        <v>1.441835368343249</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.07865813219702916</v>
+        <v>-0.07796205452664257</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.541414034026502</v>
+        <v>3.480313977371316</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.568445759082316</v>
+        <v>3.506928055824898</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.229459345393394</v>
+        <v>-5.193731689533942</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.476305596611211</v>
+        <v>1.429078955697574</v>
       </c>
       <c r="F2042" t="n">
-        <v>-0.06572800277182095</v>
+        <v>-0.06503192510143435</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.529008957419224</v>
+        <v>3.467908900764038</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.603412695694374</v>
+        <v>3.541894992436956</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.204266160892076</v>
+        <v>-5.168538505032624</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.521349807023797</v>
+        <v>1.474123166110159</v>
       </c>
       <c r="F2043" t="n">
-        <v>-0.04053481827050259</v>
+        <v>-0.039838740600116</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.579091804732073</v>
+        <v>3.517991748076887</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.597099263595812</v>
+        <v>3.535581560338394</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.192212033979113</v>
+        <v>-5.156484378119662</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.519858025690419</v>
+        <v>1.472631384776782</v>
       </c>
       <c r="F2044" t="n">
-        <v>-0.02848069135753978</v>
+        <v>-0.02778461368715318</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.580010848781289</v>
+        <v>3.518910792126102</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.598979893779948</v>
+        <v>3.53746219052253</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.198835280669472</v>
+        <v>-5.16310762481002</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.519089357198412</v>
+        <v>1.471862716284775</v>
       </c>
       <c r="F2045" t="n">
-        <v>-0.03510393804789813</v>
+        <v>-0.03440786037751153</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.577917530951209</v>
+        <v>3.516817474296023</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.61183091965783</v>
+        <v>3.550313216400412</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.095954691140879</v>
+        <v>-5.060227035281427</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.573092618887732</v>
+        <v>1.525865977974094</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.06777665148069478</v>
+        <v>0.06847272915108138</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.652496910546247</v>
+        <v>3.591396853891061</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.632033589831424</v>
+        <v>3.570515886574007</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.119396730320966</v>
+        <v>-5.083669074461514</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.583918473389291</v>
+        <v>1.536691832475654</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.06777665148069478</v>
+        <v>0.06847272915108138</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.672699580719842</v>
+        <v>3.611599524064656</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.632033589831424</v>
+        <v>3.570515886574007</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.137469238612577</v>
+        <v>-5.332152604277859</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.576689470072646</v>
+        <v>1.437298420549116</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.06777665148069478</v>
+        <v>0.06847272915108138</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.672699580719842</v>
+        <v>3.611599524064656</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.868079651332323</v>
+        <v>3.574977279467523</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.980347296657929</v>
+        <v>3.640229825803451</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.137469238612577</v>
+        <v>-5.332152604277859</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.576689470072646</v>
+        <v>1.437298420549116</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.06777665148069478</v>
+        <v>0.06847272915108138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.973411093644296</v>
+        <v>3.633293622789818</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240807.xlsx
+++ b/tame_output/ON/bt/strategyON_20240807.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,47 +834,47 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>62.9%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>32.3%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>75.8%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>106.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.5%</t>
+          <t>126.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.8%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-694.8%</t>
+          <t>-654.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-140.0%</t>
+          <t>-121.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-232.5%</t>
+          <t>-186.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>173.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.0%</t>
+          <t>-133.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.1%</t>
+          <t>-208.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-82.7%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.889331876951555</v>
+        <v>-8.678985839606478</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4157690828391223</v>
+        <v>-0.3316306679010914</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.483771824682167</v>
+        <v>-1.392726819404753</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.250056997445947</v>
+        <v>2.304684000612395</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.922984715460029</v>
+        <v>-8.712638678114951</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4247476637580756</v>
+        <v>-0.3406092488200447</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.584185192599204</v>
+        <v>-1.49314018732179</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.194291531180161</v>
+        <v>2.248918534346609</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.84951488379258</v>
+        <v>-8.639168846447502</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.379988029597675</v>
+        <v>-0.2958496146596441</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.510715360931755</v>
+        <v>-1.419670355654342</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.253745131674051</v>
+        <v>2.308372134840499</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.024639301179123</v>
+        <v>-8.814293263834045</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4354825758047758</v>
+        <v>-0.3513441608667445</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.685839778318299</v>
+        <v>-1.594794773040886</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.163225701989642</v>
+        <v>2.21785270515609</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.259091395193613</v>
+        <v>-9.048745357848535</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5364825783121674</v>
+        <v>-0.4523441633741365</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.685839778318299</v>
+        <v>-1.594794773040886</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.156006537088046</v>
+        <v>2.210633540254494</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.363466126220059</v>
+        <v>-9.153120088874982</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5849046614967222</v>
+        <v>-0.5007662465586913</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.790214509344745</v>
+        <v>-1.699169504067332</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.086709507698202</v>
+        <v>2.14133651086465</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.416252281820386</v>
+        <v>-9.205906244475308</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6049033338982968</v>
+        <v>-0.5207649189602654</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.885889995927142</v>
+        <v>-1.794844990649729</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.03042000558732</v>
+        <v>2.085047008753768</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.542289075188675</v>
+        <v>-9.331943037843597</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6526243226164978</v>
+        <v>-0.5684859076784665</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.8606383731174</v>
+        <v>-1.769593367839986</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.04826470790228</v>
+        <v>2.102891711068728</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.485217303292744</v>
+        <v>-9.274871265947667</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6258052781717245</v>
+        <v>-0.5416668632336936</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.8606383731174</v>
+        <v>-1.769593367839986</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.052255043588681</v>
+        <v>2.106882046755129</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.626889145016865</v>
+        <v>-9.416543107671787</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6839492417601143</v>
+        <v>-0.5998108268220834</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.8606383731174</v>
+        <v>-1.769593367839986</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.050779816689939</v>
+        <v>2.105406819856388</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.57729830059203</v>
+        <v>-9.366952263246953</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6490594938253085</v>
+        <v>-0.5649210788872772</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.811047528692566</v>
+        <v>-1.720002523415153</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.095587733509712</v>
+        <v>2.15021473667616</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.428379966120174</v>
+        <v>-9.218033928775096</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6025432936832487</v>
+        <v>-0.5184048787452178</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.779797937957393</v>
+        <v>-1.68875293267998</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.101286354304133</v>
+        <v>2.155913357470581</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.202534813400764</v>
+        <v>-8.992188776055684</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5026261595592758</v>
+        <v>-0.4184877446212441</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.737871262370229</v>
+        <v>-1.646826257092816</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.136021432692639</v>
+        <v>2.190648435859088</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.077956157063172</v>
+        <v>-8.867610119718092</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4516555524681802</v>
+        <v>-0.3675171375301485</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.737871262370229</v>
+        <v>-1.646826257092816</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.137160577248698</v>
+        <v>2.191787580415147</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.130851445107458</v>
+        <v>-8.920505407762379</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4701798935237873</v>
+        <v>-0.3860414785857555</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.732915916281783</v>
+        <v>-1.64187091100437</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.142767559063874</v>
+        <v>2.197394562230322</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.058718269819577</v>
+        <v>-8.848372232474498</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4355929191699985</v>
+        <v>-0.3514545042319668</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.732915916281783</v>
+        <v>-1.64187091100437</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14850126330251</v>
+        <v>2.203128266468958</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.98735187720993</v>
+        <v>-8.777005839864851</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4167836245200047</v>
+        <v>-0.332645209581973</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.661549523672135</v>
+        <v>-1.570504518394722</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.181583836474434</v>
+        <v>2.236210839640882</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.893892843224705</v>
+        <v>-8.683546805879626</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3892834922388224</v>
+        <v>-0.3051450773007907</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.661549523672135</v>
+        <v>-1.570504518394722</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.171700355161526</v>
+        <v>2.226327358327974</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.883239661671274</v>
+        <v>-8.672893624326194</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3868567801168235</v>
+        <v>-0.3027183651787917</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.661549523672135</v>
+        <v>-1.570504518394722</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.169865794662153</v>
+        <v>2.224492797828601</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.785332622994783</v>
+        <v>-8.574986585649704</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3479942796196882</v>
+        <v>-0.2638558646816564</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.593563773811579</v>
+        <v>-1.502518768534165</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.210356929605025</v>
+        <v>2.264983932771473</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.761379082018825</v>
+        <v>-8.551033044673746</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3377443570838112</v>
+        <v>-0.2536059421457795</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.569610232835621</v>
+        <v>-1.478565227558208</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.225397560336094</v>
+        <v>2.280024563502542</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.497319143696028</v>
+        <v>-8.286973106350949</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2453806979164446</v>
+        <v>-0.1612422829784128</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.305550294512825</v>
+        <v>-1.214505289235412</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.370573207168019</v>
+        <v>2.425200210334467</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.79023952019119</v>
+        <v>-7.579893482846111</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.03466411782518986</v>
+        <v>0.1188025327632216</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.305550294512825</v>
+        <v>-1.214505289235412</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.367786173507719</v>
+        <v>2.422413176674167</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.750055221825</v>
+        <v>-7.53970918447992</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05108146105950739</v>
+        <v>0.1352198759975392</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.265365996146634</v>
+        <v>-1.174320990869221</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.392240376415274</v>
+        <v>2.446867379581723</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.586655350885637</v>
+        <v>-7.376309313540558</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1158082306560093</v>
+        <v>0.1999466455940411</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.101966125207272</v>
+        <v>-1.010921119929858</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.489647120199649</v>
+        <v>2.544274123366097</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.353174128656039</v>
+        <v>-7.142828091310959</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2171251483857009</v>
+        <v>0.3012635633237326</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8684849029776731</v>
+        <v>-0.7774398977002597</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.63766028237526</v>
+        <v>2.692287285541708</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>2.921711838980584</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.167780081789072</v>
+        <v>-6.993161700303444</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.05424338195120759</v>
+        <v>0.3582379094137798</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7748853340647507</v>
+        <v>-0.6845364064577237</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.456780638541734</v>
+        <v>2.745137169974271</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>2.917079325727611</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.035504608158186</v>
+        <v>-6.860886226672558</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1025210581505891</v>
+        <v>0.4065155856131613</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.642609860433864</v>
+        <v>-0.5522609328268371</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.531513409467293</v>
+        <v>2.81986994089983</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>2.919894386415248</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.879766275598444</v>
+        <v>-6.705147894112816</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1676314518621229</v>
+        <v>0.4716259793246946</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4868715278741225</v>
+        <v>-0.3965226002670955</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.627771469690774</v>
+        <v>2.916128001123311</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>2.932800727638906</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.630766476914863</v>
+        <v>-6.456148095429235</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2801377125592137</v>
+        <v>0.5841322400217859</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2378717291905418</v>
+        <v>-0.1475228015835148</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.790077690124582</v>
+        <v>3.078434221557119</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.804824798039688</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.736356466687967</v>
+        <v>-6.561738085202339</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1099257870507535</v>
+        <v>0.4139203145133252</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3434617189636461</v>
+        <v>-0.2531127913566192</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.5987477666615</v>
+        <v>2.887104298094037</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.853369139916774</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.755091368806564</v>
+        <v>-6.580472987320936</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1509761680804012</v>
+        <v>0.4549706955429729</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3490577286237774</v>
+        <v>-0.2587088010167505</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.643934502742508</v>
+        <v>2.932291034175045</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.733490217228606</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.607151327398965</v>
+        <v>-6.432532945913337</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.0902732619552733</v>
+        <v>0.394267789417845</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3287368127152199</v>
+        <v>-0.2383878851081929</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.536248129599475</v>
+        <v>2.824604661032012</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.724776230975128</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.554181805144976</v>
+        <v>-6.379563423659349</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1027470846033904</v>
+        <v>0.4067416120659622</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.275767290461231</v>
+        <v>-0.185418362854204</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.55931585669839</v>
+        <v>2.847672388130927</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.717815618880035</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.510633398374286</v>
+        <v>-6.336015016888658</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1132058352165735</v>
+        <v>0.4172003626791452</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.275767290461231</v>
+        <v>-0.185418362854204</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.552355244603297</v>
+        <v>2.840711776035834</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.732277973261178</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.477270191895517</v>
+        <v>-6.302651810409889</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1410134721892238</v>
+        <v>0.4450079996517959</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.275767290461231</v>
+        <v>-0.185418362854204</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.56681759898444</v>
+        <v>2.855174130416977</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.726810093720373</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.369011054772995</v>
+        <v>-6.194392673287368</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1788492474974275</v>
+        <v>0.4828437749599996</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.275767290461231</v>
+        <v>-0.185418362854204</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.561349719443635</v>
+        <v>2.849706250876172</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.72430818773095</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.245719919955865</v>
+        <v>-6.071101538470237</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.225663795434857</v>
+        <v>0.5296583228974288</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1524761556441005</v>
+        <v>-0.06212722803707355</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.63282249434449</v>
+        <v>2.921179025777027</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.732009165968275</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.224570721052421</v>
+        <v>-6.049952339566794</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2418244532335594</v>
+        <v>0.5458189806961311</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1313269567406571</v>
+        <v>-0.04097802913363019</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.653212991923881</v>
+        <v>2.941569523356418</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.727789874315326</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.980805279068977</v>
+        <v>-5.806186897583349</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3351113383739879</v>
+        <v>0.6391058658365596</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1313269567406571</v>
+        <v>-0.04097802913363019</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.648993700270932</v>
+        <v>2.937350231703469</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.729914188235342</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.879042458791682</v>
+        <v>-5.704424077306054</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3779407804049217</v>
+        <v>0.6819353078674939</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1181078883482284</v>
+        <v>-0.02775896074120149</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.659049455226405</v>
+        <v>2.947405986658942</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.722656263219044</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.629192064842607</v>
+        <v>-5.45457368335698</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4706230129682538</v>
+        <v>0.7746175404308255</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1181078883482284</v>
+        <v>-0.02775896074120149</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.651791530210107</v>
+        <v>2.940148061642644</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.726255386739693</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.453299972375175</v>
+        <v>-5.278681590889548</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5445789734758755</v>
+        <v>0.8485735009384472</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1181078883482284</v>
+        <v>-0.02775896074120149</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.655390653730756</v>
+        <v>2.943747185163293</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.739582892794246</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.281853509352712</v>
+        <v>-5.107235127867084</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6264850647394145</v>
+        <v>0.9304795922019862</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.0533385746742347</v>
+        <v>0.1436875022812616</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.771586037598788</v>
+        <v>3.059942569031325</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.738603370410543</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.207563943614373</v>
+        <v>-5.032945562128745</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6552213686510471</v>
+        <v>0.9592158961136188</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.127628140412574</v>
+        <v>0.2179770680196009</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.815180254658088</v>
+        <v>3.103536786090625</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.743298171464861</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.143928201380438</v>
+        <v>-4.969309819894811</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.685370466598938</v>
+        <v>0.9893649940615101</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1912638826465085</v>
+        <v>0.2816128102535355</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.858056501052766</v>
+        <v>3.146413032485303</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.724492430248656</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.032501442054518</v>
+        <v>-4.857883060568891</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.711135429113102</v>
+        <v>1.015129956575674</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1912638826465085</v>
+        <v>0.2816128102535355</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.839250759836562</v>
+        <v>3.127607291269099</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.726235506873534</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.043004065119807</v>
+        <v>-4.868385683634179</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7086774565118636</v>
+        <v>1.012671983974436</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1807612595812196</v>
+        <v>0.2711101871882466</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.834692262622266</v>
+        <v>3.123048794054803</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.730164820708354</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.970761496948612</v>
+        <v>-4.796143115462985</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7415037976151617</v>
+        <v>1.045498325077734</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1807612595812196</v>
+        <v>0.2711101871882466</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.838621576457086</v>
+        <v>3.126978107889623</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.730843404625694</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.953047810070747</v>
+        <v>-4.778429428585119</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7492678562836479</v>
+        <v>1.05326238374622</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1839425884781364</v>
+        <v>0.2742915160851634</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.841208957712576</v>
+        <v>3.129565489145113</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.727841475845687</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.84424292459102</v>
+        <v>-4.669624543105392</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7897878816955322</v>
+        <v>1.093782409158104</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1839425884781364</v>
+        <v>0.2742915160851634</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.83820702893257</v>
+        <v>3.126563560365107</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.729420512856302</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.62422212655401</v>
+        <v>-4.449603745068382</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8793752379209505</v>
+        <v>1.183369765383522</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3251624335461167</v>
+        <v>0.4155113611531436</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.924517972983972</v>
+        <v>3.212874504416509</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.745314695658125</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.491354437490732</v>
+        <v>-4.316736056005104</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9484164963480848</v>
+        <v>1.252411023810657</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3251624335461167</v>
+        <v>0.4155113611531436</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.940412155785795</v>
+        <v>3.228768687218332</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.746460540098427</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.371181354126233</v>
+        <v>-4.196562972640606</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9976315741341861</v>
+        <v>1.301626101596758</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4453355169106156</v>
+        <v>0.5356844445176425</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.013661850244796</v>
+        <v>3.302018381677333</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.756548642659867</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.226509209026496</v>
+        <v>-4.051890827540868</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.065588534735521</v>
+        <v>1.369583062198093</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.590007662010353</v>
+        <v>0.68035658961738</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.110553239866079</v>
+        <v>3.398909771298616</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.742586134061292</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.286384036384188</v>
+        <v>-4.11176565489856</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.02767609519387</v>
+        <v>1.331670622656442</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5301328346526609</v>
+        <v>0.6204817622596879</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.060665834852889</v>
+        <v>3.349022366285426</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.757875303295501</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.166563805473351</v>
+        <v>-3.991945423987723</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.090893356792413</v>
+        <v>1.394887884254985</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5301328346526609</v>
+        <v>0.6204817622596879</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.075955004087098</v>
+        <v>3.364311535519635</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.665519502617943</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.169033511935157</v>
+        <v>-3.994415130449529</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9975496735301324</v>
+        <v>1.301544200992705</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5276631281908548</v>
+        <v>0.6180120557978817</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.982117379532456</v>
+        <v>3.270473910964993</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.584781364103244</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.237403698259167</v>
+        <v>-4.062785316773539</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8894634604858298</v>
+        <v>1.193457987948402</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5369388272270698</v>
+        <v>0.6272877548340966</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.906944660439486</v>
+        <v>3.195301191872023</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.575218072735135</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.251191751106214</v>
+        <v>-4.076573369620585</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8743849479789023</v>
+        <v>1.178379475441475</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5369388272270698</v>
+        <v>0.6272877548340966</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.897381369071377</v>
+        <v>3.185737900503914</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.712248909427338</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.306711826998804</v>
+        <v>-4.132093445513175</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9892077543140689</v>
+        <v>1.293202281776641</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5369388272270698</v>
+        <v>0.6272877548340966</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.03441220576358</v>
+        <v>3.322768737196117</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.716816141419125</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.131237567206334</v>
+        <v>-3.956619185720706</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.063964690222845</v>
+        <v>1.367959217685417</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5369388272270698</v>
+        <v>0.6272877548340966</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.038979437755367</v>
+        <v>3.327335969187904</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.692558170180332</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.242173819847583</v>
+        <v>-4.067555438361954</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9953322179275521</v>
+        <v>1.299326745390124</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5369388272270698</v>
+        <v>0.6272877548340966</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.014721466516574</v>
+        <v>3.303077997949111</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.621096483581782</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.208510274375301</v>
+        <v>-4.033891892889672</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9373359495179148</v>
+        <v>1.241330476980487</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5706023726993517</v>
+        <v>0.6609513003063785</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.963457907201394</v>
+        <v>3.25181443863393</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.631268870013915</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.148657655171577</v>
+        <v>-3.974039273685949</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9714493836315363</v>
+        <v>1.275443911094109</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5706023726993517</v>
+        <v>0.6609513003063785</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.973630293633526</v>
+        <v>3.261986825066063</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.626215140587775</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.0624141921452</v>
+        <v>-3.887795810659571</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.000893039415948</v>
+        <v>1.30488756687852</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5706023726993517</v>
+        <v>0.6609513003063785</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.968576564207386</v>
+        <v>3.256933095639923</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.6179909160323</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.10772101154418</v>
+        <v>-3.933102630058551</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9745460871008813</v>
+        <v>1.278540614563454</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5297922096901209</v>
+        <v>0.6201411372971477</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.935866241846373</v>
+        <v>3.22422277327891</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.618542789065402</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.136754116246481</v>
+        <v>-3.962135734760853</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9634847182530626</v>
+        <v>1.267479245715635</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5297922096901209</v>
+        <v>0.6201411372971477</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.936418114879475</v>
+        <v>3.224774646312012</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.547815480956768</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.043943634795621</v>
+        <v>-3.869325253309993</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.929881602724772</v>
+        <v>1.233876130187344</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6226026911409802</v>
+        <v>0.7129516187480071</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.921377095641356</v>
+        <v>3.209733627073893</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.549688956881369</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.088333104125049</v>
+        <v>-3.913714722639421</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9139992909176018</v>
+        <v>1.217993818380174</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5782132218115525</v>
+        <v>0.6685621494185794</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.8966168899683</v>
+        <v>3.184973421400837</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.544764665393092</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.204874709230391</v>
+        <v>-4.030256327744763</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8624583573871878</v>
+        <v>1.16645288484976</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4616716167062098</v>
+        <v>0.5520205443132367</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.821767635416818</v>
+        <v>3.110124166849355</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.550255961223759</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.092497708047718</v>
+        <v>-3.917879326562091</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9129004536909242</v>
+        <v>1.216894981153496</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4616716167062098</v>
+        <v>0.5520205443132367</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.827258931247485</v>
+        <v>3.115615462680022</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.561753162992298</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.120278105949071</v>
+        <v>-3.945659724463444</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9132854962989223</v>
+        <v>1.217280023761494</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4338912188048567</v>
+        <v>0.5242401464118835</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.822087894275212</v>
+        <v>3.110444425707749</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.400108882992951</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.238658778679209</v>
+        <v>-4.064040397193582</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7042889472075202</v>
+        <v>1.008283474670092</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3666733666538805</v>
+        <v>0.4570222942609073</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.62011290298528</v>
+        <v>2.908469434417817</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.520258543712157</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.34727285712254</v>
+        <v>-4.172654475636913</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7809929765493933</v>
+        <v>1.084987504011965</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3666733666538805</v>
+        <v>0.4570222942609073</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.740262563704485</v>
+        <v>3.028619095137022</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.53477156981448</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.311863818874397</v>
+        <v>-4.137245437388771</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8096696179509735</v>
+        <v>1.113664145413545</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3666733666538805</v>
+        <v>0.4570222942609073</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.754775589806808</v>
+        <v>3.043132121239345</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.532191011156848</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.273480156316246</v>
+        <v>-4.09886177483062</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8224425243166027</v>
+        <v>1.126437051779174</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4050570292120317</v>
+        <v>0.4954059568190585</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.775225228684068</v>
+        <v>3.063581760116604</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.52892004000215</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.09636382628108</v>
+        <v>-3.921745444795453</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8900180851759709</v>
+        <v>1.194012612638542</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4050570292120317</v>
+        <v>0.4954059568190585</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.771954257529369</v>
+        <v>3.060310788961906</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.529603431764063</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.141456071114626</v>
+        <v>-3.966837689628999</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8726645790044658</v>
+        <v>1.176659106467037</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3431609860426419</v>
+        <v>0.4335099136496687</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.735500023389649</v>
+        <v>3.023856554822186</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.523390407070478</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.962080649875858</v>
+        <v>-3.787462268390231</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9382017228063873</v>
+        <v>1.242196250268959</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4999377442133606</v>
+        <v>0.5902866718203874</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.823353053598495</v>
+        <v>3.111709585031031</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.504197862402068</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.007094863396464</v>
+        <v>-3.832476481910838</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9010034927297346</v>
+        <v>1.204998020192306</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.469588848898756</v>
+        <v>0.5599377765057828</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.785951171741321</v>
+        <v>3.074307703173858</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.509889424741013</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.2740993736689</v>
+        <v>-4.099480992183273</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7998932509597061</v>
+        <v>1.103887778422278</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2752258108558074</v>
+        <v>0.3655747384628342</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.675024911254498</v>
+        <v>2.963381442687035</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.509093346637515</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.375297155106073</v>
+        <v>-4.200678773620446</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7586180602813384</v>
+        <v>1.06261258774391</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2068169973104882</v>
+        <v>0.297165924917515</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.633183545023808</v>
+        <v>2.921540076456345</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.445175604934414</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.36878618849176</v>
+        <v>-4.194167807006133</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6973047052239627</v>
+        <v>1.062816935943952</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2068169973104882</v>
+        <v>0.297165924917515</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.569265803320707</v>
+        <v>2.919140038010661</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.441700324142659</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.349748060784463</v>
+        <v>-4.175129679298836</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7014446755151265</v>
+        <v>1.066956906235116</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1486333859792937</v>
+        <v>0.2389823135863205</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.530880355730235</v>
+        <v>2.88075459042019</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.560994725776849</v>
+        <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.380874691935081</v>
+        <v>-4.206256310449454</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8082884246890696</v>
+        <v>1.173800655409059</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1486333859792937</v>
+        <v>0.2389823135863205</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.650174757364426</v>
+        <v>3.00004899205438</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.561828054762983</v>
+        <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.394741453268999</v>
+        <v>-4.220123071783372</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.803575049141636</v>
+        <v>1.169087279861625</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1107754692454707</v>
+        <v>0.2011243968524976</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.628293336310266</v>
+        <v>2.97816757100022</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.567836585159909</v>
+        <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.349937281729069</v>
+        <v>-4.175318900243442</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8275052481545337</v>
+        <v>1.193017478874523</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1107754692454707</v>
+        <v>0.2011243968524976</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.634301866707192</v>
+        <v>2.984176101397146</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.465786806437108</v>
+        <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.202194311494067</v>
+        <v>-4.02757593000844</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7845526575257344</v>
+        <v>1.150064888245723</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2785828264803539</v>
+        <v>0.3689317540873807</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.632936502325321</v>
+        <v>2.982810737015275</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.468580427968589</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.286015532768765</v>
+        <v>-4.111397151283138</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.753817790547336</v>
+        <v>1.119330021267325</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2785828264803539</v>
+        <v>0.3689317540873807</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.635730123856802</v>
+        <v>2.985604358546756</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.469242776360248</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.279862826715981</v>
+        <v>-4.105244445230354</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7569412213601081</v>
+        <v>1.122453452080097</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2847355325331382</v>
+        <v>0.375084460140165</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.640084095880131</v>
+        <v>2.989958330570085</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.468323253100358</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.296672124866483</v>
+        <v>-4.122053743380856</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7492979788400176</v>
+        <v>1.114810209560007</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2679262343826365</v>
+        <v>0.3582751619896634</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.62907899372994</v>
+        <v>2.978953228419894</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.534658806897179</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.23437412609036</v>
+        <v>-4.059755744604733</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8405527321472874</v>
+        <v>1.206064962867276</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2679262343826365</v>
+        <v>0.3582751619896634</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.695414547526761</v>
+        <v>3.045288782216715</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.336950808611306</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.032583928425202</v>
+        <v>-3.857965546939575</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7235608129274775</v>
+        <v>1.089073043647466</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4659444265517909</v>
+        <v>0.5562933541588178</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.616517464542381</v>
+        <v>2.966391699232335</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.407241040933481</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.083470641111397</v>
+        <v>-3.90885225962577</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.773496360175175</v>
+        <v>1.139008590895164</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4150577138655964</v>
+        <v>0.5054066414726233</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.656275669252839</v>
+        <v>3.006149903942794</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.421868777049525</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.181211185736371</v>
+        <v>-4.006592804250745</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7490278784412288</v>
+        <v>1.114540109161218</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3991684357326162</v>
+        <v>0.489517363339643</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.661369838489095</v>
+        <v>3.011244073179049</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.420404757874196</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.241420483741656</v>
+        <v>-4.066802102256029</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7234801400637865</v>
+        <v>1.088992370783775</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3389591377273317</v>
+        <v>0.4293080653343585</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.623780240510595</v>
+        <v>2.97365447520055</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.418896375914125</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.16499843730973</v>
+        <v>-3.990380055824103</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7525405766764859</v>
+        <v>1.118052807396475</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3389591377273317</v>
+        <v>0.4293080653343585</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.622271858550524</v>
+        <v>2.972146093240478</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.418759243349561</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.120625305671161</v>
+        <v>-3.946006924185534</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7701526967673495</v>
+        <v>1.135664927487338</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3833322693659003</v>
+        <v>0.4736811969729271</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.648758604969101</v>
+        <v>2.998632839659056</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.413153037488152</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.143105656530046</v>
+        <v>-3.968487275044419</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7555543505623861</v>
+        <v>1.121066581282375</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3833322693659003</v>
+        <v>0.4736811969729271</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.643152399107692</v>
+        <v>2.993026633797646</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.419534794515956</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.09544992596899</v>
+        <v>-3.920831544483363</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7809983998146126</v>
+        <v>1.146510630534602</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4309879999269559</v>
+        <v>0.5213369275339828</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.67812759447213</v>
+        <v>3.028001829162084</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.424427167890681</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.994931767470235</v>
+        <v>-3.820313385984608</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8260980365888393</v>
+        <v>1.191610267308829</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5315061584257105</v>
+        <v>0.6218550860327373</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.743330862946107</v>
+        <v>3.093205097636062</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.411181840366553</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.055598357872624</v>
+        <v>-3.880979976386997</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7885860729037559</v>
+        <v>1.154098303623745</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4498078417071768</v>
+        <v>0.5401567693142036</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.681066545390859</v>
+        <v>3.030940780080814</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.415279542977181</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.010759956264225</v>
+        <v>-3.836141574778599</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8106191361577439</v>
+        <v>1.176131366877733</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4543512746520463</v>
+        <v>0.5447002022590731</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.687890307768409</v>
+        <v>3.037764542458364</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.419440482608259</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.030258412506234</v>
+        <v>-3.855640031020608</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8069806932920187</v>
+        <v>1.172492924012008</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.406266633372142</v>
+        <v>0.4966155609791688</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.663200462631545</v>
+        <v>3.0130746973215</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.425320085136097</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.986055575420333</v>
+        <v>-3.811437193934707</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.830541430654216</v>
+        <v>1.196053661374205</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4504694704580424</v>
+        <v>0.5408183980650693</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.695601767410922</v>
+        <v>3.045476002100877</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.423730085605344</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.023034603083776</v>
+        <v>-3.84841622159815</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8141598200580864</v>
+        <v>1.179672050778075</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.487443372249373</v>
+        <v>0.5777922998563998</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.716196108954968</v>
+        <v>3.066070343644923</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.474977850788384</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.864743185544504</v>
+        <v>-3.690124804058878</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.928724152256835</v>
+        <v>1.294236382976824</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.487443372249373</v>
+        <v>0.5777922998563998</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.767443874138008</v>
+        <v>3.117318108827963</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.473418555382637</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.657101181910027</v>
+        <v>-3.482482800424402</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.010221658304879</v>
+        <v>1.375733889024868</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6950853758838491</v>
+        <v>0.785434303490876</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.890469780912947</v>
+        <v>3.240344015602902</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.468366783620907</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.606069089187499</v>
+        <v>-3.431450707701874</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.02558272363216</v>
+        <v>1.391094954352149</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7461174686063771</v>
+        <v>0.8364663962134039</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.916037264784733</v>
+        <v>3.265911499474688</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.485554187713612</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.540844908060294</v>
+        <v>-3.366226526574668</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.068859800175747</v>
+        <v>1.434372030895736</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8113416497335827</v>
+        <v>0.9016905773406095</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.972359177553762</v>
+        <v>3.322233412243716</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.481515160012892</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.50341788798916</v>
+        <v>-3.328799506503535</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.079791580503481</v>
+        <v>1.44530381122347</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8165931877627643</v>
+        <v>0.9069421153697912</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.971471072670551</v>
+        <v>3.321345307360506</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.482771952344133</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.523529544023868</v>
+        <v>-3.348911162538243</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.073003710420838</v>
+        <v>1.438515941140827</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8276205327601835</v>
+        <v>0.9179694603672104</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.979344272000243</v>
+        <v>3.329218506690198</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.643329723365343</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.469784729596663</v>
+        <v>-3.295166348111038</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.255059407212931</v>
+        <v>1.620571637932919</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8376838422006455</v>
+        <v>0.9280327698076724</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.145940028685731</v>
+        <v>3.495814263375685</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.76344263258316</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.395002468571651</v>
+        <v>-3.220384087086026</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.405085220840753</v>
+        <v>1.770597451560742</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9124661032256581</v>
+        <v>1.002815030832685</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.310922294518555</v>
+        <v>3.66079652920851</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.755150608597019</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.368918384307843</v>
+        <v>-3.194300002822218</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.407226830560135</v>
+        <v>1.772739061280124</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9124661032256581</v>
+        <v>1.002815030832685</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.302630270532414</v>
+        <v>3.652504505222369</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.753343804180799</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.290787203458896</v>
+        <v>-3.116168821973271</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.436672498483493</v>
+        <v>1.802184729203482</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9866429141093427</v>
+        <v>1.07699184171637</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.345329552646405</v>
+        <v>3.695203787336359</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.77089820990759</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.281894742065613</v>
+        <v>-3.107276360579988</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.457783888767598</v>
+        <v>1.823296119487587</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9866429141093427</v>
+        <v>1.07699184171637</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.362883958373196</v>
+        <v>3.712758193063151</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.762753257312174</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.450370859035491</v>
+        <v>-3.275752477549866</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.382248489384231</v>
+        <v>1.747760720104219</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9586950783927619</v>
+        <v>1.049044005999789</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.337970304347832</v>
+        <v>3.687844539037787</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.744022954500036</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.752571330173907</v>
+        <v>-2.577952948688282</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.642637998116726</v>
+        <v>2.008150228836715</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8883470190223512</v>
+        <v>0.9786959466293781</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.277031165913447</v>
+        <v>3.626905400603402</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.734686976996941</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.729850226490755</v>
+        <v>-2.55523184500513</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.642390462086891</v>
+        <v>2.00790269280688</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8883470190223512</v>
+        <v>0.9786959466293781</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.267695188410352</v>
+        <v>3.617569423100306</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.89359310284811</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.859052039784797</v>
+        <v>-2.684433658299172</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.749615862620443</v>
+        <v>2.115128093340432</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.759145205728309</v>
+        <v>0.8494941333353359</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.349080226285095</v>
+        <v>3.69895446097505</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.930670925341756</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.013833046563053</v>
+        <v>-2.839214665077428</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.724781282402788</v>
+        <v>2.090293513122776</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7257775316738329</v>
+        <v>0.8161264592808597</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.366137444346056</v>
+        <v>3.716011679036011</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.927346281331301</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.006778356347879</v>
+        <v>-2.832159974862254</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.724278514478402</v>
+        <v>2.089790745198391</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7328322218890067</v>
+        <v>0.8231811494960335</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.367045614464706</v>
+        <v>3.71691984915466</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.937352434976043</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.979827132021391</v>
+        <v>-2.805208750535766</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.745065157853739</v>
+        <v>2.110577388573728</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7477125679167258</v>
+        <v>0.8380614955237526</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.385979975726078</v>
+        <v>3.735854210416034</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784104</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.121455567121003</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.115780140077708</v>
+        <v>-2.941161758592083</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.874787086776172</v>
+        <v>2.240299317496161</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7477125679167258</v>
+        <v>0.8380614955237526</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.570083107871039</v>
+        <v>3.919957342560993</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.113572262023996</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.13818825788258</v>
+        <v>-2.963569876396955</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.857940534557217</v>
+        <v>2.223452765277205</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7477125679167258</v>
+        <v>0.8380614955237526</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.562199802774032</v>
+        <v>3.912074037463986</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.115626261573633</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.286194025361979</v>
+        <v>-3.111575643876354</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.800792227115094</v>
+        <v>2.166304457835083</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6609855590531843</v>
+        <v>0.7513344866602112</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.512217597005544</v>
+        <v>3.862091831695499</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.17187997929548</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.295634951250509</v>
+        <v>-3.121016569764884</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.85326957448153</v>
+        <v>2.218781805201518</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7834126765965758</v>
+        <v>0.8737616042036026</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.641927585253426</v>
+        <v>3.991801819943381</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.174771073840781</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.347908558586151</v>
+        <v>-3.173290177100526</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.835251226092574</v>
+        <v>2.200763456812562</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7311390692609345</v>
+        <v>0.8214879968679614</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.613454515397342</v>
+        <v>3.963328750087297</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.172882886734556</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.424238536187056</v>
+        <v>-3.249620154701431</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.802831047945987</v>
+        <v>2.168343278665975</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7311390692609345</v>
+        <v>0.8214879968679614</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.611566328291117</v>
+        <v>3.961440562981072</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.167703116337419</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.62649225651141</v>
+        <v>-3.451873875025785</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.716749789419107</v>
+        <v>2.082262020139096</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.528885348936581</v>
+        <v>0.6192342765436079</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.485034325699368</v>
+        <v>3.834908560389322</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.166137126547571</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.788060682038665</v>
+        <v>-3.61344230055304</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.650556429418358</v>
+        <v>2.016068660138346</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4021024251387016</v>
+        <v>0.4924513527457285</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.407398581630792</v>
+        <v>3.757272816320747</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.17921053341349</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.920361974136218</v>
+        <v>-3.745743592650593</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.610709319445255</v>
+        <v>1.976221550165244</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4021024251387016</v>
+        <v>0.4924513527457285</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.420471988496711</v>
+        <v>3.770346223186666</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.17121573019643</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.106230284975448</v>
+        <v>-3.931611903489823</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.528367191892503</v>
+        <v>1.893879422612492</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.243536831818754</v>
+        <v>0.3338857594257808</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.317337829287682</v>
+        <v>3.667212063977637</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.169739771323432</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.13413107208492</v>
+        <v>-3.959512690599296</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.515730918175716</v>
+        <v>1.881243148895705</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2089399076758192</v>
+        <v>0.299288835282846</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.295103715928923</v>
+        <v>3.644977950618878</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787383</v>
+        <v>3.684895778787381</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.16650421530063</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.256657174787814</v>
+        <v>-4.08203879330219</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.463484921071758</v>
+        <v>1.828997151791746</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.08641380497292528</v>
+        <v>0.1767627325799521</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.218352498284386</v>
+        <v>3.568226732974341</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.233210174891134</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.487171670973403</v>
+        <v>-4.312553289487779</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.437985082188026</v>
+        <v>1.803497312908014</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.1441006912126634</v>
+        <v>-0.0537517636056366</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.146749760163536</v>
+        <v>3.496623994853491</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.373521893892981</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.743892488968227</v>
+        <v>-4.569274107482602</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.475608473991943</v>
+        <v>1.841120704711932</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.2525152653564783</v>
+        <v>-0.1621663377494514</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.222012734679094</v>
+        <v>3.571886969369049</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.442502163038621</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.897878906744367</v>
+        <v>-4.723260525258743</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.482994176027127</v>
+        <v>1.848506406747115</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.2525152653564783</v>
+        <v>-0.1621663377494514</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.290993003824734</v>
+        <v>3.640867238514689</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.428553365158742</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.847357002916701</v>
+        <v>-4.672738621431077</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.489254139678314</v>
+        <v>1.854766370398302</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.2525152653564783</v>
+        <v>-0.1621663377494514</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.277044205944855</v>
+        <v>3.62691844063481</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65633273360975</v>
+        <v>3.656332733609748</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.440423854214156</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.099832156924426</v>
+        <v>-4.925213775438801</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.400134567130638</v>
+        <v>1.765646797850627</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.2525152653564783</v>
+        <v>-0.1621663377494514</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.288914695000269</v>
+        <v>3.638788929690224</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.4416343887331</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.392727913403838</v>
+        <v>-5.218109531918214</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.284186799057817</v>
+        <v>1.649699029777806</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.2525152653564783</v>
+        <v>-0.1621663377494514</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.290125229519213</v>
+        <v>3.639999464209168</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251941</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.445756130960421</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.550271985133279</v>
+        <v>-5.375653603647655</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.225290912593362</v>
+        <v>1.59080314331335</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.3194170704967528</v>
+        <v>-0.2290681428897259</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.254105888662369</v>
+        <v>3.603980123352324</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.44083398369661</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.828236380716553</v>
+        <v>-5.653617999230929</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.109183007096242</v>
+        <v>1.47469523781623</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.409036804782237</v>
+        <v>-0.3186878771752102</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.195411900827268</v>
+        <v>3.545286135517223</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.603038040395655</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.945204073355444</v>
+        <v>-5.77058569186982</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.22459998673973</v>
+        <v>1.590112217459718</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.409036804782237</v>
+        <v>-0.3186878771752102</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.357615957526312</v>
+        <v>3.707490192216267</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.597884678359469</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.029922015576397</v>
+        <v>-5.855303634090773</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.185559447815162</v>
+        <v>1.551071678535151</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.4941528337102834</v>
+        <v>-0.4038039061032566</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.301392978133299</v>
+        <v>3.651267212823254</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.60811409592796</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.11185683384528</v>
+        <v>-5.937238452359656</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.1630149380761</v>
+        <v>1.528527168796089</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.5040875792973636</v>
+        <v>-0.4137386516903367</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.305661548349542</v>
+        <v>3.655535783039497</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.617039734383862</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.213832956093688</v>
+        <v>-6.039214574608064</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.13115012763264</v>
+        <v>1.496662358352628</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.6060637015457712</v>
+        <v>-0.5157147739387443</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.2534015134564</v>
+        <v>3.603275748146355</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.609192621628038</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.103826672616466</v>
+        <v>-5.929208291130842</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.167305528267704</v>
+        <v>1.532817758987692</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.582859129628496</v>
+        <v>-0.4925102020214691</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.25947714385094</v>
+        <v>3.609351378540895</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.613442632350012</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.960767096875541</v>
+        <v>-5.786148715389917</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.228779369286048</v>
+        <v>1.594291600006037</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.5748457030385167</v>
+        <v>-0.4844967754314898</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.268535210526902</v>
+        <v>3.618409445216857</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.620703515232548</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.659320371403703</v>
+        <v>-5.484701989918079</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.356618942357319</v>
+        <v>1.722131173077308</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.2733989775666794</v>
+        <v>-0.1830500499596526</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.456664128692541</v>
+        <v>3.806538363382495</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.621674692985259</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.683910615638887</v>
+        <v>-5.509292234153263</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.347754022415956</v>
+        <v>1.713266253135945</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.2733989775666794</v>
+        <v>-0.1830500499596526</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.457635306445251</v>
+        <v>3.807509541135206</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.622517597365014</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.632872239632367</v>
+        <v>-5.458253858146743</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.36901227719832</v>
+        <v>1.734524507918308</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.2733989775666794</v>
+        <v>-0.1830500499596526</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.458478210825007</v>
+        <v>3.808352445514961</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.64155569623916</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.591732944765736</v>
+        <v>-5.417114563280112</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.404506094019118</v>
+        <v>1.770018324739106</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.2322596827000486</v>
+        <v>-0.1419107550930218</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.502199886619131</v>
+        <v>3.852074121309085</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.457739692363094</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.481126804686134</v>
+        <v>-5.30650842320051</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.264932546174893</v>
+        <v>1.630444776894881</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.1216535426204466</v>
+        <v>-0.03130461501341975</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.384747566790826</v>
+        <v>3.734621801480781</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.461241736437058</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.611707539216977</v>
+        <v>-5.437089157731353</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.21620229643652</v>
+        <v>1.581714527156508</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.2522342771512891</v>
+        <v>-0.1618853495442623</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.309901170146285</v>
+        <v>3.659775404836239</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.445668555513141</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.447211205026015</v>
+        <v>-5.272592823540391</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.266427649188988</v>
+        <v>1.631939879908975</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.2522342771512891</v>
+        <v>-0.1618853495442623</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.294327989222368</v>
+        <v>3.644202223912322</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.444856265949571</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.474581137710447</v>
+        <v>-5.299962756224823</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.254667386551644</v>
+        <v>1.620179617271632</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.2522342771512891</v>
+        <v>-0.1618853495442623</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.293515699658797</v>
+        <v>3.643389934348751</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.454725045074643</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.484966332600337</v>
+        <v>-5.310347951114712</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.260382087720761</v>
+        <v>1.625894318440749</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.2626194720411784</v>
+        <v>-0.1722705444341516</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.297153361849936</v>
+        <v>3.64702759653989</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.525562050851068</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.503554491322562</v>
+        <v>-5.328936109836937</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.323783830008296</v>
+        <v>1.689296060728284</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.2812076307634038</v>
+        <v>-0.1908587031563769</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.356837472393026</v>
+        <v>3.70671170708298</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.522431061669367</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.503853038018597</v>
+        <v>-5.329234656532973</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.32053342214818</v>
+        <v>1.686045652868168</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.2812076307634038</v>
+        <v>-0.1908587031563769</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.353706483211325</v>
+        <v>3.703580717901279</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.526961956608758</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.40302990432817</v>
+        <v>-5.228411522842546</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.365393570563743</v>
+        <v>1.73090580128373</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.2687434152790499</v>
+        <v>-0.1783944876720231</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.365715907441328</v>
+        <v>3.715590142131282</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.527091210087301</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.212248543575763</v>
+        <v>-5.037630162090139</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.441835368343249</v>
+        <v>1.807347599063236</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.07796205452664257</v>
+        <v>0.01238687308038428</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.480313977371316</v>
+        <v>3.83018821206127</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.506928055824898</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.193731689533942</v>
+        <v>-5.019113308048318</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.429078955697574</v>
+        <v>1.794591186417561</v>
       </c>
       <c r="F2042" t="n">
-        <v>-0.06503192510143435</v>
+        <v>0.02531700250559249</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.467908900764038</v>
+        <v>3.817783135453992</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.541894992436956</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.168538505032624</v>
+        <v>-4.993920123547</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.474123166110159</v>
+        <v>1.839635396830147</v>
       </c>
       <c r="F2043" t="n">
-        <v>-0.039838740600116</v>
+        <v>0.05051018700691084</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.517991748076887</v>
+        <v>3.867865982766841</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.535581560338394</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.156484378119662</v>
+        <v>-4.981865996634038</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.472631384776782</v>
+        <v>1.83814361549677</v>
       </c>
       <c r="F2044" t="n">
-        <v>-0.02778461368715318</v>
+        <v>0.06256431391987366</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.518910792126102</v>
+        <v>3.868785026816056</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.53746219052253</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.16310762481002</v>
+        <v>-4.988489243324396</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.471862716284775</v>
+        <v>1.837374947004762</v>
       </c>
       <c r="F2045" t="n">
-        <v>-0.03440786037751153</v>
+        <v>0.05594106722951531</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.516817474296023</v>
+        <v>3.866691708985977</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.550313216400412</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.060227035281427</v>
+        <v>-4.885608653795803</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.525865977974094</v>
+        <v>1.891378208694082</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.06847272915108138</v>
+        <v>0.1588216567581082</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.591396853891061</v>
+        <v>3.941271088581015</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.570515886574007</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.083669074461514</v>
+        <v>-4.90905069297589</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.536691832475654</v>
+        <v>1.902204063195641</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.06847272915108138</v>
+        <v>0.1588216567581082</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.611599524064656</v>
+        <v>3.961473758754609</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.570515886574007</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.332152604277859</v>
+        <v>-4.927123201267501</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.437298420549116</v>
+        <v>1.894975059878997</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.06847272915108138</v>
+        <v>0.1588216567581082</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.611599524064656</v>
+        <v>3.961473758754609</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.574977279467523</v>
+        <v>3.818701340576158</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.640229825803451</v>
+        <v>4.179693171172143</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.332152604277859</v>
+        <v>-4.927123201267501</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.437298420549116</v>
+        <v>1.894975059878997</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.06847272915108138</v>
+        <v>0.1588216567581082</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.633293622789818</v>
+        <v>4.17275696815851</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240807.xlsx
+++ b/tame_output/ON/bt/strategyON_20240807.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.3%</t>
+          <t>-655.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-121.0%</t>
+          <t>-119.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.7%</t>
+          <t>-156.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>173.0%</t>
+          <t>262.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-133.7%</t>
+          <t>-134.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-208.1%</t>
+          <t>-209.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-19.5%</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.379563423659349</v>
+        <v>-6.367574934299284</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4067416120659622</v>
+        <v>0.4115370078099878</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.185418362854204</v>
+        <v>-0.1734298734941398</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.847672388130927</v>
+        <v>2.854865481746966</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.336015016888658</v>
+        <v>-6.324026527528594</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4172003626791452</v>
+        <v>0.4219957584231708</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.185418362854204</v>
+        <v>-0.1734298734941398</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.840711776035834</v>
+        <v>2.847904869651873</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.302651810409889</v>
+        <v>-6.290663321049825</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4450079996517959</v>
+        <v>0.4498033953958216</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.185418362854204</v>
+        <v>-0.1734298734941398</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.855174130416977</v>
+        <v>2.862367224033016</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.194392673287368</v>
+        <v>-6.182404183927304</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4828437749599996</v>
+        <v>0.4876391707040253</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.185418362854204</v>
+        <v>-0.1734298734941398</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.849706250876172</v>
+        <v>2.856899344492211</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.071101538470237</v>
+        <v>-6.059113049110173</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5296583228974288</v>
+        <v>0.5344537186414544</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.06212722803707355</v>
+        <v>-0.0501387386770093</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.921179025777027</v>
+        <v>2.928372119393066</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.049952339566794</v>
+        <v>-6.037963850206729</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5458189806961311</v>
+        <v>0.5506143764401568</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.04097802913363019</v>
+        <v>-0.02898953977356594</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.941569523356418</v>
+        <v>2.948762616972457</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.806186897583349</v>
+        <v>-5.794198408223285</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6391058658365596</v>
+        <v>0.6439012615805852</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.04097802913363019</v>
+        <v>-0.02898953977356594</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.937350231703469</v>
+        <v>2.944543325319507</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.704424077306054</v>
+        <v>-5.69243558794599</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6819353078674939</v>
+        <v>0.6867307036115196</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.02775896074120149</v>
+        <v>-0.01577047138113724</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.947405986658942</v>
+        <v>2.954599080274981</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.45457368335698</v>
+        <v>-5.442585193996916</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7746175404308255</v>
+        <v>0.7794129361748512</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.02775896074120149</v>
+        <v>-0.01577047138113724</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.940148061642644</v>
+        <v>2.947341155258683</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.278681590889548</v>
+        <v>-5.266693101529484</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8485735009384472</v>
+        <v>0.8533688966824728</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.02775896074120149</v>
+        <v>-0.01577047138113724</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.943747185163293</v>
+        <v>2.950940278779332</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.107235127867084</v>
+        <v>-5.09524663850702</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9304795922019862</v>
+        <v>0.9352749879460118</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1436875022812616</v>
+        <v>0.1556759916413259</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.059942569031325</v>
+        <v>3.067135662647363</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.032945562128745</v>
+        <v>-5.020957072768681</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9592158961136188</v>
+        <v>0.9640112918576444</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2179770680196009</v>
+        <v>0.2299655573796652</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.103536786090625</v>
+        <v>3.110729879706664</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.969309819894811</v>
+        <v>-4.957321330534747</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9893649940615101</v>
+        <v>0.9941603898055358</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2816128102535355</v>
+        <v>0.2936012996135997</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.146413032485303</v>
+        <v>3.153606126101342</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.857883060568891</v>
+        <v>-4.845894571208826</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.015129956575674</v>
+        <v>1.019925352319699</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2816128102535355</v>
+        <v>0.2936012996135997</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.127607291269099</v>
+        <v>3.134800384885137</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.868385683634179</v>
+        <v>-4.856397194274115</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.012671983974436</v>
+        <v>1.017467379718461</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2711101871882466</v>
+        <v>0.2830986765483108</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.123048794054803</v>
+        <v>3.130241887670842</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.796143115462985</v>
+        <v>-4.784154626102921</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.045498325077734</v>
+        <v>1.050293720821759</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2711101871882466</v>
+        <v>0.2830986765483108</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.126978107889623</v>
+        <v>3.134171201505662</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.778429428585119</v>
+        <v>-4.766440939225055</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05326238374622</v>
+        <v>1.058057779490245</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2742915160851634</v>
+        <v>0.2862800054452276</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.129565489145113</v>
+        <v>3.136758582761152</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.669624543105392</v>
+        <v>-4.657636053745328</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.093782409158104</v>
+        <v>1.09857780490213</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2742915160851634</v>
+        <v>0.2862800054452276</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.126563560365107</v>
+        <v>3.133756653981145</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.449603745068382</v>
+        <v>-4.437615255708318</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.183369765383522</v>
+        <v>1.188165161127548</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4155113611531436</v>
+        <v>0.4274998505132079</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.212874504416509</v>
+        <v>3.220067598032547</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.316736056005104</v>
+        <v>-4.30474756664504</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.252411023810657</v>
+        <v>1.257206419554682</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4155113611531436</v>
+        <v>0.4274998505132079</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.228768687218332</v>
+        <v>3.235961780834371</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.196562972640606</v>
+        <v>-4.184574483280541</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.301626101596758</v>
+        <v>1.306421497340784</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5356844445176425</v>
+        <v>0.5476729338777069</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.302018381677333</v>
+        <v>3.309211475293372</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.051890827540868</v>
+        <v>-4.039902338180804</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.369583062198093</v>
+        <v>1.374378457942119</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.68035658961738</v>
+        <v>0.6923450789774444</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.398909771298616</v>
+        <v>3.406102864914654</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.11176565489856</v>
+        <v>-4.099777165538496</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.331670622656442</v>
+        <v>1.336466018400468</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6204817622596879</v>
+        <v>0.6324702516197522</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.349022366285426</v>
+        <v>3.356215459901465</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.991945423987723</v>
+        <v>-3.979956934627659</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.394887884254985</v>
+        <v>1.399683279999011</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6204817622596879</v>
+        <v>0.6324702516197522</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.364311535519635</v>
+        <v>3.371504629135674</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.994415130449529</v>
+        <v>-3.982426641089465</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.301544200992705</v>
+        <v>1.30633959673673</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6180120557978817</v>
+        <v>0.630000545157946</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.270473910964993</v>
+        <v>3.277667004581031</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.062785316773539</v>
+        <v>-4.050796827413475</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.193457987948402</v>
+        <v>1.198253383692428</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6272877548340966</v>
+        <v>0.639276244194161</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.195301191872023</v>
+        <v>3.202494285488062</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.076573369620585</v>
+        <v>-4.064584880260521</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.178379475441475</v>
+        <v>1.1831748711855</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6272877548340966</v>
+        <v>0.639276244194161</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.185737900503914</v>
+        <v>3.192930994119953</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.132093445513175</v>
+        <v>-4.120104956153111</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.293202281776641</v>
+        <v>1.297997677520667</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6272877548340966</v>
+        <v>0.639276244194161</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.322768737196117</v>
+        <v>3.329961830812155</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.956619185720706</v>
+        <v>-3.944630696360642</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.367959217685417</v>
+        <v>1.372754613429442</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6272877548340966</v>
+        <v>0.639276244194161</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.327335969187904</v>
+        <v>3.334529062803943</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.067555438361954</v>
+        <v>-4.05556694900189</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.299326745390124</v>
+        <v>1.30412214113415</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6272877548340966</v>
+        <v>0.639276244194161</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.303077997949111</v>
+        <v>3.31027109156515</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.033891892889672</v>
+        <v>-4.021903403529608</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.241330476980487</v>
+        <v>1.246125872724513</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6609513003063785</v>
+        <v>0.6729397896664429</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.25181443863393</v>
+        <v>3.259007532249969</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.974039273685949</v>
+        <v>-3.962050784325885</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.275443911094109</v>
+        <v>1.280239306838134</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6609513003063785</v>
+        <v>0.6729397896664429</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.261986825066063</v>
+        <v>3.269179918682101</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.887795810659571</v>
+        <v>-3.875807321299507</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.30488756687852</v>
+        <v>1.309682962622546</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6609513003063785</v>
+        <v>0.6729397896664429</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.256933095639923</v>
+        <v>3.264126189255962</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.933102630058551</v>
+        <v>-3.921114140698487</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.278540614563454</v>
+        <v>1.283336010307479</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6201411372971477</v>
+        <v>0.6321296266572121</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.22422277327891</v>
+        <v>3.231415866894949</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.962135734760853</v>
+        <v>-3.950147245400788</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.267479245715635</v>
+        <v>1.27227464145966</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6201411372971477</v>
+        <v>0.6321296266572121</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.224774646312012</v>
+        <v>3.23196773992805</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.869325253309993</v>
+        <v>-3.857336763949929</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.233876130187344</v>
+        <v>1.23867152593137</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7129516187480071</v>
+        <v>0.7249401081080714</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.209733627073893</v>
+        <v>3.216926720689932</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.913714722639421</v>
+        <v>-3.901726233279357</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.217993818380174</v>
+        <v>1.222789214124199</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6685621494185794</v>
+        <v>0.6805506387786437</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.184973421400837</v>
+        <v>3.192166515016876</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.030256327744763</v>
+        <v>-4.018267838384699</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.16645288484976</v>
+        <v>1.171248280593785</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5520205443132367</v>
+        <v>0.564009033673301</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.110124166849355</v>
+        <v>3.117317260465393</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.917879326562091</v>
+        <v>-3.905890837202027</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.216894981153496</v>
+        <v>1.221690376897522</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5520205443132367</v>
+        <v>0.564009033673301</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.115615462680022</v>
+        <v>3.12280855629606</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.945659724463444</v>
+        <v>-3.93367123510338</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.217280023761494</v>
+        <v>1.222075419505519</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5242401464118835</v>
+        <v>0.5362286357719479</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.110444425707749</v>
+        <v>3.117637519323788</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.064040397193582</v>
+        <v>-4.052051907833518</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.008283474670092</v>
+        <v>1.013078870414117</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4570222942609073</v>
+        <v>0.4690107836209717</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.908469434417817</v>
+        <v>2.915662528033855</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.172654475636913</v>
+        <v>-4.160665986276849</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.084987504011965</v>
+        <v>1.089782899755991</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4570222942609073</v>
+        <v>0.4690107836209717</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.028619095137022</v>
+        <v>3.035812188753061</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.137245437388771</v>
+        <v>-4.125256948028706</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.113664145413545</v>
+        <v>1.118459541157571</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4570222942609073</v>
+        <v>0.4690107836209717</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.043132121239345</v>
+        <v>3.050325214855384</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.09886177483062</v>
+        <v>-4.086873285470555</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.126437051779174</v>
+        <v>1.1312324475232</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4954059568190585</v>
+        <v>0.5073944461791229</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.063581760116604</v>
+        <v>3.070774853732643</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.921745444795453</v>
+        <v>-3.909756955435389</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.194012612638542</v>
+        <v>1.198808008382568</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4954059568190585</v>
+        <v>0.5073944461791229</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.060310788961906</v>
+        <v>3.067503882577945</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.966837689628999</v>
+        <v>-3.954849200268935</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.176659106467037</v>
+        <v>1.181454502211063</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4335099136496687</v>
+        <v>0.4454984030097331</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.023856554822186</v>
+        <v>3.031049648438224</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.787462268390231</v>
+        <v>-3.775473779030167</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.242196250268959</v>
+        <v>1.246991646012984</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5902866718203874</v>
+        <v>0.6022751611804518</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.111709585031031</v>
+        <v>3.11890267864707</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.832476481910838</v>
+        <v>-3.820487992550774</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.204998020192306</v>
+        <v>1.209793415936332</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5599377765057828</v>
+        <v>0.5719262658658472</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.074307703173858</v>
+        <v>3.081500796789897</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.099480992183273</v>
+        <v>-4.087492502823209</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.103887778422278</v>
+        <v>1.108683174166303</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3655747384628342</v>
+        <v>0.3775632278228986</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.963381442687035</v>
+        <v>2.970574536303074</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.200678773620446</v>
+        <v>-4.188690284260382</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.06261258774391</v>
+        <v>1.067407983487936</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.297165924917515</v>
+        <v>0.3091544142775794</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.921540076456345</v>
+        <v>2.928733170072384</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.194167807006133</v>
+        <v>-4.182179317646069</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.062816935943952</v>
+        <v>1.067612331687977</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.297165924917515</v>
+        <v>0.3091544142775794</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.919140038010661</v>
+        <v>2.9263331316267</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.175129679298836</v>
+        <v>-4.163141189938772</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.066956906235116</v>
+        <v>1.071752301979141</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2389823135863205</v>
+        <v>0.2509708029463849</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.88075459042019</v>
+        <v>2.887947684036228</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.206256310449454</v>
+        <v>-4.19426782108939</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.173800655409059</v>
+        <v>1.178596051153084</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2389823135863205</v>
+        <v>0.2509708029463849</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.00004899205438</v>
+        <v>3.007242085670419</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.220123071783372</v>
+        <v>-4.208134582423308</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.169087279861625</v>
+        <v>1.173882675605651</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2011243968524976</v>
+        <v>0.2131128862125619</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.97816757100022</v>
+        <v>2.985360664616258</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.175318900243442</v>
+        <v>-4.163330410883378</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.193017478874523</v>
+        <v>1.197812874618549</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2011243968524976</v>
+        <v>0.2131128862125619</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.984176101397146</v>
+        <v>2.991369195013184</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.02757593000844</v>
+        <v>-4.015587440648376</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.150064888245723</v>
+        <v>1.154860283989749</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3689317540873807</v>
+        <v>0.3809202434474451</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.982810737015275</v>
+        <v>2.990003830631314</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.111397151283138</v>
+        <v>-4.099408661923074</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.119330021267325</v>
+        <v>1.124125417011351</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3689317540873807</v>
+        <v>0.3809202434474451</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.985604358546756</v>
+        <v>2.992797452162795</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.105244445230354</v>
+        <v>-4.09325595587029</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.122453452080097</v>
+        <v>1.127248847824123</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.375084460140165</v>
+        <v>0.3870729495002294</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.989958330570085</v>
+        <v>2.997151424186124</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.122053743380856</v>
+        <v>-4.110065254020792</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.114810209560007</v>
+        <v>1.119605605304032</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3582751619896634</v>
+        <v>0.3702636513497277</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.978953228419894</v>
+        <v>2.986146322035933</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.059755744604733</v>
+        <v>-4.047767255244669</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.206064962867276</v>
+        <v>1.210860358611302</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3582751619896634</v>
+        <v>0.3702636513497277</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.045288782216715</v>
+        <v>3.052481875832754</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.857965546939575</v>
+        <v>-3.845977057579511</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.089073043647466</v>
+        <v>1.093868439391492</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5562933541588178</v>
+        <v>0.5682818435188821</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.966391699232335</v>
+        <v>2.973584792848373</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.90885225962577</v>
+        <v>-3.896863770265706</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.139008590895164</v>
+        <v>1.14380398663919</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5054066414726233</v>
+        <v>0.5173951308326876</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.006149903942794</v>
+        <v>3.013342997558832</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.006592804250745</v>
+        <v>-3.99460431489068</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.114540109161218</v>
+        <v>1.119335504905243</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.489517363339643</v>
+        <v>0.5015058526997074</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.011244073179049</v>
+        <v>3.018437166795088</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.066802102256029</v>
+        <v>-4.054813612895965</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.088992370783775</v>
+        <v>1.093787766527801</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4293080653343585</v>
+        <v>0.4412965546944229</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.97365447520055</v>
+        <v>2.980847568816588</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.990380055824103</v>
+        <v>-3.978391566464039</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.118052807396475</v>
+        <v>1.1228482031405</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4293080653343585</v>
+        <v>0.4412965546944229</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.972146093240478</v>
+        <v>2.979339186856517</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.946006924185534</v>
+        <v>-3.93401843482547</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.135664927487338</v>
+        <v>1.140460323231364</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4736811969729271</v>
+        <v>0.4856696863329915</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.998632839659056</v>
+        <v>3.005825933275094</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.968487275044419</v>
+        <v>-3.956498785684355</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.121066581282375</v>
+        <v>1.125861977026401</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4736811969729271</v>
+        <v>0.4856696863329915</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.993026633797646</v>
+        <v>3.000219727413685</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.920831544483363</v>
+        <v>-3.908843055123299</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.146510630534602</v>
+        <v>1.151306026278628</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5213369275339828</v>
+        <v>0.5333254168940471</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.028001829162084</v>
+        <v>3.035194922778123</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.820313385984608</v>
+        <v>-3.808324896624544</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.191610267308829</v>
+        <v>1.196405663052854</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6218550860327373</v>
+        <v>0.6338435753928017</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.093205097636062</v>
+        <v>3.100398191252101</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.880979976386997</v>
+        <v>-3.868991487026933</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.154098303623745</v>
+        <v>1.158893699367771</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5401567693142036</v>
+        <v>0.552145258674268</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.030940780080814</v>
+        <v>3.038133873696852</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.836141574778599</v>
+        <v>-3.824153085418535</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.176131366877733</v>
+        <v>1.180926762621759</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5447002022590731</v>
+        <v>0.5566886916191375</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.037764542458364</v>
+        <v>3.044957636074403</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.855640031020608</v>
+        <v>-3.843651541660543</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.172492924012008</v>
+        <v>1.177288319756034</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4966155609791688</v>
+        <v>0.5086040503392332</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.0130746973215</v>
+        <v>3.020267790937538</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.811437193934707</v>
+        <v>-3.799448704574643</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.196053661374205</v>
+        <v>1.200849057118231</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5408183980650693</v>
+        <v>0.5528068874251336</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.045476002100877</v>
+        <v>3.052669095716916</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.84841622159815</v>
+        <v>-3.836427732238086</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.179672050778075</v>
+        <v>1.184467446522101</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5777922998563998</v>
+        <v>0.5897807892164642</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.066070343644923</v>
+        <v>3.073263437260962</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.690124804058878</v>
+        <v>-3.678136314698814</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.294236382976824</v>
+        <v>1.29903177872085</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5777922998563998</v>
+        <v>0.5897807892164642</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117318108827963</v>
+        <v>3.124511202444001</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.482482800424402</v>
+        <v>-3.470494311064338</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.375733889024868</v>
+        <v>1.380529284768893</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.785434303490876</v>
+        <v>0.7974227928509403</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.240344015602902</v>
+        <v>3.24753710921894</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.431450707701874</v>
+        <v>-3.41946221834181</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.391094954352149</v>
+        <v>1.395890350096174</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8364663962134039</v>
+        <v>0.8484548855734683</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265911499474688</v>
+        <v>3.273104593090727</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.366226526574668</v>
+        <v>-3.354238037214604</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.434372030895736</v>
+        <v>1.439167426639762</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9016905773406095</v>
+        <v>0.9136790667006739</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322233412243716</v>
+        <v>3.329426505859755</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.328799506503535</v>
+        <v>-3.316811017143471</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.44530381122347</v>
+        <v>1.450099206967495</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9069421153697912</v>
+        <v>0.9189306047298555</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321345307360506</v>
+        <v>3.328538400976544</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.348911162538243</v>
+        <v>-3.336922673178179</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.438515941140827</v>
+        <v>1.443311336884852</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9179694603672104</v>
+        <v>0.9299579497272747</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329218506690198</v>
+        <v>3.336411600306236</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.295166348111038</v>
+        <v>-3.283177858750974</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.620571637932919</v>
+        <v>1.625367033676945</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9280327698076724</v>
+        <v>0.9400212591677367</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.495814263375685</v>
+        <v>3.503007356991724</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.220384087086026</v>
+        <v>-3.208395597725962</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.770597451560742</v>
+        <v>1.775392847304767</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.002815030832685</v>
+        <v>1.014803520192749</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.66079652920851</v>
+        <v>3.667989622824549</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.194300002822218</v>
+        <v>-3.182311513462154</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.772739061280124</v>
+        <v>1.777534457024149</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.002815030832685</v>
+        <v>1.014803520192749</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.652504505222369</v>
+        <v>3.659697598838408</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.116168821973271</v>
+        <v>-3.104180332613207</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.802184729203482</v>
+        <v>1.806980124947508</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.07699184171637</v>
+        <v>1.088980331076434</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.695203787336359</v>
+        <v>3.702396880952398</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.107276360579988</v>
+        <v>-3.095287871219924</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.823296119487587</v>
+        <v>1.828091515231612</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.07699184171637</v>
+        <v>1.088980331076434</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.712758193063151</v>
+        <v>3.71995128667919</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.275752477549866</v>
+        <v>-3.263763988189802</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.747760720104219</v>
+        <v>1.752556115848245</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.049044005999789</v>
+        <v>1.061032495359853</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.687844539037787</v>
+        <v>3.695037632653825</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.577952948688282</v>
+        <v>-2.565964459328218</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.008150228836715</v>
+        <v>2.01294562458074</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9786959466293781</v>
+        <v>0.9906844359894427</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.626905400603402</v>
+        <v>3.634098494219441</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.55523184500513</v>
+        <v>-2.543243355645066</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.00790269280688</v>
+        <v>2.012698088550906</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9786959466293781</v>
+        <v>0.9906844359894427</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.617569423100306</v>
+        <v>3.624762516716345</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.684433658299172</v>
+        <v>-2.672445168939108</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.115128093340432</v>
+        <v>2.119923489084458</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8494941333353359</v>
+        <v>0.8614826226954004</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.69895446097505</v>
+        <v>3.706147554591089</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.839214665077428</v>
+        <v>-2.827226175717364</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.090293513122776</v>
+        <v>2.095088908866802</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8161264592808597</v>
+        <v>0.8281149486409243</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.716011679036011</v>
+        <v>3.72320477265205</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.832159974862254</v>
+        <v>-2.82017148550219</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.089790745198391</v>
+        <v>2.094586140942416</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8231811494960335</v>
+        <v>0.8351696388560981</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.71691984915466</v>
+        <v>3.724112942770699</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.805208750535766</v>
+        <v>-2.793220261175702</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.110577388573728</v>
+        <v>2.115372784317754</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8380614955237526</v>
+        <v>0.8500499848838172</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.735854210416034</v>
+        <v>3.743047304032072</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.941161758592083</v>
+        <v>-2.929173269232018</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.240299317496161</v>
+        <v>2.245094713240187</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8380614955237526</v>
+        <v>0.8500499848838172</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919957342560993</v>
+        <v>3.927150436177032</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.963569876396955</v>
+        <v>-2.951581387036891</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.223452765277205</v>
+        <v>2.228248161021231</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8380614955237526</v>
+        <v>0.8500499848838172</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.912074037463986</v>
+        <v>3.919267131080025</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.111575643876354</v>
+        <v>-3.09958715451629</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.166304457835083</v>
+        <v>2.171099853579109</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7513344866602112</v>
+        <v>0.7633229760202758</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.862091831695499</v>
+        <v>3.869284925311538</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.121016569764884</v>
+        <v>-3.10902808040482</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.218781805201518</v>
+        <v>2.223577200945544</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8737616042036026</v>
+        <v>0.8857500935636672</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.991801819943381</v>
+        <v>3.99899491355942</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.173290177100526</v>
+        <v>-3.161301687740461</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.200763456812562</v>
+        <v>2.205558852556588</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8214879968679614</v>
+        <v>0.8334764862280259</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.963328750087297</v>
+        <v>3.970521843703336</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.249620154701431</v>
+        <v>-3.237631665341367</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.168343278665975</v>
+        <v>2.173138674410001</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8214879968679614</v>
+        <v>0.8334764862280259</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.961440562981072</v>
+        <v>3.968633656597111</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.451873875025785</v>
+        <v>-3.439885385665721</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.082262020139096</v>
+        <v>2.087057415883122</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6192342765436079</v>
+        <v>0.6312227659036724</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.834908560389322</v>
+        <v>3.842101654005361</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.61344230055304</v>
+        <v>-3.601453811192976</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016068660138346</v>
+        <v>2.020864055882372</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4924513527457285</v>
+        <v>0.5044398421057931</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.757272816320747</v>
+        <v>3.764465909936786</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.745743592650593</v>
+        <v>-3.733755103290529</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.976221550165244</v>
+        <v>1.981016945909269</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4924513527457285</v>
+        <v>0.5044398421057931</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.770346223186666</v>
+        <v>3.777539316802704</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.931611903489823</v>
+        <v>-3.919623414129759</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.893879422612492</v>
+        <v>1.898674818356517</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3338857594257808</v>
+        <v>0.3458742487858454</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.667212063977637</v>
+        <v>3.674405157593676</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.959512690599296</v>
+        <v>-3.947524201239232</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.881243148895705</v>
+        <v>1.88603854463973</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.299288835282846</v>
+        <v>0.3112773246429106</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.644977950618878</v>
+        <v>3.652171044234917</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.08203879330219</v>
+        <v>-4.070050303942126</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.828997151791746</v>
+        <v>1.833792547535771</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1767627325799521</v>
+        <v>0.1887512219400167</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.568226732974341</v>
+        <v>3.575419826590379</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.312553289487779</v>
+        <v>-4.300564800127715</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.803497312908014</v>
+        <v>1.80829270865204</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.0537517636056366</v>
+        <v>-0.04176327424557202</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.496623994853491</v>
+        <v>3.50381708846953</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.569274107482602</v>
+        <v>-4.557285618122538</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.841120704711932</v>
+        <v>1.845916100455957</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1621663377494514</v>
+        <v>-0.1501778483893869</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.571886969369049</v>
+        <v>3.579080062985088</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.723260525258743</v>
+        <v>-4.711272035898679</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.848506406747115</v>
+        <v>1.853301802491141</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1621663377494514</v>
+        <v>-0.1501778483893869</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.640867238514689</v>
+        <v>3.648060332130728</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.672738621431077</v>
+        <v>-4.660750132071013</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.854766370398302</v>
+        <v>1.859561766142328</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1621663377494514</v>
+        <v>-0.1501778483893869</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.62691844063481</v>
+        <v>3.634111534250849</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.925213775438801</v>
+        <v>-4.913225286078737</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.765646797850627</v>
+        <v>1.770442193594652</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1621663377494514</v>
+        <v>-0.1501778483893869</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.638788929690224</v>
+        <v>3.645982023306263</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.218109531918214</v>
+        <v>-5.206121042558149</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.649699029777806</v>
+        <v>1.654494425521831</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1621663377494514</v>
+        <v>-0.1501778483893869</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.639999464209168</v>
+        <v>3.647192557825206</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.375653603647655</v>
+        <v>-5.363665114287591</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.59080314331335</v>
+        <v>1.595598539057376</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.2290681428897259</v>
+        <v>-0.2170796535296614</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.603980123352324</v>
+        <v>3.611173216968363</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.653617999230929</v>
+        <v>-5.641629509870865</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.47469523781623</v>
+        <v>1.479490633560256</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.3186878771752102</v>
+        <v>-0.3066993878151456</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.545286135517223</v>
+        <v>3.552479229133262</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.77058569186982</v>
+        <v>-5.758597202509756</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.590112217459718</v>
+        <v>1.594907613203744</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.3186878771752102</v>
+        <v>-0.3066993878151456</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.707490192216267</v>
+        <v>3.714683285832306</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.855303634090773</v>
+        <v>-5.843315144730709</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.551071678535151</v>
+        <v>1.555867074279177</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.4038039061032566</v>
+        <v>-0.391815416743192</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.651267212823254</v>
+        <v>3.658460306439292</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.937238452359656</v>
+        <v>-5.925249962999592</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.528527168796089</v>
+        <v>1.533322564540114</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.4137386516903367</v>
+        <v>-0.4017501623302722</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.655535783039497</v>
+        <v>3.662728876655536</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.039214574608064</v>
+        <v>-6.027226085248</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.496662358352628</v>
+        <v>1.501457754096654</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.5157147739387443</v>
+        <v>-0.5037262845786797</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.603275748146355</v>
+        <v>3.610468841762394</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.929208291130842</v>
+        <v>-5.917219801770778</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.532817758987692</v>
+        <v>1.537613154731718</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4925102020214691</v>
+        <v>-0.4805217126614045</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.609351378540895</v>
+        <v>3.616544472156934</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.786148715389917</v>
+        <v>-5.774160226029853</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.594291600006037</v>
+        <v>1.599086995750062</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4844967754314898</v>
+        <v>-0.4725082860714253</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.618409445216857</v>
+        <v>3.625602538832896</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.484701989918079</v>
+        <v>-5.472713500558015</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.722131173077308</v>
+        <v>1.726926568821333</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1830500499596526</v>
+        <v>-0.171061560599588</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.806538363382495</v>
+        <v>3.813731456998534</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.509292234153263</v>
+        <v>-5.497303744793199</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.713266253135945</v>
+        <v>1.71806164887997</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1830500499596526</v>
+        <v>-0.171061560599588</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.807509541135206</v>
+        <v>3.814702634751245</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.458253858146743</v>
+        <v>-5.446265368786679</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.734524507918308</v>
+        <v>1.739319903662333</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1830500499596526</v>
+        <v>-0.171061560599588</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.808352445514961</v>
+        <v>3.815545539131</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.417114563280112</v>
+        <v>-5.405126073920048</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.770018324739106</v>
+        <v>1.774813720483131</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.1419107550930218</v>
+        <v>-0.1299222657329572</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.852074121309085</v>
+        <v>3.859267214925124</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.30650842320051</v>
+        <v>-5.294519933840446</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.630444776894881</v>
+        <v>1.635240172638907</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.03130461501341975</v>
+        <v>-0.01931612565335517</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.734621801480781</v>
+        <v>3.74181489509682</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.437089157731353</v>
+        <v>-5.425100668371289</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.581714527156508</v>
+        <v>1.586509922900533</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1618853495442623</v>
+        <v>-0.1498968601841977</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.659775404836239</v>
+        <v>3.666968498452278</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.272592823540391</v>
+        <v>-5.260604334180327</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.631939879908975</v>
+        <v>1.636735275653001</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1618853495442623</v>
+        <v>-0.1498968601841977</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.644202223912322</v>
+        <v>3.65139531752836</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.299962756224823</v>
+        <v>-5.287974266864759</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.620179617271632</v>
+        <v>1.624975013015657</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1618853495442623</v>
+        <v>-0.1498968601841977</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.643389934348751</v>
+        <v>3.65058302796479</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.310347951114712</v>
+        <v>-5.298359461754648</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.625894318440749</v>
+        <v>1.630689714184774</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1722705444341516</v>
+        <v>-0.160282055074087</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.64702759653989</v>
+        <v>3.654220690155929</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.328936109836937</v>
+        <v>-5.316947620476873</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.689296060728284</v>
+        <v>1.69409145647231</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.1908587031563769</v>
+        <v>-0.1788702137963123</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.70671170708298</v>
+        <v>3.713904800699019</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.329234656532973</v>
+        <v>-5.317246167172909</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.686045652868168</v>
+        <v>1.690841048612194</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.1908587031563769</v>
+        <v>-0.1788702137963123</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.703580717901279</v>
+        <v>3.710773811517317</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.228411522842546</v>
+        <v>-5.216423033482481</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.73090580128373</v>
+        <v>1.735701197027756</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.1783944876720231</v>
+        <v>-0.1664059983119585</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.715590142131282</v>
+        <v>3.722783235747321</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.037630162090139</v>
+        <v>-5.025641672730075</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.807347599063236</v>
+        <v>1.812142994807262</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.01238687308038428</v>
+        <v>0.02437536244044886</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.83018821206127</v>
+        <v>3.837381305677309</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.019113308048318</v>
+        <v>-5.007124818688254</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.794591186417561</v>
+        <v>1.799386582161587</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.02531700250559249</v>
+        <v>0.03730549186565707</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.817783135453992</v>
+        <v>3.82497622907003</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.993920123547</v>
+        <v>-4.981931634186936</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.839635396830147</v>
+        <v>1.844430792574172</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.05051018700691084</v>
+        <v>0.06249867636697543</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.867865982766841</v>
+        <v>3.87505907638288</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.981865996634038</v>
+        <v>-4.969877507273973</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.83814361549677</v>
+        <v>1.842939011240795</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.06256431391987366</v>
+        <v>0.07455280327993824</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.868785026816056</v>
+        <v>3.875978120432095</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.988489243324396</v>
+        <v>-4.976500753964332</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.837374947004762</v>
+        <v>1.842170342748788</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.05594106722951531</v>
+        <v>0.06792955658957989</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.866691708985977</v>
+        <v>3.873884802602016</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.885608653795803</v>
+        <v>-4.873620164435739</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.891378208694082</v>
+        <v>1.896173604438107</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.1588216567581082</v>
+        <v>0.1708101461181728</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.941271088581015</v>
+        <v>3.948464182197054</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.90905069297589</v>
+        <v>-4.897062203615826</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.902204063195641</v>
+        <v>1.906999458939667</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.1588216567581082</v>
+        <v>0.1708101461181728</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.961473758754609</v>
+        <v>3.968666852370649</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.927123201267501</v>
+        <v>-4.915134711907437</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.894975059878997</v>
+        <v>1.899770455623022</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.1588216567581082</v>
+        <v>0.1708101461181728</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.961473758754609</v>
+        <v>3.968666852370649</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.818701340576158</v>
+        <v>3.867287382469507</v>
       </c>
       <c r="C2049" t="n">
         <v>4.179693171172143</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.927123201267501</v>
+        <v>-4.943670734237966</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.894975059878997</v>
+        <v>2.20186845316321</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.1588216567581082</v>
+        <v>0.1422741237876444</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.17275696815851</v>
+        <v>4.26505764544473</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240807.xlsx
+++ b/tame_output/ON/bt/strategyON_20240807.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>106.3%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.1%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-655.9%</t>
+          <t>-673.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,37 +1145,37 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-119.8%</t>
+          <t>-153.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-188.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>262.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.6%</t>
+          <t>-129.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.8%</t>
+          <t>-211.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-45.5%</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706666</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.678985839606478</v>
+        <v>-8.889331876951555</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3316306679010914</v>
+        <v>-0.4157690828391223</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.392726819404753</v>
+        <v>-1.483771824682167</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.304684000612395</v>
+        <v>2.250056997445947</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.712638678114951</v>
+        <v>-8.922984715460029</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3406092488200447</v>
+        <v>-0.4247476637580756</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.49314018732179</v>
+        <v>-1.584185192599204</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.248918534346609</v>
+        <v>2.194291531180161</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.639168846447502</v>
+        <v>-8.84951488379258</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2958496146596441</v>
+        <v>-0.379988029597675</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.419670355654342</v>
+        <v>-1.510715360931755</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.308372134840499</v>
+        <v>2.253745131674051</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.814293263834045</v>
+        <v>-9.024639301179123</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3513441608667445</v>
+        <v>-0.4354825758047758</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.594794773040886</v>
+        <v>-1.685839778318299</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.21785270515609</v>
+        <v>2.163225701989642</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.048745357848535</v>
+        <v>-9.259091395193613</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4523441633741365</v>
+        <v>-0.5364825783121674</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.594794773040886</v>
+        <v>-1.685839778318299</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.210633540254494</v>
+        <v>2.156006537088046</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.153120088874982</v>
+        <v>-9.363466126220059</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5007662465586913</v>
+        <v>-0.5849046614967222</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.699169504067332</v>
+        <v>-1.790214509344745</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.14133651086465</v>
+        <v>2.086709507698202</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.205906244475308</v>
+        <v>-9.416252281820386</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5207649189602654</v>
+        <v>-0.6049033338982968</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.794844990649729</v>
+        <v>-1.885889995927142</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.085047008753768</v>
+        <v>2.03042000558732</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.331943037843597</v>
+        <v>-9.542289075188675</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5684859076784665</v>
+        <v>-0.6526243226164978</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.769593367839986</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.102891711068728</v>
+        <v>2.04826470790228</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.274871265947667</v>
+        <v>-9.485217303292744</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5416668632336936</v>
+        <v>-0.6258052781717245</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.769593367839986</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.106882046755129</v>
+        <v>2.052255043588681</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.416543107671787</v>
+        <v>-9.626889145016865</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5998108268220834</v>
+        <v>-0.6839492417601143</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.769593367839986</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.105406819856388</v>
+        <v>2.050779816689939</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.366952263246953</v>
+        <v>-9.57729830059203</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5649210788872772</v>
+        <v>-0.6490594938253085</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.720002523415153</v>
+        <v>-1.811047528692566</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.15021473667616</v>
+        <v>2.095587733509712</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.218033928775096</v>
+        <v>-9.428379966120174</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5184048787452178</v>
+        <v>-0.6025432936832487</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.68875293267998</v>
+        <v>-1.779797937957393</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.155913357470581</v>
+        <v>2.101286354304133</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.992188776055684</v>
+        <v>-9.202534813400764</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4184877446212441</v>
+        <v>-0.5026261595592758</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.646826257092816</v>
+        <v>-1.737871262370229</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.190648435859088</v>
+        <v>2.136021432692639</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.867610119718092</v>
+        <v>-9.077956157063172</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3675171375301485</v>
+        <v>-0.4516555524681802</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.646826257092816</v>
+        <v>-1.737871262370229</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.191787580415147</v>
+        <v>2.137160577248698</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.920505407762379</v>
+        <v>-9.130851445107458</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3860414785857555</v>
+        <v>-0.4701798935237873</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.64187091100437</v>
+        <v>-1.732915916281783</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.197394562230322</v>
+        <v>2.142767559063874</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.848372232474498</v>
+        <v>-9.058718269819577</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3514545042319668</v>
+        <v>-0.4355929191699985</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.64187091100437</v>
+        <v>-1.732915916281783</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.203128266468958</v>
+        <v>2.14850126330251</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.777005839864851</v>
+        <v>-8.98735187720993</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.332645209581973</v>
+        <v>-0.4167836245200047</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.570504518394722</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.236210839640882</v>
+        <v>2.181583836474434</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.683546805879626</v>
+        <v>-8.893892843224705</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3051450773007907</v>
+        <v>-0.3892834922388224</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.570504518394722</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.226327358327974</v>
+        <v>2.171700355161526</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.672893624326194</v>
+        <v>-8.883239661671274</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3027183651787917</v>
+        <v>-0.3868567801168235</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.570504518394722</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.224492797828601</v>
+        <v>2.169865794662153</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.574986585649704</v>
+        <v>-8.785332622994783</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2638558646816564</v>
+        <v>-0.3479942796196882</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.502518768534165</v>
+        <v>-1.593563773811579</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.264983932771473</v>
+        <v>2.210356929605025</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.551033044673746</v>
+        <v>-8.761379082018825</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2536059421457795</v>
+        <v>-0.3377443570838112</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.478565227558208</v>
+        <v>-1.569610232835621</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.280024563502542</v>
+        <v>2.225397560336094</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.286973106350949</v>
+        <v>-8.497319143696028</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1612422829784128</v>
+        <v>-0.2453806979164446</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.214505289235412</v>
+        <v>-1.305550294512825</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.425200210334467</v>
+        <v>2.370573207168019</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.579893482846111</v>
+        <v>-7.79023952019119</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1188025327632216</v>
+        <v>0.03466411782518986</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.214505289235412</v>
+        <v>-1.305550294512825</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.422413176674167</v>
+        <v>2.367786173507719</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.53970918447992</v>
+        <v>-7.750055221825</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1352198759975392</v>
+        <v>0.05108146105950739</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.174320990869221</v>
+        <v>-1.265365996146634</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.446867379581723</v>
+        <v>2.392240376415274</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.376309313540558</v>
+        <v>-7.586655350885637</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1999466455940411</v>
+        <v>0.1158082306560093</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.010921119929858</v>
+        <v>-1.101966125207272</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.544274123366097</v>
+        <v>2.489647120199649</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.142828091310959</v>
+        <v>-7.353174128656039</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3012635633237326</v>
+        <v>0.2171251483857009</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7774398977002597</v>
+        <v>-0.8684849029776731</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.692287285541708</v>
+        <v>2.63766028237526</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.993161700303444</v>
+        <v>-7.203507737648524</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3582379094137798</v>
+        <v>0.274099494475748</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6845364064577237</v>
+        <v>-0.7755814117351372</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.745137169974271</v>
+        <v>2.690510166807822</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.860886226672558</v>
+        <v>-7.071232264017637</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4065155856131613</v>
+        <v>0.3223771706751295</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5522609328268371</v>
+        <v>-0.6433059381042505</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.81986994089983</v>
+        <v>2.765242937733382</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.705147894112816</v>
+        <v>-6.915493931457895</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4716259793246946</v>
+        <v>0.3874875643866629</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3965226002670955</v>
+        <v>-0.487567605544509</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.916128001123311</v>
+        <v>2.861500997956863</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.456148095429235</v>
+        <v>-6.666494132774314</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5841322400217859</v>
+        <v>0.4999938250837541</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1475228015835148</v>
+        <v>-0.2385678068609283</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.078434221557119</v>
+        <v>3.023807218390671</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.561738085202339</v>
+        <v>-6.772084122547419</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4139203145133252</v>
+        <v>0.3297818995752935</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2531127913566192</v>
+        <v>-0.3441577966340326</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.887104298094037</v>
+        <v>2.832477294927589</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.580472987320936</v>
+        <v>-6.790819024666016</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4549706955429729</v>
+        <v>0.3708322806049411</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2587088010167505</v>
+        <v>-0.3497538062941639</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.932291034175045</v>
+        <v>2.877664031008597</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.432532945913337</v>
+        <v>-6.642878983258417</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.394267789417845</v>
+        <v>0.3101293744798133</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2383878851081929</v>
+        <v>-0.3294328903856064</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.824604661032012</v>
+        <v>2.769977657865564</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.367574934299284</v>
+        <v>-6.589909461004428</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4115370078099878</v>
+        <v>0.3226031971279304</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1734298734941398</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.854865481746966</v>
+        <v>2.793045384964479</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.324026527528594</v>
+        <v>-6.546361054233738</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4219957584231708</v>
+        <v>0.3330619477411134</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1734298734941398</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.847904869651873</v>
+        <v>2.786084772869386</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.290663321049825</v>
+        <v>-6.512997847754969</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4498033953958216</v>
+        <v>0.3608695847137642</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1734298734941398</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.862367224033016</v>
+        <v>2.800547127250529</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.182404183927304</v>
+        <v>-6.404738710632447</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4876391707040253</v>
+        <v>0.3987053600219679</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1734298734941398</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.856899344492211</v>
+        <v>2.795079247709724</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.059113049110173</v>
+        <v>-6.281447575815316</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5344537186414544</v>
+        <v>0.445519907959397</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.0501387386770093</v>
+        <v>-0.153172233314487</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.928372119393066</v>
+        <v>2.866552022610579</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.037963850206729</v>
+        <v>-6.260298376911873</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5506143764401568</v>
+        <v>0.4616805657580993</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.02898953977356594</v>
+        <v>-0.1320230344110436</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.948762616972457</v>
+        <v>2.88694252018997</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.794198408223285</v>
+        <v>-6.016532934928429</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6439012615805852</v>
+        <v>0.5549674508985278</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.02898953977356594</v>
+        <v>-0.1320230344110436</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.944543325319507</v>
+        <v>2.882723228537021</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.69243558794599</v>
+        <v>-5.914770114651134</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6867307036115196</v>
+        <v>0.5977968929294621</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.01577047138113724</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.954599080274981</v>
+        <v>2.892778983492494</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.442585193996916</v>
+        <v>-5.664919720702059</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7794129361748512</v>
+        <v>0.6904791254927938</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.01577047138113724</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.947341155258683</v>
+        <v>2.885521058476196</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.266693101529484</v>
+        <v>-5.489027628234627</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8533688966824728</v>
+        <v>0.7644350860004154</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.01577047138113724</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.950940278779332</v>
+        <v>2.889120181996845</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.09524663850702</v>
+        <v>-5.317581165212164</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9352749879460118</v>
+        <v>0.8463411772639544</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1556759916413259</v>
+        <v>0.05264249700384821</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.067135662647363</v>
+        <v>3.005315565864877</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.020957072768681</v>
+        <v>-5.243291599473825</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9640112918576444</v>
+        <v>0.875077481175587</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2299655573796652</v>
+        <v>0.1269320627421875</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.110729879706664</v>
+        <v>3.048909782924177</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.957321330534747</v>
+        <v>-5.17965585723989</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9941603898055358</v>
+        <v>0.9052265791234784</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2936012996135997</v>
+        <v>0.190567804976122</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.153606126101342</v>
+        <v>3.091786029318855</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.845894571208826</v>
+        <v>-5.06822909791397</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.019925352319699</v>
+        <v>0.930991541637642</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2936012996135997</v>
+        <v>0.190567804976122</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.134800384885137</v>
+        <v>3.072980288102651</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.856397194274115</v>
+        <v>-5.078731720979259</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.017467379718461</v>
+        <v>0.9285335690364036</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2830986765483108</v>
+        <v>0.1800651819108331</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.130241887670842</v>
+        <v>3.068421790888355</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.784154626102921</v>
+        <v>-5.006489152808064</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.050293720821759</v>
+        <v>0.9613599101397019</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2830986765483108</v>
+        <v>0.1800651819108331</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.134171201505662</v>
+        <v>3.072351104723175</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.766440939225055</v>
+        <v>-4.988775465930199</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.058057779490245</v>
+        <v>0.9691239688081881</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2862800054452276</v>
+        <v>0.18324651080775</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.136758582761152</v>
+        <v>3.074938485978665</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.657636053745328</v>
+        <v>-4.879970580450472</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.09857780490213</v>
+        <v>1.009643994220072</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2862800054452276</v>
+        <v>0.18324651080775</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.133756653981145</v>
+        <v>3.071936557198658</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.437615255708318</v>
+        <v>-4.659949782413461</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.188165161127548</v>
+        <v>1.099231350445491</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4274998505132079</v>
+        <v>0.3244663558757302</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.220067598032547</v>
+        <v>3.158247501250061</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.30474756664504</v>
+        <v>-4.527082093350184</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.257206419554682</v>
+        <v>1.168272608872625</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4274998505132079</v>
+        <v>0.3244663558757302</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.235961780834371</v>
+        <v>3.174141684051884</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.184574483280541</v>
+        <v>-4.406909009985685</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.306421497340784</v>
+        <v>1.217487686658726</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5476729338777069</v>
+        <v>0.4446394392402291</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.309211475293372</v>
+        <v>3.247391378510885</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.039902338180804</v>
+        <v>-4.262236864885947</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.374378457942119</v>
+        <v>1.285444647260061</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6923450789774444</v>
+        <v>0.5893115843399666</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.406102864914654</v>
+        <v>3.344282768132168</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.099777165538496</v>
+        <v>-4.32211169224364</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336466018400468</v>
+        <v>1.24753220771841</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6324702516197522</v>
+        <v>0.5294367569822744</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.356215459901465</v>
+        <v>3.294395363118978</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.979956934627659</v>
+        <v>-4.202291461332803</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.399683279999011</v>
+        <v>1.310749469316953</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6324702516197522</v>
+        <v>0.5294367569822744</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.371504629135674</v>
+        <v>3.309684532353187</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.982426641089465</v>
+        <v>-4.204761167794609</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.30633959673673</v>
+        <v>1.217405786054673</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.630000545157946</v>
+        <v>0.5269670505204682</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.277667004581031</v>
+        <v>3.215846907798545</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.050796827413475</v>
+        <v>-4.273131354118619</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198253383692428</v>
+        <v>1.10931957301037</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.639276244194161</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.202494285488062</v>
+        <v>3.140674188705575</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.064584880260521</v>
+        <v>-4.286919406965666</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.1831748711855</v>
+        <v>1.094241060503442</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.639276244194161</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.192930994119953</v>
+        <v>3.131110897337466</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.120104956153111</v>
+        <v>-4.342439482858255</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.297997677520667</v>
+        <v>1.209063866838609</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.639276244194161</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.329961830812155</v>
+        <v>3.268141734029669</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.944630696360642</v>
+        <v>-4.166965223065786</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.372754613429442</v>
+        <v>1.283820802747385</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.639276244194161</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.334529062803943</v>
+        <v>3.272708966021456</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.05556694900189</v>
+        <v>-4.277901475707035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.30412214113415</v>
+        <v>1.215188330452092</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.639276244194161</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.31027109156515</v>
+        <v>3.248450994782663</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.021903403529608</v>
+        <v>-4.244237930234752</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.246125872724513</v>
+        <v>1.157192062042455</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6729397896664429</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.259007532249969</v>
+        <v>3.197187435467483</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.962050784325885</v>
+        <v>-4.132054857543753</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.280239306838134</v>
+        <v>1.212237677550987</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6729397896664429</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.269179918682101</v>
+        <v>3.207359821899615</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.875807321299507</v>
+        <v>-4.045811394517376</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.309682962622546</v>
+        <v>1.241681333335398</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6729397896664429</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.264126189255962</v>
+        <v>3.202306092473475</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.921114140698487</v>
+        <v>-4.091118213916356</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.283336010307479</v>
+        <v>1.215334381020332</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6321296266572121</v>
+        <v>0.5290961320197343</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.231415866894949</v>
+        <v>3.169595770112462</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.950147245400788</v>
+        <v>-4.120151318618657</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.27227464145966</v>
+        <v>1.204273012172513</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6321296266572121</v>
+        <v>0.5290961320197343</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.23196773992805</v>
+        <v>3.170147643145564</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.857336763949929</v>
+        <v>-4.027340837167797</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.23867152593137</v>
+        <v>1.170669896644222</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7249401081080714</v>
+        <v>0.6219066134705936</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.216926720689932</v>
+        <v>3.155106623907445</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.901726233279357</v>
+        <v>-4.071730306497225</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.222789214124199</v>
+        <v>1.154787584837052</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6805506387786437</v>
+        <v>0.577517144141166</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.192166515016876</v>
+        <v>3.130346418234389</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.018267838384699</v>
+        <v>-4.188271911602567</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.171248280593785</v>
+        <v>1.103246651306638</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.564009033673301</v>
+        <v>0.4609755390358232</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.117317260465393</v>
+        <v>3.055497163682907</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.905890837202027</v>
+        <v>-4.075894910419894</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.221690376897522</v>
+        <v>1.153688747610375</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.564009033673301</v>
+        <v>0.4609755390358232</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.12280855629606</v>
+        <v>3.060988459513574</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.93367123510338</v>
+        <v>-4.103675308321247</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.222075419505519</v>
+        <v>1.154073790218373</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5362286357719479</v>
+        <v>0.4331951411344701</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.117637519323788</v>
+        <v>3.055817422541301</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.052051907833518</v>
+        <v>-4.222055981051385</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.013078870414117</v>
+        <v>0.9450772411269706</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4690107836209717</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.915662528033855</v>
+        <v>2.853842431251369</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.160665986276849</v>
+        <v>-4.330670059494716</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.089782899755991</v>
+        <v>1.021781270468844</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4690107836209717</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.035812188753061</v>
+        <v>2.973992091970574</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.125256948028706</v>
+        <v>-4.295261021246573</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.118459541157571</v>
+        <v>1.050457911870424</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4690107836209717</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.050325214855384</v>
+        <v>2.988505118072897</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.086873285470555</v>
+        <v>-4.256877358688422</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.1312324475232</v>
+        <v>1.063230818236053</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5073944461791229</v>
+        <v>0.4043609515416451</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.070774853732643</v>
+        <v>3.008954756950156</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.909756955435389</v>
+        <v>-4.079761028653256</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.198808008382568</v>
+        <v>1.130806379095421</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5073944461791229</v>
+        <v>0.4043609515416451</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.067503882577945</v>
+        <v>3.005683785795458</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.954849200268935</v>
+        <v>-4.124853273486802</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.181454502211063</v>
+        <v>1.113452872923916</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4454984030097331</v>
+        <v>0.3424649083722553</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.031049648438224</v>
+        <v>2.969229551655738</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.775473779030167</v>
+        <v>-3.945477852248034</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.246991646012984</v>
+        <v>1.178990016725838</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6022751611804518</v>
+        <v>0.499241666542974</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.11890267864707</v>
+        <v>3.057082581864583</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.820487992550774</v>
+        <v>-3.99049206576864</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.209793415936332</v>
+        <v>1.141791786649185</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5719262658658472</v>
+        <v>0.4688927712283694</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.081500796789897</v>
+        <v>3.01968070000741</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.087492502823209</v>
+        <v>-4.257496576041076</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.108683174166303</v>
+        <v>1.040681544879156</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3775632278228986</v>
+        <v>0.2745297331854208</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.970574536303074</v>
+        <v>2.908754439520587</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.188690284260382</v>
+        <v>-4.358694357478249</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.067407983487936</v>
+        <v>0.9994063542007887</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3091544142775794</v>
+        <v>0.2061209196401016</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.928733170072384</v>
+        <v>2.866913073289897</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.182179317646069</v>
+        <v>-4.352183390863936</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.067612331687977</v>
+        <v>0.9996107024008305</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3091544142775794</v>
+        <v>0.2061209196401016</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.9263331316267</v>
+        <v>2.864513034844213</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.163141189938772</v>
+        <v>-4.333145263156639</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.071752301979141</v>
+        <v>1.003750672691994</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2509708029463849</v>
+        <v>0.1479373083089071</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.887947684036228</v>
+        <v>2.826127587253742</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.19426782108939</v>
+        <v>-4.364271894307257</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.178596051153084</v>
+        <v>1.110594421865937</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2509708029463849</v>
+        <v>0.1479373083089071</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.007242085670419</v>
+        <v>2.945421988887932</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.208134582423308</v>
+        <v>-4.378138655641175</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.173882675605651</v>
+        <v>1.105881046318504</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2131128862125619</v>
+        <v>0.1100793915750841</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.985360664616258</v>
+        <v>2.923540567833772</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.163330410883378</v>
+        <v>-4.333334484101245</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.197812874618549</v>
+        <v>1.129811245331402</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2131128862125619</v>
+        <v>0.1100793915750841</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.991369195013184</v>
+        <v>2.929549098230698</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.015587440648376</v>
+        <v>-4.185591513866243</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.154860283989749</v>
+        <v>1.086858654702602</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3809202434474451</v>
+        <v>0.2778867488099673</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.990003830631314</v>
+        <v>2.928183733848827</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.099408661923074</v>
+        <v>-4.269412735140941</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.124125417011351</v>
+        <v>1.056123787724204</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3809202434474451</v>
+        <v>0.2778867488099673</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.992797452162795</v>
+        <v>2.930977355380308</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.09325595587029</v>
+        <v>-4.263260029088157</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.127248847824123</v>
+        <v>1.059247218536976</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3870729495002294</v>
+        <v>0.2840394548627516</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.997151424186124</v>
+        <v>2.935331327403637</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.110065254020792</v>
+        <v>-4.280069327238659</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.119605605304032</v>
+        <v>1.051603976016885</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3702636513497277</v>
+        <v>0.2672301567122499</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.986146322035933</v>
+        <v>2.924326225253446</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.047767255244669</v>
+        <v>-4.217771328462536</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.210860358611302</v>
+        <v>1.142858729324155</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3702636513497277</v>
+        <v>0.2672301567122499</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.052481875832754</v>
+        <v>2.990661779050267</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.845977057579511</v>
+        <v>-4.015981130797378</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.093868439391492</v>
+        <v>1.025866810104346</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5682818435188821</v>
+        <v>0.4652483488814043</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.973584792848373</v>
+        <v>2.911764696065887</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.896863770265706</v>
+        <v>-4.066867843483573</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.14380398663919</v>
+        <v>1.075802357352043</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5173951308326876</v>
+        <v>0.4143616361952098</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.013342997558832</v>
+        <v>2.951522900776345</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.99460431489068</v>
+        <v>-4.164608388108547</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.119335504905243</v>
+        <v>1.051333875618097</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5015058526997074</v>
+        <v>0.3984723580622296</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.018437166795088</v>
+        <v>2.956617070012601</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.054813612895965</v>
+        <v>-4.224817686113832</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.093787766527801</v>
+        <v>1.025786137240654</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4412965546944229</v>
+        <v>0.3382630600569451</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.980847568816588</v>
+        <v>2.919027472034102</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.978391566464039</v>
+        <v>-4.148395639681906</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.1228482031405</v>
+        <v>1.054846573853354</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4412965546944229</v>
+        <v>0.3382630600569451</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.979339186856517</v>
+        <v>2.91751909007403</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.93401843482547</v>
+        <v>-4.104022508043337</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.140460323231364</v>
+        <v>1.072458693944217</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4856696863329915</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.005825933275094</v>
+        <v>2.944005836492608</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.956498785684355</v>
+        <v>-4.126502858902222</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.125861977026401</v>
+        <v>1.057860347739254</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4856696863329915</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.000219727413685</v>
+        <v>2.938399630631198</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.908843055123299</v>
+        <v>-4.01623606340314</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.151306026278628</v>
+        <v>1.108348822966691</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5333254168940471</v>
+        <v>0.4929029871945952</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.035194922778123</v>
+        <v>3.010941464958452</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.808324896624544</v>
+        <v>-3.915717904904385</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.196405663052854</v>
+        <v>1.153448459740918</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6338435753928017</v>
+        <v>0.5934211456933498</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.100398191252101</v>
+        <v>3.07614473343243</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.868991487026933</v>
+        <v>-3.976384495306774</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.158893699367771</v>
+        <v>1.115936496055835</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.552145258674268</v>
+        <v>0.5117228289748161</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.038133873696852</v>
+        <v>3.013880415877181</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.824153085418535</v>
+        <v>-3.931546093698376</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.180926762621759</v>
+        <v>1.137969559309822</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5566886916191375</v>
+        <v>0.5162662619196856</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.044957636074403</v>
+        <v>3.020704178254732</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.843651541660543</v>
+        <v>-3.951044549940384</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.177288319756034</v>
+        <v>1.134331116444097</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5086040503392332</v>
+        <v>0.4681816206397813</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.020267790937538</v>
+        <v>2.996014333117867</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.799448704574643</v>
+        <v>-3.906841712854484</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.200849057118231</v>
+        <v>1.157891853806294</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5528068874251336</v>
+        <v>0.5123844577256818</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.052669095716916</v>
+        <v>3.028415637897245</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.836427732238086</v>
+        <v>-3.943820740517927</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.184467446522101</v>
+        <v>1.141510243210165</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5897807892164642</v>
+        <v>0.5493583595170123</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.073263437260962</v>
+        <v>3.049009979441291</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.678136314698814</v>
+        <v>-3.785529322978655</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.29903177872085</v>
+        <v>1.256074575408913</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5897807892164642</v>
+        <v>0.5493583595170123</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.124511202444001</v>
+        <v>3.10025774462433</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.470494311064338</v>
+        <v>-3.577887319344179</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.380529284768893</v>
+        <v>1.337572081456957</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7974227928509403</v>
+        <v>0.7570003631514884</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24753710921894</v>
+        <v>3.223283651399269</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.41946221834181</v>
+        <v>-3.526855226621651</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.395890350096174</v>
+        <v>1.352933146784238</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8484548855734683</v>
+        <v>0.8080324558740164</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.273104593090727</v>
+        <v>3.248851135271056</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.354238037214604</v>
+        <v>-3.461631045494445</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.439167426639762</v>
+        <v>1.396210223327825</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9136790667006739</v>
+        <v>0.873256637001222</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.329426505859755</v>
+        <v>3.305173048040084</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.316811017143471</v>
+        <v>-3.424204025423311</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.450099206967495</v>
+        <v>1.407142003655559</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9189306047298555</v>
+        <v>0.8785081750304037</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.328538400976544</v>
+        <v>3.304284943156873</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.336922673178179</v>
+        <v>-3.44431568145802</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.443311336884852</v>
+        <v>1.400354133572916</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9299579497272747</v>
+        <v>0.8895355200278229</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.336411600306236</v>
+        <v>3.312158142486565</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.283177858750974</v>
+        <v>-3.390570867030815</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.625367033676945</v>
+        <v>1.582409830365009</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9400212591677367</v>
+        <v>0.8995988294682848</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.503007356991724</v>
+        <v>3.478753899172053</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.208395597725962</v>
+        <v>-3.315788606005802</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.775392847304767</v>
+        <v>1.732435643992831</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.014803520192749</v>
+        <v>0.9743810904932975</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.667989622824549</v>
+        <v>3.643736165004878</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.182311513462154</v>
+        <v>-3.289704521741994</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.777534457024149</v>
+        <v>1.734577253712213</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.014803520192749</v>
+        <v>0.9743810904932975</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.659697598838408</v>
+        <v>3.635444141018737</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.104180332613207</v>
+        <v>-3.211573340893048</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.806980124947508</v>
+        <v>1.764022921635571</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.088980331076434</v>
+        <v>1.048557901376982</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.702396880952398</v>
+        <v>3.678143423132727</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.095287871219924</v>
+        <v>-3.202680879499765</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.828091515231612</v>
+        <v>1.785134311919676</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.088980331076434</v>
+        <v>1.048557901376982</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.71995128667919</v>
+        <v>3.695697828859518</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.263763988189802</v>
+        <v>-3.371156996469642</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.752556115848245</v>
+        <v>1.709598912536309</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.061032495359853</v>
+        <v>1.020610065660401</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.695037632653825</v>
+        <v>3.670784174834154</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.565964459328218</v>
+        <v>-2.673357467608059</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.01294562458074</v>
+        <v>1.969988421268804</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9906844359894427</v>
+        <v>0.9502620062899907</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.634098494219441</v>
+        <v>3.609845036399769</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.543243355645066</v>
+        <v>-2.650636363924907</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.012698088550906</v>
+        <v>1.96974088523897</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9906844359894427</v>
+        <v>0.9502620062899907</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.624762516716345</v>
+        <v>3.600509058896674</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.672445168939108</v>
+        <v>-2.779838177218949</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.119923489084458</v>
+        <v>2.076966285772522</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8614826226954004</v>
+        <v>0.8210601929959485</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.706147554591089</v>
+        <v>3.681894096771418</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.827226175717364</v>
+        <v>-2.934619183997205</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.095088908866802</v>
+        <v>2.052131705554866</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8281149486409243</v>
+        <v>0.7876925189414723</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.72320477265205</v>
+        <v>3.698951314832378</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.82017148550219</v>
+        <v>-2.927564493782031</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.094586140942416</v>
+        <v>2.05162893763048</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8351696388560981</v>
+        <v>0.7947472091566461</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.724112942770699</v>
+        <v>3.699859484951028</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.793220261175702</v>
+        <v>-2.900613269455543</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.115372784317754</v>
+        <v>2.072415581005817</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8500499848838172</v>
+        <v>0.8096275551843652</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.743047304032072</v>
+        <v>3.718793846212401</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784104</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.929173269232018</v>
+        <v>-3.036566277511859</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.245094713240187</v>
+        <v>2.20213750992825</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8500499848838172</v>
+        <v>0.8096275551843652</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.927150436177032</v>
+        <v>3.902896978357361</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.951581387036891</v>
+        <v>-3.058974395316731</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.228248161021231</v>
+        <v>2.185290957709295</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8500499848838172</v>
+        <v>0.8096275551843652</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.919267131080025</v>
+        <v>3.895013673260354</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.09958715451629</v>
+        <v>-3.206980162796131</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.171099853579109</v>
+        <v>2.128142650267172</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7633229760202758</v>
+        <v>0.7229005463208238</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.869284925311538</v>
+        <v>3.845031467491867</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.10902808040482</v>
+        <v>-3.216421088684661</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.223577200945544</v>
+        <v>2.180619997633607</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8857500935636672</v>
+        <v>0.8453276638642152</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.99899491355942</v>
+        <v>3.974741455739748</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.161301687740461</v>
+        <v>-3.268694696020302</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.205558852556588</v>
+        <v>2.162601649244652</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8334764862280259</v>
+        <v>0.793054056528574</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.970521843703336</v>
+        <v>3.946268385883664</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.237631665341367</v>
+        <v>-3.345024673621208</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.173138674410001</v>
+        <v>2.130181471098065</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8334764862280259</v>
+        <v>0.793054056528574</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.968633656597111</v>
+        <v>3.94438019877744</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.439885385665721</v>
+        <v>-3.547278393945561</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.087057415883122</v>
+        <v>2.044100212571186</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6312227659036724</v>
+        <v>0.5908003362042205</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.842101654005361</v>
+        <v>3.81784819618569</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.601453811192976</v>
+        <v>-3.708846819472817</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.020864055882372</v>
+        <v>1.977906852570436</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5044398421057931</v>
+        <v>0.4640174124063411</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.764465909936786</v>
+        <v>3.740212452117115</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.733755103290529</v>
+        <v>-3.84114811157037</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.981016945909269</v>
+        <v>1.938059742597333</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5044398421057931</v>
+        <v>0.4640174124063411</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.777539316802704</v>
+        <v>3.753285858983033</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.919623414129759</v>
+        <v>-4.027016422409599</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.898674818356517</v>
+        <v>1.855717615044581</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3458742487858454</v>
+        <v>0.3054518190863934</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.674405157593676</v>
+        <v>3.650151699774005</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.947524201239232</v>
+        <v>-4.054917209519072</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.88603854463973</v>
+        <v>1.843081341327794</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3112773246429106</v>
+        <v>0.2708548949434586</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.652171044234917</v>
+        <v>3.627917586415246</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787381</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.070050303942126</v>
+        <v>-4.177443312221966</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.833792547535771</v>
+        <v>1.790835344223836</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1887512219400167</v>
+        <v>0.1483287922405647</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.575419826590379</v>
+        <v>3.551166368770708</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.300564800127715</v>
+        <v>-4.407957808407555</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.80829270865204</v>
+        <v>1.765335505340104</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.04176327424557202</v>
+        <v>-0.082185703945024</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.50381708846953</v>
+        <v>3.479563630649859</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.557285618122538</v>
+        <v>-4.664678626402379</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.845916100455957</v>
+        <v>1.802958897144021</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1501778483893869</v>
+        <v>-0.1906002780888388</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.579080062985088</v>
+        <v>3.554826605165417</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.711272035898679</v>
+        <v>-4.81866504417852</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.853301802491141</v>
+        <v>1.810344599179205</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1501778483893869</v>
+        <v>-0.1906002780888388</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.648060332130728</v>
+        <v>3.623806874311057</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.660750132071013</v>
+        <v>-4.768143140350854</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.859561766142328</v>
+        <v>1.816604562830392</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1501778483893869</v>
+        <v>-0.1906002780888388</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.634111534250849</v>
+        <v>3.609858076431177</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609748</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.913225286078737</v>
+        <v>-5.020618294358578</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.770442193594652</v>
+        <v>1.727484990282716</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1501778483893869</v>
+        <v>-0.1906002780888388</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.645982023306263</v>
+        <v>3.621728565486591</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973152</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.206121042558149</v>
+        <v>-5.31351405083799</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.654494425521831</v>
+        <v>1.611537222209895</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1501778483893869</v>
+        <v>-0.1906002780888388</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.647192557825206</v>
+        <v>3.622939100005535</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251941</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.363665114287591</v>
+        <v>-5.471058122567432</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.595598539057376</v>
+        <v>1.55264133574544</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.2170796535296614</v>
+        <v>-0.2575020832291133</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.611173216968363</v>
+        <v>3.586919759148692</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.641629509870865</v>
+        <v>-5.749022518150706</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.479490633560256</v>
+        <v>1.436533430248319</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.3066993878151456</v>
+        <v>-0.3471218175145976</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.552479229133262</v>
+        <v>3.528225771313591</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.758597202509756</v>
+        <v>-5.865990210789596</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.594907613203744</v>
+        <v>1.551950409891807</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.3066993878151456</v>
+        <v>-0.3471218175145976</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.714683285832306</v>
+        <v>3.690429828012635</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.843315144730709</v>
+        <v>-5.95070815301055</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.555867074279177</v>
+        <v>1.51290987096724</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.391815416743192</v>
+        <v>-0.432237846442644</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.658460306439292</v>
+        <v>3.634206848619622</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.925249962999592</v>
+        <v>-6.032642971279433</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.533322564540114</v>
+        <v>1.490365361228178</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.4017501623302722</v>
+        <v>-0.4421725920297241</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.662728876655536</v>
+        <v>3.638475418835864</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.027226085248</v>
+        <v>-6.13461909352784</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.501457754096654</v>
+        <v>1.458500550784717</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.5037262845786797</v>
+        <v>-0.5441487142781317</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.610468841762394</v>
+        <v>3.586215383942722</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.917219801770778</v>
+        <v>-6.024612810050619</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.537613154731718</v>
+        <v>1.494655951419781</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4805217126614045</v>
+        <v>-0.5209441423608565</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.616544472156934</v>
+        <v>3.592291014337263</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.774160226029853</v>
+        <v>-5.881553234309694</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.599086995750062</v>
+        <v>1.556129792438126</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4725082860714253</v>
+        <v>-0.5129307157708772</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.625602538832896</v>
+        <v>3.601349081013224</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.472713500558015</v>
+        <v>-5.580106508837856</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.726926568821333</v>
+        <v>1.683969365509397</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.171061560599588</v>
+        <v>-0.21148399029904</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.813731456998534</v>
+        <v>3.789477999178863</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.497303744793199</v>
+        <v>-5.60469675307304</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.71806164887997</v>
+        <v>1.675104445568034</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.171061560599588</v>
+        <v>-0.21148399029904</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.814702634751245</v>
+        <v>3.790449176931574</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.446265368786679</v>
+        <v>-5.55365837706652</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.739319903662333</v>
+        <v>1.696362700350397</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.171061560599588</v>
+        <v>-0.21148399029904</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.815545539131</v>
+        <v>3.791292081311329</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.405126073920048</v>
+        <v>-5.512519082199889</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.774813720483131</v>
+        <v>1.731856517171195</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.1299222657329572</v>
+        <v>-0.1703446954324092</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.859267214925124</v>
+        <v>3.835013757105453</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.294519933840446</v>
+        <v>-5.401912942120287</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.635240172638907</v>
+        <v>1.59228296932697</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.01931612565335517</v>
+        <v>-0.05973855535280714</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.74181489509682</v>
+        <v>3.717561437277148</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.425100668371289</v>
+        <v>-5.532493676651129</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.586509922900533</v>
+        <v>1.543552719588597</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1498968601841977</v>
+        <v>-0.1903192898836497</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.666968498452278</v>
+        <v>3.642715040632607</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.260604334180327</v>
+        <v>-5.367997342460168</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.636735275653001</v>
+        <v>1.593778072341064</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1498968601841977</v>
+        <v>-0.1903192898836497</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.65139531752836</v>
+        <v>3.627141859708689</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.287974266864759</v>
+        <v>-5.3953672751446</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.624975013015657</v>
+        <v>1.582017809703721</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1498968601841977</v>
+        <v>-0.1903192898836497</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.65058302796479</v>
+        <v>3.626329570145119</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.298359461754648</v>
+        <v>-5.405752470034489</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.630689714184774</v>
+        <v>1.587732510872838</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.160282055074087</v>
+        <v>-0.200704484773539</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.654220690155929</v>
+        <v>3.629967232336258</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.316947620476873</v>
+        <v>-5.424340628756714</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.69409145647231</v>
+        <v>1.651134253160373</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.1788702137963123</v>
+        <v>-0.2192926434957643</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.713904800699019</v>
+        <v>3.689651342879348</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.317246167172909</v>
+        <v>-5.42463917545275</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.690841048612194</v>
+        <v>1.647883845300257</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.1788702137963123</v>
+        <v>-0.2192926434957643</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.710773811517317</v>
+        <v>3.686520353697646</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.216423033482481</v>
+        <v>-5.323816041762322</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.735701197027756</v>
+        <v>1.69274399371582</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.1664059983119585</v>
+        <v>-0.2068284280114105</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.722783235747321</v>
+        <v>3.69852977792765</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.025641672730075</v>
+        <v>-5.133034681009915</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.812142994807262</v>
+        <v>1.769185791495326</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.02437536244044886</v>
+        <v>-0.01604706725900312</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.837381305677309</v>
+        <v>3.813127847857638</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.007124818688254</v>
+        <v>-5.114517826968095</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.799386582161587</v>
+        <v>1.756429378849651</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.03730549186565707</v>
+        <v>-0.003116937833794908</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.82497622907003</v>
+        <v>3.800722771250359</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.981931634186936</v>
+        <v>-5.089324642466777</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.844430792574172</v>
+        <v>1.801473589262236</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.06249867636697543</v>
+        <v>0.02207624666752345</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.87505907638288</v>
+        <v>3.850805618563208</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.969877507273973</v>
+        <v>-5.077270515553814</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.842939011240795</v>
+        <v>1.799981807928859</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.07455280327993824</v>
+        <v>0.03413037358048626</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.875978120432095</v>
+        <v>3.851724662612424</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.976500753964332</v>
+        <v>-5.083893762244172</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.842170342748788</v>
+        <v>1.799213139436851</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.06792955658957989</v>
+        <v>0.02750712689012791</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.873884802602016</v>
+        <v>3.849631344782344</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.873620164435739</v>
+        <v>-4.98101317271558</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.896173604438107</v>
+        <v>1.853216401126171</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.1708101461181728</v>
+        <v>0.1303877164187208</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.948464182197054</v>
+        <v>3.924210724377382</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.897062203615826</v>
+        <v>-5.004455211895666</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.906999458939667</v>
+        <v>1.864042255627731</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.1708101461181728</v>
+        <v>0.1303877164187208</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.968666852370649</v>
+        <v>3.944413394550977</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.915134711907437</v>
+        <v>-5.09964327321058</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.899770455623022</v>
+        <v>1.825967031101765</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.1708101461181728</v>
+        <v>0.1303877164187208</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.968666852370649</v>
+        <v>3.944413394550977</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.867287382469507</v>
+        <v>3.858240217235639</v>
       </c>
       <c r="C2049" t="n">
-        <v>4.179693171172143</v>
+        <v>3.927077607790221</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.943670734237966</v>
+        <v>-5.119552466590925</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.20186845316321</v>
+        <v>1.878900196840104</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.1422741237876444</v>
+        <v>0.1303877164187208</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.26505764544473</v>
+        <v>4.005310237641454</v>
       </c>
     </row>
   </sheetData>
